--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:Q200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -495,7 +495,11 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -561,6 +565,26 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Opted Out?</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Opt-Out Date</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Bounced?</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Bounce Date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -618,6 +642,18 @@
       </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Met at a webinar in July</t>
         </is>
@@ -640,6 +676,10 @@
       <c r="K3" s="5" t="n"/>
       <c r="L3" s="6" t="n"/>
       <c r="M3" s="5" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -658,6 +698,10 @@
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -676,6 +720,10 @@
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="6" t="n"/>
       <c r="M5" s="5" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -694,6 +742,10 @@
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="5" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -712,6 +764,10 @@
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="6" t="n"/>
       <c r="M7" s="5" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -730,6 +786,10 @@
       <c r="K8" s="5" t="n"/>
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="5" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -748,6 +808,10 @@
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="6" t="n"/>
       <c r="M9" s="5" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -766,6 +830,10 @@
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="6" t="n"/>
       <c r="M10" s="5" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -784,6 +852,10 @@
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="6" t="n"/>
       <c r="M11" s="5" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -802,6 +874,10 @@
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="6" t="n"/>
       <c r="M12" s="5" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -820,6 +896,10 @@
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="6" t="n"/>
       <c r="M13" s="5" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -838,6 +918,10 @@
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="6" t="n"/>
       <c r="M14" s="5" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -856,6 +940,10 @@
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="6" t="n"/>
       <c r="M15" s="5" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -874,6 +962,10 @@
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="5" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -892,6 +984,10 @@
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="5" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -910,6 +1006,10 @@
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="6" t="n"/>
       <c r="M18" s="5" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -928,6 +1028,10 @@
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="5" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -946,6 +1050,10 @@
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="6" t="n"/>
       <c r="M20" s="5" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -964,6 +1072,10 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="5" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -982,6 +1094,10 @@
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="6" t="n"/>
       <c r="M22" s="5" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1000,6 +1116,10 @@
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="5" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1018,6 +1138,10 @@
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="6" t="n"/>
       <c r="M24" s="5" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1036,6 +1160,10 @@
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="6" t="n"/>
       <c r="M25" s="5" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1054,6 +1182,10 @@
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="6" t="n"/>
       <c r="M26" s="5" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="6" t="n"/>
+      <c r="Q26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1072,6 +1204,10 @@
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="6" t="n"/>
       <c r="M27" s="5" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1090,6 +1226,10 @@
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="6" t="n"/>
       <c r="M28" s="5" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="6" t="n"/>
+      <c r="Q28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1108,6 +1248,10 @@
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="6" t="n"/>
       <c r="M29" s="5" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1126,6 +1270,10 @@
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="6" t="n"/>
       <c r="M30" s="5" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1144,6 +1292,10 @@
       <c r="K31" s="5" t="n"/>
       <c r="L31" s="6" t="n"/>
       <c r="M31" s="5" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1162,6 +1314,10 @@
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="6" t="n"/>
       <c r="M32" s="5" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1180,6 +1336,10 @@
       <c r="K33" s="5" t="n"/>
       <c r="L33" s="6" t="n"/>
       <c r="M33" s="5" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1198,6 +1358,10 @@
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="6" t="n"/>
       <c r="M34" s="5" t="n"/>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="6" t="n"/>
+      <c r="Q34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1216,6 +1380,10 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="6" t="n"/>
       <c r="M35" s="5" t="n"/>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1234,6 +1402,10 @@
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="6" t="n"/>
       <c r="M36" s="5" t="n"/>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="6" t="n"/>
+      <c r="Q36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1252,6 +1424,10 @@
       <c r="K37" s="5" t="n"/>
       <c r="L37" s="6" t="n"/>
       <c r="M37" s="5" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1270,6 +1446,10 @@
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="6" t="n"/>
       <c r="M38" s="5" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="6" t="n"/>
+      <c r="Q38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1288,6 +1468,10 @@
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="6" t="n"/>
       <c r="M39" s="5" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="6" t="n"/>
+      <c r="Q39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1306,6 +1490,10 @@
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="6" t="n"/>
       <c r="M40" s="5" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="6" t="n"/>
+      <c r="Q40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1324,6 +1512,10 @@
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="6" t="n"/>
       <c r="M41" s="5" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1342,6 +1534,10 @@
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="6" t="n"/>
       <c r="M42" s="5" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="6" t="n"/>
+      <c r="Q42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1360,6 +1556,10 @@
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="6" t="n"/>
       <c r="M43" s="5" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1378,6 +1578,10 @@
       <c r="K44" s="5" t="n"/>
       <c r="L44" s="6" t="n"/>
       <c r="M44" s="5" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="6" t="n"/>
+      <c r="Q44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1396,6 +1600,10 @@
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="6" t="n"/>
       <c r="M45" s="5" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="6" t="n"/>
+      <c r="Q45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1414,6 +1622,10 @@
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="6" t="n"/>
       <c r="M46" s="5" t="n"/>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="6" t="n"/>
+      <c r="Q46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1432,6 +1644,10 @@
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="6" t="n"/>
       <c r="M47" s="5" t="n"/>
+      <c r="N47" s="6" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="6" t="n"/>
+      <c r="Q47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1450,6 +1666,10 @@
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="5" t="n"/>
+      <c r="N48" s="6" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="6" t="n"/>
+      <c r="Q48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1468,6 +1688,10 @@
       <c r="K49" s="5" t="n"/>
       <c r="L49" s="6" t="n"/>
       <c r="M49" s="5" t="n"/>
+      <c r="N49" s="6" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="6" t="n"/>
+      <c r="Q49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1486,6 +1710,10 @@
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="6" t="n"/>
       <c r="M50" s="5" t="n"/>
+      <c r="N50" s="6" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="6" t="n"/>
+      <c r="Q50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -1504,6 +1732,10 @@
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="6" t="n"/>
       <c r="M51" s="5" t="n"/>
+      <c r="N51" s="6" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="6" t="n"/>
+      <c r="Q51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -1522,6 +1754,10 @@
       <c r="K52" s="5" t="n"/>
       <c r="L52" s="6" t="n"/>
       <c r="M52" s="5" t="n"/>
+      <c r="N52" s="6" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="6" t="n"/>
+      <c r="Q52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -1540,6 +1776,10 @@
       <c r="K53" s="5" t="n"/>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="5" t="n"/>
+      <c r="N53" s="6" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="6" t="n"/>
+      <c r="Q53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -1558,6 +1798,10 @@
       <c r="K54" s="5" t="n"/>
       <c r="L54" s="6" t="n"/>
       <c r="M54" s="5" t="n"/>
+      <c r="N54" s="6" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="6" t="n"/>
+      <c r="Q54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -1576,6 +1820,10 @@
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="6" t="n"/>
       <c r="M55" s="5" t="n"/>
+      <c r="N55" s="6" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="6" t="n"/>
+      <c r="Q55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -1594,6 +1842,10 @@
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="6" t="n"/>
       <c r="M56" s="5" t="n"/>
+      <c r="N56" s="6" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="6" t="n"/>
+      <c r="Q56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -1612,6 +1864,10 @@
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="6" t="n"/>
       <c r="M57" s="5" t="n"/>
+      <c r="N57" s="6" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="6" t="n"/>
+      <c r="Q57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -1630,6 +1886,10 @@
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="6" t="n"/>
       <c r="M58" s="5" t="n"/>
+      <c r="N58" s="6" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="6" t="n"/>
+      <c r="Q58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -1648,6 +1908,10 @@
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="6" t="n"/>
       <c r="M59" s="5" t="n"/>
+      <c r="N59" s="6" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="6" t="n"/>
+      <c r="Q59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -1666,6 +1930,10 @@
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="6" t="n"/>
       <c r="M60" s="5" t="n"/>
+      <c r="N60" s="6" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="6" t="n"/>
+      <c r="Q60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -1684,6 +1952,10 @@
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="6" t="n"/>
       <c r="M61" s="5" t="n"/>
+      <c r="N61" s="6" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="6" t="n"/>
+      <c r="Q61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -1702,6 +1974,10 @@
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="6" t="n"/>
       <c r="M62" s="5" t="n"/>
+      <c r="N62" s="6" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="6" t="n"/>
+      <c r="Q62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -1720,6 +1996,10 @@
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="6" t="n"/>
       <c r="M63" s="5" t="n"/>
+      <c r="N63" s="6" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="6" t="n"/>
+      <c r="Q63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -1738,6 +2018,10 @@
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="6" t="n"/>
       <c r="M64" s="5" t="n"/>
+      <c r="N64" s="6" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="6" t="n"/>
+      <c r="Q64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -1756,6 +2040,10 @@
       <c r="K65" s="5" t="n"/>
       <c r="L65" s="6" t="n"/>
       <c r="M65" s="5" t="n"/>
+      <c r="N65" s="6" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="6" t="n"/>
+      <c r="Q65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -1774,6 +2062,10 @@
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="6" t="n"/>
       <c r="M66" s="5" t="n"/>
+      <c r="N66" s="6" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="6" t="n"/>
+      <c r="Q66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -1792,6 +2084,10 @@
       <c r="K67" s="5" t="n"/>
       <c r="L67" s="6" t="n"/>
       <c r="M67" s="5" t="n"/>
+      <c r="N67" s="6" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="6" t="n"/>
+      <c r="Q67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -1810,6 +2106,10 @@
       <c r="K68" s="5" t="n"/>
       <c r="L68" s="6" t="n"/>
       <c r="M68" s="5" t="n"/>
+      <c r="N68" s="6" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="6" t="n"/>
+      <c r="Q68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -1828,6 +2128,10 @@
       <c r="K69" s="5" t="n"/>
       <c r="L69" s="6" t="n"/>
       <c r="M69" s="5" t="n"/>
+      <c r="N69" s="6" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="6" t="n"/>
+      <c r="Q69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -1846,6 +2150,10 @@
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="6" t="n"/>
       <c r="M70" s="5" t="n"/>
+      <c r="N70" s="6" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="6" t="n"/>
+      <c r="Q70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -1864,6 +2172,10 @@
       <c r="K71" s="5" t="n"/>
       <c r="L71" s="6" t="n"/>
       <c r="M71" s="5" t="n"/>
+      <c r="N71" s="6" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="6" t="n"/>
+      <c r="Q71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -1882,6 +2194,10 @@
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="6" t="n"/>
       <c r="M72" s="5" t="n"/>
+      <c r="N72" s="6" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="6" t="n"/>
+      <c r="Q72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -1900,6 +2216,10 @@
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="6" t="n"/>
       <c r="M73" s="5" t="n"/>
+      <c r="N73" s="6" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="6" t="n"/>
+      <c r="Q73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -1918,6 +2238,10 @@
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="6" t="n"/>
       <c r="M74" s="5" t="n"/>
+      <c r="N74" s="6" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="6" t="n"/>
+      <c r="Q74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -1936,6 +2260,10 @@
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="6" t="n"/>
       <c r="M75" s="5" t="n"/>
+      <c r="N75" s="6" t="n"/>
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="6" t="n"/>
+      <c r="Q75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -1954,6 +2282,10 @@
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="6" t="n"/>
       <c r="M76" s="5" t="n"/>
+      <c r="N76" s="6" t="n"/>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="6" t="n"/>
+      <c r="Q76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -1972,6 +2304,10 @@
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="6" t="n"/>
       <c r="M77" s="5" t="n"/>
+      <c r="N77" s="6" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="6" t="n"/>
+      <c r="Q77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -1990,6 +2326,10 @@
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="6" t="n"/>
       <c r="M78" s="5" t="n"/>
+      <c r="N78" s="6" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="6" t="n"/>
+      <c r="Q78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -2008,6 +2348,10 @@
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="6" t="n"/>
       <c r="M79" s="5" t="n"/>
+      <c r="N79" s="6" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="6" t="n"/>
+      <c r="Q79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -2026,6 +2370,10 @@
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="6" t="n"/>
       <c r="M80" s="5" t="n"/>
+      <c r="N80" s="6" t="n"/>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="6" t="n"/>
+      <c r="Q80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -2044,6 +2392,10 @@
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="6" t="n"/>
       <c r="M81" s="5" t="n"/>
+      <c r="N81" s="6" t="n"/>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="6" t="n"/>
+      <c r="Q81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -2062,6 +2414,10 @@
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="6" t="n"/>
       <c r="M82" s="5" t="n"/>
+      <c r="N82" s="6" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="6" t="n"/>
+      <c r="Q82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -2080,6 +2436,10 @@
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="6" t="n"/>
       <c r="M83" s="5" t="n"/>
+      <c r="N83" s="6" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="6" t="n"/>
+      <c r="Q83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -2098,6 +2458,10 @@
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="6" t="n"/>
       <c r="M84" s="5" t="n"/>
+      <c r="N84" s="6" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="6" t="n"/>
+      <c r="Q84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -2116,6 +2480,10 @@
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="6" t="n"/>
       <c r="M85" s="5" t="n"/>
+      <c r="N85" s="6" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="6" t="n"/>
+      <c r="Q85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -2134,6 +2502,10 @@
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="6" t="n"/>
       <c r="M86" s="5" t="n"/>
+      <c r="N86" s="6" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="6" t="n"/>
+      <c r="Q86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -2152,6 +2524,10 @@
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="6" t="n"/>
       <c r="M87" s="5" t="n"/>
+      <c r="N87" s="6" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="6" t="n"/>
+      <c r="Q87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -2170,6 +2546,10 @@
       <c r="K88" s="5" t="n"/>
       <c r="L88" s="6" t="n"/>
       <c r="M88" s="5" t="n"/>
+      <c r="N88" s="6" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="6" t="n"/>
+      <c r="Q88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -2188,6 +2568,10 @@
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="6" t="n"/>
       <c r="M89" s="5" t="n"/>
+      <c r="N89" s="6" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="6" t="n"/>
+      <c r="Q89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -2206,6 +2590,10 @@
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="6" t="n"/>
       <c r="M90" s="5" t="n"/>
+      <c r="N90" s="6" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="6" t="n"/>
+      <c r="Q90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -2224,6 +2612,10 @@
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="6" t="n"/>
       <c r="M91" s="5" t="n"/>
+      <c r="N91" s="6" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="6" t="n"/>
+      <c r="Q91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -2242,6 +2634,10 @@
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="6" t="n"/>
       <c r="M92" s="5" t="n"/>
+      <c r="N92" s="6" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="6" t="n"/>
+      <c r="Q92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -2260,6 +2656,10 @@
       <c r="K93" s="5" t="n"/>
       <c r="L93" s="6" t="n"/>
       <c r="M93" s="5" t="n"/>
+      <c r="N93" s="6" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="6" t="n"/>
+      <c r="Q93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -2278,6 +2678,10 @@
       <c r="K94" s="5" t="n"/>
       <c r="L94" s="6" t="n"/>
       <c r="M94" s="5" t="n"/>
+      <c r="N94" s="6" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="6" t="n"/>
+      <c r="Q94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -2296,6 +2700,10 @@
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="6" t="n"/>
       <c r="M95" s="5" t="n"/>
+      <c r="N95" s="6" t="n"/>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="6" t="n"/>
+      <c r="Q95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -2314,6 +2722,10 @@
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="6" t="n"/>
       <c r="M96" s="5" t="n"/>
+      <c r="N96" s="6" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="6" t="n"/>
+      <c r="Q96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -2332,6 +2744,10 @@
       <c r="K97" s="5" t="n"/>
       <c r="L97" s="6" t="n"/>
       <c r="M97" s="5" t="n"/>
+      <c r="N97" s="6" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="6" t="n"/>
+      <c r="Q97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -2350,6 +2766,10 @@
       <c r="K98" s="5" t="n"/>
       <c r="L98" s="6" t="n"/>
       <c r="M98" s="5" t="n"/>
+      <c r="N98" s="6" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="6" t="n"/>
+      <c r="Q98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -2368,6 +2788,10 @@
       <c r="K99" s="5" t="n"/>
       <c r="L99" s="6" t="n"/>
       <c r="M99" s="5" t="n"/>
+      <c r="N99" s="6" t="n"/>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="6" t="n"/>
+      <c r="Q99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -2386,6 +2810,10 @@
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="6" t="n"/>
       <c r="M100" s="5" t="n"/>
+      <c r="N100" s="6" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="6" t="n"/>
+      <c r="Q100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -2404,6 +2832,10 @@
       <c r="K101" s="5" t="n"/>
       <c r="L101" s="6" t="n"/>
       <c r="M101" s="5" t="n"/>
+      <c r="N101" s="6" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="6" t="n"/>
+      <c r="Q101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -2422,6 +2854,10 @@
       <c r="K102" s="5" t="n"/>
       <c r="L102" s="6" t="n"/>
       <c r="M102" s="5" t="n"/>
+      <c r="N102" s="6" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="6" t="n"/>
+      <c r="Q102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -2440,6 +2876,10 @@
       <c r="K103" s="5" t="n"/>
       <c r="L103" s="6" t="n"/>
       <c r="M103" s="5" t="n"/>
+      <c r="N103" s="6" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="6" t="n"/>
+      <c r="Q103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -2458,6 +2898,10 @@
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="6" t="n"/>
       <c r="M104" s="5" t="n"/>
+      <c r="N104" s="6" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="6" t="n"/>
+      <c r="Q104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -2476,6 +2920,10 @@
       <c r="K105" s="5" t="n"/>
       <c r="L105" s="6" t="n"/>
       <c r="M105" s="5" t="n"/>
+      <c r="N105" s="6" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="6" t="n"/>
+      <c r="Q105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -2494,6 +2942,10 @@
       <c r="K106" s="5" t="n"/>
       <c r="L106" s="6" t="n"/>
       <c r="M106" s="5" t="n"/>
+      <c r="N106" s="6" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="6" t="n"/>
+      <c r="Q106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -2512,6 +2964,10 @@
       <c r="K107" s="5" t="n"/>
       <c r="L107" s="6" t="n"/>
       <c r="M107" s="5" t="n"/>
+      <c r="N107" s="6" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="6" t="n"/>
+      <c r="Q107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -2530,6 +2986,10 @@
       <c r="K108" s="5" t="n"/>
       <c r="L108" s="6" t="n"/>
       <c r="M108" s="5" t="n"/>
+      <c r="N108" s="6" t="n"/>
+      <c r="O108" s="5" t="n"/>
+      <c r="P108" s="6" t="n"/>
+      <c r="Q108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -2548,6 +3008,10 @@
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="6" t="n"/>
       <c r="M109" s="5" t="n"/>
+      <c r="N109" s="6" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="6" t="n"/>
+      <c r="Q109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -2566,6 +3030,10 @@
       <c r="K110" s="5" t="n"/>
       <c r="L110" s="6" t="n"/>
       <c r="M110" s="5" t="n"/>
+      <c r="N110" s="6" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="6" t="n"/>
+      <c r="Q110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -2584,6 +3052,10 @@
       <c r="K111" s="5" t="n"/>
       <c r="L111" s="6" t="n"/>
       <c r="M111" s="5" t="n"/>
+      <c r="N111" s="6" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="6" t="n"/>
+      <c r="Q111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -2602,6 +3074,10 @@
       <c r="K112" s="5" t="n"/>
       <c r="L112" s="6" t="n"/>
       <c r="M112" s="5" t="n"/>
+      <c r="N112" s="6" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="6" t="n"/>
+      <c r="Q112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -2620,6 +3096,10 @@
       <c r="K113" s="5" t="n"/>
       <c r="L113" s="6" t="n"/>
       <c r="M113" s="5" t="n"/>
+      <c r="N113" s="6" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="6" t="n"/>
+      <c r="Q113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -2638,6 +3118,10 @@
       <c r="K114" s="5" t="n"/>
       <c r="L114" s="6" t="n"/>
       <c r="M114" s="5" t="n"/>
+      <c r="N114" s="6" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="6" t="n"/>
+      <c r="Q114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -2656,6 +3140,10 @@
       <c r="K115" s="5" t="n"/>
       <c r="L115" s="6" t="n"/>
       <c r="M115" s="5" t="n"/>
+      <c r="N115" s="6" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="6" t="n"/>
+      <c r="Q115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -2674,6 +3162,10 @@
       <c r="K116" s="5" t="n"/>
       <c r="L116" s="6" t="n"/>
       <c r="M116" s="5" t="n"/>
+      <c r="N116" s="6" t="n"/>
+      <c r="O116" s="5" t="n"/>
+      <c r="P116" s="6" t="n"/>
+      <c r="Q116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -2692,6 +3184,10 @@
       <c r="K117" s="5" t="n"/>
       <c r="L117" s="6" t="n"/>
       <c r="M117" s="5" t="n"/>
+      <c r="N117" s="6" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="6" t="n"/>
+      <c r="Q117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -2710,6 +3206,10 @@
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="6" t="n"/>
       <c r="M118" s="5" t="n"/>
+      <c r="N118" s="6" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="6" t="n"/>
+      <c r="Q118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -2728,6 +3228,10 @@
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="6" t="n"/>
       <c r="M119" s="5" t="n"/>
+      <c r="N119" s="6" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="6" t="n"/>
+      <c r="Q119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -2746,6 +3250,10 @@
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="6" t="n"/>
       <c r="M120" s="5" t="n"/>
+      <c r="N120" s="6" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="6" t="n"/>
+      <c r="Q120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -2764,6 +3272,10 @@
       <c r="K121" s="5" t="n"/>
       <c r="L121" s="6" t="n"/>
       <c r="M121" s="5" t="n"/>
+      <c r="N121" s="6" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="6" t="n"/>
+      <c r="Q121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -2782,6 +3294,10 @@
       <c r="K122" s="5" t="n"/>
       <c r="L122" s="6" t="n"/>
       <c r="M122" s="5" t="n"/>
+      <c r="N122" s="6" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="6" t="n"/>
+      <c r="Q122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -2800,6 +3316,10 @@
       <c r="K123" s="5" t="n"/>
       <c r="L123" s="6" t="n"/>
       <c r="M123" s="5" t="n"/>
+      <c r="N123" s="6" t="n"/>
+      <c r="O123" s="5" t="n"/>
+      <c r="P123" s="6" t="n"/>
+      <c r="Q123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -2818,6 +3338,10 @@
       <c r="K124" s="5" t="n"/>
       <c r="L124" s="6" t="n"/>
       <c r="M124" s="5" t="n"/>
+      <c r="N124" s="6" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="6" t="n"/>
+      <c r="Q124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -2836,6 +3360,10 @@
       <c r="K125" s="5" t="n"/>
       <c r="L125" s="6" t="n"/>
       <c r="M125" s="5" t="n"/>
+      <c r="N125" s="6" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="6" t="n"/>
+      <c r="Q125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -2854,6 +3382,10 @@
       <c r="K126" s="5" t="n"/>
       <c r="L126" s="6" t="n"/>
       <c r="M126" s="5" t="n"/>
+      <c r="N126" s="6" t="n"/>
+      <c r="O126" s="5" t="n"/>
+      <c r="P126" s="6" t="n"/>
+      <c r="Q126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -2872,6 +3404,10 @@
       <c r="K127" s="5" t="n"/>
       <c r="L127" s="6" t="n"/>
       <c r="M127" s="5" t="n"/>
+      <c r="N127" s="6" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="6" t="n"/>
+      <c r="Q127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -2890,6 +3426,10 @@
       <c r="K128" s="5" t="n"/>
       <c r="L128" s="6" t="n"/>
       <c r="M128" s="5" t="n"/>
+      <c r="N128" s="6" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="6" t="n"/>
+      <c r="Q128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -2908,6 +3448,10 @@
       <c r="K129" s="5" t="n"/>
       <c r="L129" s="6" t="n"/>
       <c r="M129" s="5" t="n"/>
+      <c r="N129" s="6" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="6" t="n"/>
+      <c r="Q129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -2926,6 +3470,10 @@
       <c r="K130" s="5" t="n"/>
       <c r="L130" s="6" t="n"/>
       <c r="M130" s="5" t="n"/>
+      <c r="N130" s="6" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="6" t="n"/>
+      <c r="Q130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -2944,6 +3492,10 @@
       <c r="K131" s="5" t="n"/>
       <c r="L131" s="6" t="n"/>
       <c r="M131" s="5" t="n"/>
+      <c r="N131" s="6" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="6" t="n"/>
+      <c r="Q131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -2962,6 +3514,10 @@
       <c r="K132" s="5" t="n"/>
       <c r="L132" s="6" t="n"/>
       <c r="M132" s="5" t="n"/>
+      <c r="N132" s="6" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="6" t="n"/>
+      <c r="Q132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -2980,6 +3536,10 @@
       <c r="K133" s="5" t="n"/>
       <c r="L133" s="6" t="n"/>
       <c r="M133" s="5" t="n"/>
+      <c r="N133" s="6" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="6" t="n"/>
+      <c r="Q133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -2998,6 +3558,10 @@
       <c r="K134" s="5" t="n"/>
       <c r="L134" s="6" t="n"/>
       <c r="M134" s="5" t="n"/>
+      <c r="N134" s="6" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="6" t="n"/>
+      <c r="Q134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -3016,6 +3580,10 @@
       <c r="K135" s="5" t="n"/>
       <c r="L135" s="6" t="n"/>
       <c r="M135" s="5" t="n"/>
+      <c r="N135" s="6" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="6" t="n"/>
+      <c r="Q135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -3034,6 +3602,10 @@
       <c r="K136" s="5" t="n"/>
       <c r="L136" s="6" t="n"/>
       <c r="M136" s="5" t="n"/>
+      <c r="N136" s="6" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="6" t="n"/>
+      <c r="Q136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -3052,6 +3624,10 @@
       <c r="K137" s="5" t="n"/>
       <c r="L137" s="6" t="n"/>
       <c r="M137" s="5" t="n"/>
+      <c r="N137" s="6" t="n"/>
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="6" t="n"/>
+      <c r="Q137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -3070,6 +3646,10 @@
       <c r="K138" s="5" t="n"/>
       <c r="L138" s="6" t="n"/>
       <c r="M138" s="5" t="n"/>
+      <c r="N138" s="6" t="n"/>
+      <c r="O138" s="5" t="n"/>
+      <c r="P138" s="6" t="n"/>
+      <c r="Q138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -3088,6 +3668,10 @@
       <c r="K139" s="5" t="n"/>
       <c r="L139" s="6" t="n"/>
       <c r="M139" s="5" t="n"/>
+      <c r="N139" s="6" t="n"/>
+      <c r="O139" s="5" t="n"/>
+      <c r="P139" s="6" t="n"/>
+      <c r="Q139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -3106,6 +3690,10 @@
       <c r="K140" s="5" t="n"/>
       <c r="L140" s="6" t="n"/>
       <c r="M140" s="5" t="n"/>
+      <c r="N140" s="6" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="6" t="n"/>
+      <c r="Q140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -3124,6 +3712,10 @@
       <c r="K141" s="5" t="n"/>
       <c r="L141" s="6" t="n"/>
       <c r="M141" s="5" t="n"/>
+      <c r="N141" s="6" t="n"/>
+      <c r="O141" s="5" t="n"/>
+      <c r="P141" s="6" t="n"/>
+      <c r="Q141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -3142,6 +3734,10 @@
       <c r="K142" s="5" t="n"/>
       <c r="L142" s="6" t="n"/>
       <c r="M142" s="5" t="n"/>
+      <c r="N142" s="6" t="n"/>
+      <c r="O142" s="5" t="n"/>
+      <c r="P142" s="6" t="n"/>
+      <c r="Q142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -3160,6 +3756,10 @@
       <c r="K143" s="5" t="n"/>
       <c r="L143" s="6" t="n"/>
       <c r="M143" s="5" t="n"/>
+      <c r="N143" s="6" t="n"/>
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="6" t="n"/>
+      <c r="Q143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -3178,6 +3778,10 @@
       <c r="K144" s="5" t="n"/>
       <c r="L144" s="6" t="n"/>
       <c r="M144" s="5" t="n"/>
+      <c r="N144" s="6" t="n"/>
+      <c r="O144" s="5" t="n"/>
+      <c r="P144" s="6" t="n"/>
+      <c r="Q144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -3196,6 +3800,10 @@
       <c r="K145" s="5" t="n"/>
       <c r="L145" s="6" t="n"/>
       <c r="M145" s="5" t="n"/>
+      <c r="N145" s="6" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="6" t="n"/>
+      <c r="Q145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -3214,6 +3822,10 @@
       <c r="K146" s="5" t="n"/>
       <c r="L146" s="6" t="n"/>
       <c r="M146" s="5" t="n"/>
+      <c r="N146" s="6" t="n"/>
+      <c r="O146" s="5" t="n"/>
+      <c r="P146" s="6" t="n"/>
+      <c r="Q146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -3232,6 +3844,10 @@
       <c r="K147" s="5" t="n"/>
       <c r="L147" s="6" t="n"/>
       <c r="M147" s="5" t="n"/>
+      <c r="N147" s="6" t="n"/>
+      <c r="O147" s="5" t="n"/>
+      <c r="P147" s="6" t="n"/>
+      <c r="Q147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -3250,6 +3866,10 @@
       <c r="K148" s="5" t="n"/>
       <c r="L148" s="6" t="n"/>
       <c r="M148" s="5" t="n"/>
+      <c r="N148" s="6" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="6" t="n"/>
+      <c r="Q148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -3268,6 +3888,10 @@
       <c r="K149" s="5" t="n"/>
       <c r="L149" s="6" t="n"/>
       <c r="M149" s="5" t="n"/>
+      <c r="N149" s="6" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="6" t="n"/>
+      <c r="Q149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -3286,6 +3910,10 @@
       <c r="K150" s="5" t="n"/>
       <c r="L150" s="6" t="n"/>
       <c r="M150" s="5" t="n"/>
+      <c r="N150" s="6" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="6" t="n"/>
+      <c r="Q150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -3304,6 +3932,10 @@
       <c r="K151" s="5" t="n"/>
       <c r="L151" s="6" t="n"/>
       <c r="M151" s="5" t="n"/>
+      <c r="N151" s="6" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="6" t="n"/>
+      <c r="Q151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -3322,6 +3954,10 @@
       <c r="K152" s="5" t="n"/>
       <c r="L152" s="6" t="n"/>
       <c r="M152" s="5" t="n"/>
+      <c r="N152" s="6" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="6" t="n"/>
+      <c r="Q152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -3340,6 +3976,10 @@
       <c r="K153" s="5" t="n"/>
       <c r="L153" s="6" t="n"/>
       <c r="M153" s="5" t="n"/>
+      <c r="N153" s="6" t="n"/>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="6" t="n"/>
+      <c r="Q153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -3358,6 +3998,10 @@
       <c r="K154" s="5" t="n"/>
       <c r="L154" s="6" t="n"/>
       <c r="M154" s="5" t="n"/>
+      <c r="N154" s="6" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="6" t="n"/>
+      <c r="Q154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -3376,6 +4020,10 @@
       <c r="K155" s="5" t="n"/>
       <c r="L155" s="6" t="n"/>
       <c r="M155" s="5" t="n"/>
+      <c r="N155" s="6" t="n"/>
+      <c r="O155" s="5" t="n"/>
+      <c r="P155" s="6" t="n"/>
+      <c r="Q155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -3394,6 +4042,10 @@
       <c r="K156" s="5" t="n"/>
       <c r="L156" s="6" t="n"/>
       <c r="M156" s="5" t="n"/>
+      <c r="N156" s="6" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="6" t="n"/>
+      <c r="Q156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -3412,6 +4064,10 @@
       <c r="K157" s="5" t="n"/>
       <c r="L157" s="6" t="n"/>
       <c r="M157" s="5" t="n"/>
+      <c r="N157" s="6" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="6" t="n"/>
+      <c r="Q157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -3430,6 +4086,10 @@
       <c r="K158" s="5" t="n"/>
       <c r="L158" s="6" t="n"/>
       <c r="M158" s="5" t="n"/>
+      <c r="N158" s="6" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="6" t="n"/>
+      <c r="Q158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -3448,6 +4108,10 @@
       <c r="K159" s="5" t="n"/>
       <c r="L159" s="6" t="n"/>
       <c r="M159" s="5" t="n"/>
+      <c r="N159" s="6" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="6" t="n"/>
+      <c r="Q159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -3466,6 +4130,10 @@
       <c r="K160" s="5" t="n"/>
       <c r="L160" s="6" t="n"/>
       <c r="M160" s="5" t="n"/>
+      <c r="N160" s="6" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="6" t="n"/>
+      <c r="Q160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -3484,6 +4152,10 @@
       <c r="K161" s="5" t="n"/>
       <c r="L161" s="6" t="n"/>
       <c r="M161" s="5" t="n"/>
+      <c r="N161" s="6" t="n"/>
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="6" t="n"/>
+      <c r="Q161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -3502,6 +4174,10 @@
       <c r="K162" s="5" t="n"/>
       <c r="L162" s="6" t="n"/>
       <c r="M162" s="5" t="n"/>
+      <c r="N162" s="6" t="n"/>
+      <c r="O162" s="5" t="n"/>
+      <c r="P162" s="6" t="n"/>
+      <c r="Q162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -3520,6 +4196,10 @@
       <c r="K163" s="5" t="n"/>
       <c r="L163" s="6" t="n"/>
       <c r="M163" s="5" t="n"/>
+      <c r="N163" s="6" t="n"/>
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="6" t="n"/>
+      <c r="Q163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -3538,6 +4218,10 @@
       <c r="K164" s="5" t="n"/>
       <c r="L164" s="6" t="n"/>
       <c r="M164" s="5" t="n"/>
+      <c r="N164" s="6" t="n"/>
+      <c r="O164" s="5" t="n"/>
+      <c r="P164" s="6" t="n"/>
+      <c r="Q164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -3556,6 +4240,10 @@
       <c r="K165" s="5" t="n"/>
       <c r="L165" s="6" t="n"/>
       <c r="M165" s="5" t="n"/>
+      <c r="N165" s="6" t="n"/>
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="6" t="n"/>
+      <c r="Q165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -3574,6 +4262,10 @@
       <c r="K166" s="5" t="n"/>
       <c r="L166" s="6" t="n"/>
       <c r="M166" s="5" t="n"/>
+      <c r="N166" s="6" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="6" t="n"/>
+      <c r="Q166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -3592,6 +4284,10 @@
       <c r="K167" s="5" t="n"/>
       <c r="L167" s="6" t="n"/>
       <c r="M167" s="5" t="n"/>
+      <c r="N167" s="6" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="6" t="n"/>
+      <c r="Q167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -3610,6 +4306,10 @@
       <c r="K168" s="5" t="n"/>
       <c r="L168" s="6" t="n"/>
       <c r="M168" s="5" t="n"/>
+      <c r="N168" s="6" t="n"/>
+      <c r="O168" s="5" t="n"/>
+      <c r="P168" s="6" t="n"/>
+      <c r="Q168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -3628,6 +4328,10 @@
       <c r="K169" s="5" t="n"/>
       <c r="L169" s="6" t="n"/>
       <c r="M169" s="5" t="n"/>
+      <c r="N169" s="6" t="n"/>
+      <c r="O169" s="5" t="n"/>
+      <c r="P169" s="6" t="n"/>
+      <c r="Q169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -3646,6 +4350,10 @@
       <c r="K170" s="5" t="n"/>
       <c r="L170" s="6" t="n"/>
       <c r="M170" s="5" t="n"/>
+      <c r="N170" s="6" t="n"/>
+      <c r="O170" s="5" t="n"/>
+      <c r="P170" s="6" t="n"/>
+      <c r="Q170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -3664,6 +4372,10 @@
       <c r="K171" s="5" t="n"/>
       <c r="L171" s="6" t="n"/>
       <c r="M171" s="5" t="n"/>
+      <c r="N171" s="6" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="6" t="n"/>
+      <c r="Q171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -3682,6 +4394,10 @@
       <c r="K172" s="5" t="n"/>
       <c r="L172" s="6" t="n"/>
       <c r="M172" s="5" t="n"/>
+      <c r="N172" s="6" t="n"/>
+      <c r="O172" s="5" t="n"/>
+      <c r="P172" s="6" t="n"/>
+      <c r="Q172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -3700,6 +4416,10 @@
       <c r="K173" s="5" t="n"/>
       <c r="L173" s="6" t="n"/>
       <c r="M173" s="5" t="n"/>
+      <c r="N173" s="6" t="n"/>
+      <c r="O173" s="5" t="n"/>
+      <c r="P173" s="6" t="n"/>
+      <c r="Q173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -3718,6 +4438,10 @@
       <c r="K174" s="5" t="n"/>
       <c r="L174" s="6" t="n"/>
       <c r="M174" s="5" t="n"/>
+      <c r="N174" s="6" t="n"/>
+      <c r="O174" s="5" t="n"/>
+      <c r="P174" s="6" t="n"/>
+      <c r="Q174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -3736,6 +4460,10 @@
       <c r="K175" s="5" t="n"/>
       <c r="L175" s="6" t="n"/>
       <c r="M175" s="5" t="n"/>
+      <c r="N175" s="6" t="n"/>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="6" t="n"/>
+      <c r="Q175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -3754,6 +4482,10 @@
       <c r="K176" s="5" t="n"/>
       <c r="L176" s="6" t="n"/>
       <c r="M176" s="5" t="n"/>
+      <c r="N176" s="6" t="n"/>
+      <c r="O176" s="5" t="n"/>
+      <c r="P176" s="6" t="n"/>
+      <c r="Q176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -3772,6 +4504,10 @@
       <c r="K177" s="5" t="n"/>
       <c r="L177" s="6" t="n"/>
       <c r="M177" s="5" t="n"/>
+      <c r="N177" s="6" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="6" t="n"/>
+      <c r="Q177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -3790,6 +4526,10 @@
       <c r="K178" s="5" t="n"/>
       <c r="L178" s="6" t="n"/>
       <c r="M178" s="5" t="n"/>
+      <c r="N178" s="6" t="n"/>
+      <c r="O178" s="5" t="n"/>
+      <c r="P178" s="6" t="n"/>
+      <c r="Q178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -3808,6 +4548,10 @@
       <c r="K179" s="5" t="n"/>
       <c r="L179" s="6" t="n"/>
       <c r="M179" s="5" t="n"/>
+      <c r="N179" s="6" t="n"/>
+      <c r="O179" s="5" t="n"/>
+      <c r="P179" s="6" t="n"/>
+      <c r="Q179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -3826,6 +4570,10 @@
       <c r="K180" s="5" t="n"/>
       <c r="L180" s="6" t="n"/>
       <c r="M180" s="5" t="n"/>
+      <c r="N180" s="6" t="n"/>
+      <c r="O180" s="5" t="n"/>
+      <c r="P180" s="6" t="n"/>
+      <c r="Q180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -3844,6 +4592,10 @@
       <c r="K181" s="5" t="n"/>
       <c r="L181" s="6" t="n"/>
       <c r="M181" s="5" t="n"/>
+      <c r="N181" s="6" t="n"/>
+      <c r="O181" s="5" t="n"/>
+      <c r="P181" s="6" t="n"/>
+      <c r="Q181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -3862,6 +4614,10 @@
       <c r="K182" s="5" t="n"/>
       <c r="L182" s="6" t="n"/>
       <c r="M182" s="5" t="n"/>
+      <c r="N182" s="6" t="n"/>
+      <c r="O182" s="5" t="n"/>
+      <c r="P182" s="6" t="n"/>
+      <c r="Q182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -3880,6 +4636,10 @@
       <c r="K183" s="5" t="n"/>
       <c r="L183" s="6" t="n"/>
       <c r="M183" s="5" t="n"/>
+      <c r="N183" s="6" t="n"/>
+      <c r="O183" s="5" t="n"/>
+      <c r="P183" s="6" t="n"/>
+      <c r="Q183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -3898,6 +4658,10 @@
       <c r="K184" s="5" t="n"/>
       <c r="L184" s="6" t="n"/>
       <c r="M184" s="5" t="n"/>
+      <c r="N184" s="6" t="n"/>
+      <c r="O184" s="5" t="n"/>
+      <c r="P184" s="6" t="n"/>
+      <c r="Q184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -3916,6 +4680,10 @@
       <c r="K185" s="5" t="n"/>
       <c r="L185" s="6" t="n"/>
       <c r="M185" s="5" t="n"/>
+      <c r="N185" s="6" t="n"/>
+      <c r="O185" s="5" t="n"/>
+      <c r="P185" s="6" t="n"/>
+      <c r="Q185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -3934,6 +4702,10 @@
       <c r="K186" s="5" t="n"/>
       <c r="L186" s="6" t="n"/>
       <c r="M186" s="5" t="n"/>
+      <c r="N186" s="6" t="n"/>
+      <c r="O186" s="5" t="n"/>
+      <c r="P186" s="6" t="n"/>
+      <c r="Q186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -3952,6 +4724,10 @@
       <c r="K187" s="5" t="n"/>
       <c r="L187" s="6" t="n"/>
       <c r="M187" s="5" t="n"/>
+      <c r="N187" s="6" t="n"/>
+      <c r="O187" s="5" t="n"/>
+      <c r="P187" s="6" t="n"/>
+      <c r="Q187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -3970,6 +4746,10 @@
       <c r="K188" s="5" t="n"/>
       <c r="L188" s="6" t="n"/>
       <c r="M188" s="5" t="n"/>
+      <c r="N188" s="6" t="n"/>
+      <c r="O188" s="5" t="n"/>
+      <c r="P188" s="6" t="n"/>
+      <c r="Q188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -3988,6 +4768,10 @@
       <c r="K189" s="5" t="n"/>
       <c r="L189" s="6" t="n"/>
       <c r="M189" s="5" t="n"/>
+      <c r="N189" s="6" t="n"/>
+      <c r="O189" s="5" t="n"/>
+      <c r="P189" s="6" t="n"/>
+      <c r="Q189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -4006,6 +4790,10 @@
       <c r="K190" s="5" t="n"/>
       <c r="L190" s="6" t="n"/>
       <c r="M190" s="5" t="n"/>
+      <c r="N190" s="6" t="n"/>
+      <c r="O190" s="5" t="n"/>
+      <c r="P190" s="6" t="n"/>
+      <c r="Q190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -4024,6 +4812,10 @@
       <c r="K191" s="5" t="n"/>
       <c r="L191" s="6" t="n"/>
       <c r="M191" s="5" t="n"/>
+      <c r="N191" s="6" t="n"/>
+      <c r="O191" s="5" t="n"/>
+      <c r="P191" s="6" t="n"/>
+      <c r="Q191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -4042,6 +4834,10 @@
       <c r="K192" s="5" t="n"/>
       <c r="L192" s="6" t="n"/>
       <c r="M192" s="5" t="n"/>
+      <c r="N192" s="6" t="n"/>
+      <c r="O192" s="5" t="n"/>
+      <c r="P192" s="6" t="n"/>
+      <c r="Q192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -4060,6 +4856,10 @@
       <c r="K193" s="5" t="n"/>
       <c r="L193" s="6" t="n"/>
       <c r="M193" s="5" t="n"/>
+      <c r="N193" s="6" t="n"/>
+      <c r="O193" s="5" t="n"/>
+      <c r="P193" s="6" t="n"/>
+      <c r="Q193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -4078,6 +4878,10 @@
       <c r="K194" s="5" t="n"/>
       <c r="L194" s="6" t="n"/>
       <c r="M194" s="5" t="n"/>
+      <c r="N194" s="6" t="n"/>
+      <c r="O194" s="5" t="n"/>
+      <c r="P194" s="6" t="n"/>
+      <c r="Q194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -4096,6 +4900,10 @@
       <c r="K195" s="5" t="n"/>
       <c r="L195" s="6" t="n"/>
       <c r="M195" s="5" t="n"/>
+      <c r="N195" s="6" t="n"/>
+      <c r="O195" s="5" t="n"/>
+      <c r="P195" s="6" t="n"/>
+      <c r="Q195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -4114,6 +4922,10 @@
       <c r="K196" s="5" t="n"/>
       <c r="L196" s="6" t="n"/>
       <c r="M196" s="5" t="n"/>
+      <c r="N196" s="6" t="n"/>
+      <c r="O196" s="5" t="n"/>
+      <c r="P196" s="6" t="n"/>
+      <c r="Q196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -4132,6 +4944,10 @@
       <c r="K197" s="5" t="n"/>
       <c r="L197" s="6" t="n"/>
       <c r="M197" s="5" t="n"/>
+      <c r="N197" s="6" t="n"/>
+      <c r="O197" s="5" t="n"/>
+      <c r="P197" s="6" t="n"/>
+      <c r="Q197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -4150,6 +4966,10 @@
       <c r="K198" s="5" t="n"/>
       <c r="L198" s="6" t="n"/>
       <c r="M198" s="5" t="n"/>
+      <c r="N198" s="6" t="n"/>
+      <c r="O198" s="5" t="n"/>
+      <c r="P198" s="6" t="n"/>
+      <c r="Q198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -4168,6 +4988,10 @@
       <c r="K199" s="5" t="n"/>
       <c r="L199" s="6" t="n"/>
       <c r="M199" s="5" t="n"/>
+      <c r="N199" s="6" t="n"/>
+      <c r="O199" s="5" t="n"/>
+      <c r="P199" s="6" t="n"/>
+      <c r="Q199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -4186,16 +5010,26 @@
       <c r="K200" s="5" t="n"/>
       <c r="L200" s="6" t="n"/>
       <c r="M200" s="5" t="n"/>
+      <c r="N200" s="6" t="n"/>
+      <c r="O200" s="5" t="n"/>
+      <c r="P200" s="6" t="n"/>
+      <c r="Q200" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation sqref="F2:F201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"New,Email 1 Sent,Follow-up 1 Sent,Follow-up 2 Sent,Replied,LinkedIn Connected,LinkedIn Msg Sent,Booked,Not Interested,Cold"</formula1>
+      <formula1>"New,Email 1 Sent,Follow-up 1 Sent,Follow-up 2 Sent,Replied,LinkedIn Connected,LinkedIn Msg Sent,Booked,Not Interested,Opted Out,Bounced,Cold"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Send Initial Email,Send Follow-up Email,Send LinkedIn Connection Note,Send LinkedIn Follow-up,Wait,Mark Booked,None"</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4209,7 +5043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4270,7 +5104,21 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7. See email_templates.md and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>7. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>8. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>9. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -660,554 +660,1798 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Subhadeep Ghosh</t>
+        </is>
+      </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/subhadeep-ghosh-221b007</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H3" s="5">
         <f>IF(G3="","",TODAY()-G3)</f>
         <v/>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="n"/>
-      <c r="M3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N3" s="6" t="n"/>
-      <c r="O3" s="5" t="n"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="5" t="n"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Presales Solutions Consultant role at Tata Consultancy Services</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Anas Aljarrah</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>anas.aljarrah@motorolasolutions.com</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anas-aljarrah</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H4" s="5">
         <f>IF(G4="","",TODAY()-G4)</f>
         <v/>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="n"/>
-      <c r="M4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N4" s="6" t="n"/>
-      <c r="O4" s="5" t="n"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="5" t="n"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Annabi</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>hugo@edko.io</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/hugo-annabi</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H5" s="5">
         <f>IF(G5="","",TODAY()-G5)</f>
         <v/>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="5" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N5" s="6" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="5" t="n"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bedirhan Akay</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>bedirhan.akay@apollo.eco</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bedirhan-a-614b09105</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H6" s="5">
         <f>IF(G6="","",TODAY()-G6)</f>
         <v/>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="n"/>
-      <c r="M6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N6" s="6" t="n"/>
-      <c r="O6" s="5" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="5" t="n"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Sakshi Maheshwari</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>sakmahes@cisco.com</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sakshimaheshwari19</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H7" s="5">
         <f>IF(G7="","",TODAY()-G7)</f>
         <v/>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="5" t="n"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N7" s="6" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="5" t="n"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Mehdi Rabia</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>mehdi.rabia@flatpay.com</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/mehdi-rabia-346189389</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Bounced - LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H8" s="5">
         <f>IF(G8="","",TODAY()-G8)</f>
         <v/>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="n"/>
-      <c r="M8" s="5" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N8" s="6" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="5" t="n"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12, bounced same day (Address not found - the address couldn't be found, or is unable to receive mail.). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Nael Ayadi</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>nael.ayadi@papernest.com</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/nael-ayadi-sports-business-consulting</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H9" s="5">
         <f>IF(G9="","",TODAY()-G9)</f>
         <v/>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="n"/>
-      <c r="M9" s="5" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="5" t="n"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Joel Masats</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>joel.masats@driverevel.com</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/joel-masats-81a035259</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H10" s="5">
         <f>IF(G10="","",TODAY()-G10)</f>
         <v/>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="n"/>
-      <c r="M10" s="5" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="5" t="n"/>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="5" t="n"/>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Rohit Saha</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>rohit@ramd.am</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rohittsaha</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H11" s="5">
         <f>IF(G11="","",TODAY()-G11)</f>
         <v/>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="n"/>
-      <c r="M11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="5" t="n"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="5" t="n"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Suvendu Sutar</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>suvendu.sutar@wipro.com</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/suvendu-sutar-1b3360178</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H12" s="5">
         <f>IF(G12="","",TODAY()-G12)</f>
         <v/>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="n"/>
-      <c r="M12" s="5" t="n"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="5" t="n"/>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="5" t="n"/>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Adrien Gagniere</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>adrien@in-leed.com</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/adrien-gagniere-902996263</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Bounced - LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H13" s="5">
         <f>IF(G13="","",TODAY()-G13)</f>
         <v/>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="n"/>
-      <c r="M13" s="5" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="5" t="n"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12, bounced same day (550 No Such User (address not found)). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Boris-Mihail Todorov</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>boris.todorov@paynetics.digital</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/boris-mihail-todorov</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H14" s="5">
         <f>IF(G14="","",TODAY()-G14)</f>
         <v/>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="n"/>
-      <c r="M14" s="5" t="n"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="5" t="n"/>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="5" t="n"/>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Souhaila Bouquoyoue</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>souhaila.bouquoyoue@berger-levrault.com</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/souhaila-bouquoyoue</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H15" s="5">
         <f>IF(G15="","",TODAY()-G15)</f>
         <v/>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="5" t="n"/>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="5" t="n"/>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Paulina Nordgren</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>paulina.nordgren@wolterskluwer.com</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/paulinanordgren</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Bounced - LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H16" s="5">
         <f>IF(G16="","",TODAY()-G16)</f>
         <v/>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="n"/>
-      <c r="M16" s="5" t="n"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="5" t="n"/>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12, bounced same day (550 5.7.1 Service unavailable / message blocked). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Tanishq Munjal</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>tanishq@speargrowth.com</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/tanishq-munjal</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H17" s="5">
         <f>IF(G17="","",TODAY()-G17)</f>
         <v/>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="n"/>
-      <c r="M17" s="5" t="n"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="5" t="n"/>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="5" t="n"/>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Business Development Representative &amp; Account Executive role at Spear Growth</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Siddharth Srivastava</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>siddharth.srivastava@o9solutions.com</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/siddharth-srivastava-1b32b3202</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H18" s="5">
         <f>IF(G18="","",TODAY()-G18)</f>
         <v/>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="n"/>
-      <c r="M18" s="5" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="5" t="n"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="5" t="n"/>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Katie Collopy</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>katie@maverickmedia.eu</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/katie-collopy-37a0191a1</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H19" s="5">
         <f>IF(G19="","",TODAY()-G19)</f>
         <v/>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="n"/>
-      <c r="M19" s="5" t="n"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="5" t="n"/>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="5" t="n"/>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales and Business Development Representative role at Maverick Media</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Ines Diallo</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>ines.diallo@infinit.com</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/in%c3%a8s-diallo-918447172</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H20" s="5">
         <f>IF(G20="","",TODAY()-G20)</f>
         <v/>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="n"/>
-      <c r="M20" s="5" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="5" t="n"/>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="5" t="n"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Lin Ye</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>lin.ye@siemens.com</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/lin-ye-171224178</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H21" s="5">
         <f>IF(G21="","",TODAY()-G21)</f>
         <v/>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="n"/>
-      <c r="M21" s="5" t="n"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="5" t="n"/>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="5" t="n"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Samuel Sebban</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>samuel.sebban@pytheascapital.com</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/samuel-sebban-1b1054231</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H22" s="5">
         <f>IF(G22="","",TODAY()-G22)</f>
         <v/>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="n"/>
-      <c r="M22" s="5" t="n"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="5" t="n"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="5" t="n"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Come Belmokadem</t>
+        </is>
+      </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/c%c3%b4me-melis-belmokadem-390094344</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H23" s="5">
         <f>IF(G23="","",TODAY()-G23)</f>
         <v/>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="n"/>
-      <c r="M23" s="5" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="5" t="n"/>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="5" t="n"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales Business Development Representative role at Luxiris</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Franco Rizzi</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>franco.rizzi@siemens.com</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/frizzi</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Drafted</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H24" s="5">
         <f>IF(G24="","",TODAY()-G24)</f>
         <v/>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="n"/>
-      <c r="M24" s="5" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N24" s="6" t="n"/>
-      <c r="O24" s="5" t="n"/>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="5" t="n"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Dagmar Ilisson</t>
+        </is>
+      </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dagmar-ilisson-962358212</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H25" s="5">
         <f>IF(G25="","",TODAY()-G25)</f>
         <v/>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="n"/>
-      <c r="M25" s="5" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N25" s="6" t="n"/>
-      <c r="O25" s="5" t="n"/>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="5" t="n"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales and Business Development Representative role at Eversports</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Umut Ateș</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/umut-ate%c8%99-172743164</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Connection Requested</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="H26" s="5">
         <f>IF(G26="","",TODAY()-G26)</f>
         <v/>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Message 1 (if connected)</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="n"/>
-      <c r="M26" s="5" t="n"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N26" s="6" t="n"/>
-      <c r="O26" s="5" t="n"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="5" t="n"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales role at OPLOG</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Andreea Traistaru</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>andreea.traistaru@salespartner.app</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/andreea-tr%c4%83istaru-3347a7139</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="H27" s="5">
         <f>IF(G27="","",TODAY()-G27)</f>
         <v/>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="n"/>
-      <c r="M27" s="5" t="n"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N27" s="6" t="n"/>
-      <c r="O27" s="5" t="n"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="5" t="n"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Drafted</t>
+          <t>Opted Out</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
@@ -1737,10 +1737,12 @@
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1749,7 +1751,7 @@
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative &amp; Account Executive role at Spear Growth</t>
+          <t>Replied to Email 1 with Unsubscribe request (received 2026-08-12 12:40). Permanently excluded.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1853,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Drafted</t>
+          <t>Bounced</t>
         </is>
       </c>
       <c r="G19" s="6" t="n">
@@ -1863,11 +1865,11 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send LinkedIn Connection Request</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
@@ -1883,13 +1885,15 @@
       <c r="N19" s="6" t="n"/>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>46246</v>
+      </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales and Business Development Representative role at Maverick Media</t>
+          <t>Email bounced: address not found (mailer-daemon, 2026-08-12 12:39). Do not re-email; pivoted to LinkedIn.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +115,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -499,7 +500,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -585,6 +586,11 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -653,7 +659,12 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Met at a webinar in July</t>
         </is>
@@ -721,6 +732,11 @@
       <c r="P3" s="6" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
           <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Presales Solutions Consultant role at Tata Consultancy Services</t>
         </is>
       </c>
@@ -770,10 +786,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J4" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -795,6 +809,11 @@
       <c r="P4" s="6" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -844,10 +863,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J5" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -869,6 +886,11 @@
       <c r="P5" s="6" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -918,10 +940,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J6" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -943,6 +963,11 @@
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -992,10 +1017,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J7" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1017,6 +1040,11 @@
       <c r="P7" s="6" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1091,6 +1119,11 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12, bounced same day (Address not found - the address couldn't be found, or is unable to receive mail.). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
         </is>
       </c>
@@ -1140,10 +1173,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J9" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1165,6 +1196,11 @@
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1213,7 +1249,7 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1235,6 +1271,11 @@
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
           <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches</t>
         </is>
       </c>
@@ -1284,10 +1325,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J11" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1309,6 +1348,11 @@
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1358,10 +1402,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J12" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1383,6 +1425,11 @@
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1457,6 +1504,11 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12, bounced same day (550 No Such User (address not found)). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
         </is>
       </c>
@@ -1506,10 +1558,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J14" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1531,6 +1581,11 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1580,10 +1635,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J15" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1605,6 +1658,11 @@
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -1679,6 +1737,11 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12, bounced same day (550 5.7.1 Service unavailable / message blocked). Retroactively logged from Gmail — see run digest. Pivoting to LinkedIn since LinkedIn URL available.</t>
         </is>
       </c>
@@ -1751,6 +1814,11 @@
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
           <t>Replied to Email 1 with Unsubscribe request (received 2026-08-12 12:40). Permanently excluded.</t>
         </is>
       </c>
@@ -1799,7 +1867,7 @@
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1821,6 +1889,11 @@
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
           <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc.</t>
         </is>
       </c>
@@ -1893,6 +1966,11 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
           <t>Email bounced: address not found (mailer-daemon, 2026-08-12 12:39). Do not re-email; pivoted to LinkedIn.</t>
         </is>
       </c>
@@ -1942,10 +2020,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J20" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1967,6 +2043,11 @@
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -2015,7 +2096,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -2037,6 +2118,11 @@
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
           <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
         </is>
       </c>
@@ -2086,10 +2172,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J22" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -2111,6 +2195,11 @@
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
       </c>
@@ -2177,6 +2266,11 @@
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
           <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales Business Development Representative role at Luxiris</t>
         </is>
       </c>
@@ -2225,7 +2319,7 @@
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -2247,6 +2341,11 @@
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
           <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
         </is>
       </c>
@@ -2313,6 +2412,11 @@
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
           <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales and Business Development Representative role at Eversports</t>
         </is>
       </c>
@@ -2379,6 +2483,11 @@
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="5" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
           <t>No email available via Apollo (Basic Trial plan blocks enrichment) — LinkedIn-only outreach. Hook: Saw your Sales role at OPLOG</t>
         </is>
       </c>
@@ -2428,10 +2537,8 @@
           <t>Send Follow-up 1</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="J27" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2452,6 +2559,11 @@
       </c>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
         </is>
@@ -2478,6 +2590,7 @@
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -2500,6 +2613,7 @@
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -2522,6 +2636,7 @@
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -2544,6 +2659,7 @@
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -2566,6 +2682,7 @@
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -2588,6 +2705,7 @@
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="6" t="n"/>
       <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -2610,6 +2728,7 @@
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -2632,6 +2751,7 @@
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="6" t="n"/>
       <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -2654,6 +2774,7 @@
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -2676,6 +2797,7 @@
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="6" t="n"/>
       <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -2698,6 +2820,7 @@
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -2720,6 +2843,7 @@
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="6" t="n"/>
       <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -2742,6 +2866,7 @@
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -2764,6 +2889,7 @@
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="6" t="n"/>
       <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -2786,6 +2912,7 @@
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -2808,6 +2935,7 @@
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="6" t="n"/>
       <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -2830,6 +2958,7 @@
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -2852,6 +2981,7 @@
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="6" t="n"/>
       <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -2874,6 +3004,7 @@
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -2896,6 +3027,7 @@
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="6" t="n"/>
       <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2918,6 +3050,7 @@
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2940,6 +3073,7 @@
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="6" t="n"/>
       <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2962,6 +3096,7 @@
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="6" t="n"/>
       <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2984,6 +3119,7 @@
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="6" t="n"/>
       <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -3006,6 +3142,7 @@
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="6" t="n"/>
       <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -3028,6 +3165,7 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="6" t="n"/>
       <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -3050,6 +3188,7 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="6" t="n"/>
       <c r="Q54" s="5" t="n"/>
+      <c r="R54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -3072,6 +3211,7 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="6" t="n"/>
       <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -3094,6 +3234,7 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="6" t="n"/>
       <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -3116,6 +3257,7 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="6" t="n"/>
       <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -3138,6 +3280,7 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="6" t="n"/>
       <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -3160,6 +3303,7 @@
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="6" t="n"/>
       <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -3182,6 +3326,7 @@
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="6" t="n"/>
       <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -3204,6 +3349,7 @@
       <c r="O61" s="5" t="n"/>
       <c r="P61" s="6" t="n"/>
       <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -3226,6 +3372,7 @@
       <c r="O62" s="5" t="n"/>
       <c r="P62" s="6" t="n"/>
       <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -3248,6 +3395,7 @@
       <c r="O63" s="5" t="n"/>
       <c r="P63" s="6" t="n"/>
       <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -3270,6 +3418,7 @@
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="6" t="n"/>
       <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -3292,6 +3441,7 @@
       <c r="O65" s="5" t="n"/>
       <c r="P65" s="6" t="n"/>
       <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -3314,6 +3464,7 @@
       <c r="O66" s="5" t="n"/>
       <c r="P66" s="6" t="n"/>
       <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -3336,6 +3487,7 @@
       <c r="O67" s="5" t="n"/>
       <c r="P67" s="6" t="n"/>
       <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -3358,6 +3510,7 @@
       <c r="O68" s="5" t="n"/>
       <c r="P68" s="6" t="n"/>
       <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -3380,6 +3533,7 @@
       <c r="O69" s="5" t="n"/>
       <c r="P69" s="6" t="n"/>
       <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -3402,6 +3556,7 @@
       <c r="O70" s="5" t="n"/>
       <c r="P70" s="6" t="n"/>
       <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -3424,6 +3579,7 @@
       <c r="O71" s="5" t="n"/>
       <c r="P71" s="6" t="n"/>
       <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -3446,6 +3602,7 @@
       <c r="O72" s="5" t="n"/>
       <c r="P72" s="6" t="n"/>
       <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -3468,6 +3625,7 @@
       <c r="O73" s="5" t="n"/>
       <c r="P73" s="6" t="n"/>
       <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -3490,6 +3648,7 @@
       <c r="O74" s="5" t="n"/>
       <c r="P74" s="6" t="n"/>
       <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -3512,6 +3671,7 @@
       <c r="O75" s="5" t="n"/>
       <c r="P75" s="6" t="n"/>
       <c r="Q75" s="5" t="n"/>
+      <c r="R75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -3534,6 +3694,7 @@
       <c r="O76" s="5" t="n"/>
       <c r="P76" s="6" t="n"/>
       <c r="Q76" s="5" t="n"/>
+      <c r="R76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -3556,6 +3717,7 @@
       <c r="O77" s="5" t="n"/>
       <c r="P77" s="6" t="n"/>
       <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -3578,6 +3740,7 @@
       <c r="O78" s="5" t="n"/>
       <c r="P78" s="6" t="n"/>
       <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -3600,6 +3763,7 @@
       <c r="O79" s="5" t="n"/>
       <c r="P79" s="6" t="n"/>
       <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -3622,6 +3786,7 @@
       <c r="O80" s="5" t="n"/>
       <c r="P80" s="6" t="n"/>
       <c r="Q80" s="5" t="n"/>
+      <c r="R80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -3644,6 +3809,7 @@
       <c r="O81" s="5" t="n"/>
       <c r="P81" s="6" t="n"/>
       <c r="Q81" s="5" t="n"/>
+      <c r="R81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -3666,6 +3832,7 @@
       <c r="O82" s="5" t="n"/>
       <c r="P82" s="6" t="n"/>
       <c r="Q82" s="5" t="n"/>
+      <c r="R82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -3688,6 +3855,7 @@
       <c r="O83" s="5" t="n"/>
       <c r="P83" s="6" t="n"/>
       <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -3710,6 +3878,7 @@
       <c r="O84" s="5" t="n"/>
       <c r="P84" s="6" t="n"/>
       <c r="Q84" s="5" t="n"/>
+      <c r="R84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -3732,6 +3901,7 @@
       <c r="O85" s="5" t="n"/>
       <c r="P85" s="6" t="n"/>
       <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -3754,6 +3924,7 @@
       <c r="O86" s="5" t="n"/>
       <c r="P86" s="6" t="n"/>
       <c r="Q86" s="5" t="n"/>
+      <c r="R86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -3776,6 +3947,7 @@
       <c r="O87" s="5" t="n"/>
       <c r="P87" s="6" t="n"/>
       <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -3798,6 +3970,7 @@
       <c r="O88" s="5" t="n"/>
       <c r="P88" s="6" t="n"/>
       <c r="Q88" s="5" t="n"/>
+      <c r="R88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -3820,6 +3993,7 @@
       <c r="O89" s="5" t="n"/>
       <c r="P89" s="6" t="n"/>
       <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -3842,6 +4016,7 @@
       <c r="O90" s="5" t="n"/>
       <c r="P90" s="6" t="n"/>
       <c r="Q90" s="5" t="n"/>
+      <c r="R90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -3864,6 +4039,7 @@
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="6" t="n"/>
       <c r="Q91" s="5" t="n"/>
+      <c r="R91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -3886,6 +4062,7 @@
       <c r="O92" s="5" t="n"/>
       <c r="P92" s="6" t="n"/>
       <c r="Q92" s="5" t="n"/>
+      <c r="R92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -3908,6 +4085,7 @@
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="6" t="n"/>
       <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -3930,6 +4108,7 @@
       <c r="O94" s="5" t="n"/>
       <c r="P94" s="6" t="n"/>
       <c r="Q94" s="5" t="n"/>
+      <c r="R94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -3952,6 +4131,7 @@
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="6" t="n"/>
       <c r="Q95" s="5" t="n"/>
+      <c r="R95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -3974,6 +4154,7 @@
       <c r="O96" s="5" t="n"/>
       <c r="P96" s="6" t="n"/>
       <c r="Q96" s="5" t="n"/>
+      <c r="R96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -3996,6 +4177,7 @@
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="6" t="n"/>
       <c r="Q97" s="5" t="n"/>
+      <c r="R97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -4018,6 +4200,7 @@
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="6" t="n"/>
       <c r="Q98" s="5" t="n"/>
+      <c r="R98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -4040,6 +4223,7 @@
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="6" t="n"/>
       <c r="Q99" s="5" t="n"/>
+      <c r="R99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -4062,6 +4246,7 @@
       <c r="O100" s="5" t="n"/>
       <c r="P100" s="6" t="n"/>
       <c r="Q100" s="5" t="n"/>
+      <c r="R100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -4084,6 +4269,7 @@
       <c r="O101" s="5" t="n"/>
       <c r="P101" s="6" t="n"/>
       <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -4106,6 +4292,7 @@
       <c r="O102" s="5" t="n"/>
       <c r="P102" s="6" t="n"/>
       <c r="Q102" s="5" t="n"/>
+      <c r="R102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -4128,6 +4315,7 @@
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="6" t="n"/>
       <c r="Q103" s="5" t="n"/>
+      <c r="R103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -4150,6 +4338,7 @@
       <c r="O104" s="5" t="n"/>
       <c r="P104" s="6" t="n"/>
       <c r="Q104" s="5" t="n"/>
+      <c r="R104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -4172,6 +4361,7 @@
       <c r="O105" s="5" t="n"/>
       <c r="P105" s="6" t="n"/>
       <c r="Q105" s="5" t="n"/>
+      <c r="R105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -4194,6 +4384,7 @@
       <c r="O106" s="5" t="n"/>
       <c r="P106" s="6" t="n"/>
       <c r="Q106" s="5" t="n"/>
+      <c r="R106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -4216,6 +4407,7 @@
       <c r="O107" s="5" t="n"/>
       <c r="P107" s="6" t="n"/>
       <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -4238,6 +4430,7 @@
       <c r="O108" s="5" t="n"/>
       <c r="P108" s="6" t="n"/>
       <c r="Q108" s="5" t="n"/>
+      <c r="R108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -4260,6 +4453,7 @@
       <c r="O109" s="5" t="n"/>
       <c r="P109" s="6" t="n"/>
       <c r="Q109" s="5" t="n"/>
+      <c r="R109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -4282,6 +4476,7 @@
       <c r="O110" s="5" t="n"/>
       <c r="P110" s="6" t="n"/>
       <c r="Q110" s="5" t="n"/>
+      <c r="R110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -4304,6 +4499,7 @@
       <c r="O111" s="5" t="n"/>
       <c r="P111" s="6" t="n"/>
       <c r="Q111" s="5" t="n"/>
+      <c r="R111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -4326,6 +4522,7 @@
       <c r="O112" s="5" t="n"/>
       <c r="P112" s="6" t="n"/>
       <c r="Q112" s="5" t="n"/>
+      <c r="R112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -4348,6 +4545,7 @@
       <c r="O113" s="5" t="n"/>
       <c r="P113" s="6" t="n"/>
       <c r="Q113" s="5" t="n"/>
+      <c r="R113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -4370,6 +4568,7 @@
       <c r="O114" s="5" t="n"/>
       <c r="P114" s="6" t="n"/>
       <c r="Q114" s="5" t="n"/>
+      <c r="R114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -4392,6 +4591,7 @@
       <c r="O115" s="5" t="n"/>
       <c r="P115" s="6" t="n"/>
       <c r="Q115" s="5" t="n"/>
+      <c r="R115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -4414,6 +4614,7 @@
       <c r="O116" s="5" t="n"/>
       <c r="P116" s="6" t="n"/>
       <c r="Q116" s="5" t="n"/>
+      <c r="R116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -4436,6 +4637,7 @@
       <c r="O117" s="5" t="n"/>
       <c r="P117" s="6" t="n"/>
       <c r="Q117" s="5" t="n"/>
+      <c r="R117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -4458,6 +4660,7 @@
       <c r="O118" s="5" t="n"/>
       <c r="P118" s="6" t="n"/>
       <c r="Q118" s="5" t="n"/>
+      <c r="R118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -4480,6 +4683,7 @@
       <c r="O119" s="5" t="n"/>
       <c r="P119" s="6" t="n"/>
       <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -4502,6 +4706,7 @@
       <c r="O120" s="5" t="n"/>
       <c r="P120" s="6" t="n"/>
       <c r="Q120" s="5" t="n"/>
+      <c r="R120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -4524,6 +4729,7 @@
       <c r="O121" s="5" t="n"/>
       <c r="P121" s="6" t="n"/>
       <c r="Q121" s="5" t="n"/>
+      <c r="R121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -4546,6 +4752,7 @@
       <c r="O122" s="5" t="n"/>
       <c r="P122" s="6" t="n"/>
       <c r="Q122" s="5" t="n"/>
+      <c r="R122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -4568,6 +4775,7 @@
       <c r="O123" s="5" t="n"/>
       <c r="P123" s="6" t="n"/>
       <c r="Q123" s="5" t="n"/>
+      <c r="R123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -4590,6 +4798,7 @@
       <c r="O124" s="5" t="n"/>
       <c r="P124" s="6" t="n"/>
       <c r="Q124" s="5" t="n"/>
+      <c r="R124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -4612,6 +4821,7 @@
       <c r="O125" s="5" t="n"/>
       <c r="P125" s="6" t="n"/>
       <c r="Q125" s="5" t="n"/>
+      <c r="R125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -4634,6 +4844,7 @@
       <c r="O126" s="5" t="n"/>
       <c r="P126" s="6" t="n"/>
       <c r="Q126" s="5" t="n"/>
+      <c r="R126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -4656,6 +4867,7 @@
       <c r="O127" s="5" t="n"/>
       <c r="P127" s="6" t="n"/>
       <c r="Q127" s="5" t="n"/>
+      <c r="R127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -4678,6 +4890,7 @@
       <c r="O128" s="5" t="n"/>
       <c r="P128" s="6" t="n"/>
       <c r="Q128" s="5" t="n"/>
+      <c r="R128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -4700,6 +4913,7 @@
       <c r="O129" s="5" t="n"/>
       <c r="P129" s="6" t="n"/>
       <c r="Q129" s="5" t="n"/>
+      <c r="R129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -4722,6 +4936,7 @@
       <c r="O130" s="5" t="n"/>
       <c r="P130" s="6" t="n"/>
       <c r="Q130" s="5" t="n"/>
+      <c r="R130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -4744,6 +4959,7 @@
       <c r="O131" s="5" t="n"/>
       <c r="P131" s="6" t="n"/>
       <c r="Q131" s="5" t="n"/>
+      <c r="R131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -4766,6 +4982,7 @@
       <c r="O132" s="5" t="n"/>
       <c r="P132" s="6" t="n"/>
       <c r="Q132" s="5" t="n"/>
+      <c r="R132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -4788,6 +5005,7 @@
       <c r="O133" s="5" t="n"/>
       <c r="P133" s="6" t="n"/>
       <c r="Q133" s="5" t="n"/>
+      <c r="R133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -4810,6 +5028,7 @@
       <c r="O134" s="5" t="n"/>
       <c r="P134" s="6" t="n"/>
       <c r="Q134" s="5" t="n"/>
+      <c r="R134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -4832,6 +5051,7 @@
       <c r="O135" s="5" t="n"/>
       <c r="P135" s="6" t="n"/>
       <c r="Q135" s="5" t="n"/>
+      <c r="R135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -4854,6 +5074,7 @@
       <c r="O136" s="5" t="n"/>
       <c r="P136" s="6" t="n"/>
       <c r="Q136" s="5" t="n"/>
+      <c r="R136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -4876,6 +5097,7 @@
       <c r="O137" s="5" t="n"/>
       <c r="P137" s="6" t="n"/>
       <c r="Q137" s="5" t="n"/>
+      <c r="R137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -4898,6 +5120,7 @@
       <c r="O138" s="5" t="n"/>
       <c r="P138" s="6" t="n"/>
       <c r="Q138" s="5" t="n"/>
+      <c r="R138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -4920,6 +5143,7 @@
       <c r="O139" s="5" t="n"/>
       <c r="P139" s="6" t="n"/>
       <c r="Q139" s="5" t="n"/>
+      <c r="R139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -4942,6 +5166,7 @@
       <c r="O140" s="5" t="n"/>
       <c r="P140" s="6" t="n"/>
       <c r="Q140" s="5" t="n"/>
+      <c r="R140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -4964,6 +5189,7 @@
       <c r="O141" s="5" t="n"/>
       <c r="P141" s="6" t="n"/>
       <c r="Q141" s="5" t="n"/>
+      <c r="R141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -4986,6 +5212,7 @@
       <c r="O142" s="5" t="n"/>
       <c r="P142" s="6" t="n"/>
       <c r="Q142" s="5" t="n"/>
+      <c r="R142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -5008,6 +5235,7 @@
       <c r="O143" s="5" t="n"/>
       <c r="P143" s="6" t="n"/>
       <c r="Q143" s="5" t="n"/>
+      <c r="R143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -5030,6 +5258,7 @@
       <c r="O144" s="5" t="n"/>
       <c r="P144" s="6" t="n"/>
       <c r="Q144" s="5" t="n"/>
+      <c r="R144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -5052,6 +5281,7 @@
       <c r="O145" s="5" t="n"/>
       <c r="P145" s="6" t="n"/>
       <c r="Q145" s="5" t="n"/>
+      <c r="R145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -5074,6 +5304,7 @@
       <c r="O146" s="5" t="n"/>
       <c r="P146" s="6" t="n"/>
       <c r="Q146" s="5" t="n"/>
+      <c r="R146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -5096,6 +5327,7 @@
       <c r="O147" s="5" t="n"/>
       <c r="P147" s="6" t="n"/>
       <c r="Q147" s="5" t="n"/>
+      <c r="R147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -5118,6 +5350,7 @@
       <c r="O148" s="5" t="n"/>
       <c r="P148" s="6" t="n"/>
       <c r="Q148" s="5" t="n"/>
+      <c r="R148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -5140,6 +5373,7 @@
       <c r="O149" s="5" t="n"/>
       <c r="P149" s="6" t="n"/>
       <c r="Q149" s="5" t="n"/>
+      <c r="R149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -5162,6 +5396,7 @@
       <c r="O150" s="5" t="n"/>
       <c r="P150" s="6" t="n"/>
       <c r="Q150" s="5" t="n"/>
+      <c r="R150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -5184,6 +5419,7 @@
       <c r="O151" s="5" t="n"/>
       <c r="P151" s="6" t="n"/>
       <c r="Q151" s="5" t="n"/>
+      <c r="R151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -5206,6 +5442,7 @@
       <c r="O152" s="5" t="n"/>
       <c r="P152" s="6" t="n"/>
       <c r="Q152" s="5" t="n"/>
+      <c r="R152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -5228,6 +5465,7 @@
       <c r="O153" s="5" t="n"/>
       <c r="P153" s="6" t="n"/>
       <c r="Q153" s="5" t="n"/>
+      <c r="R153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -5250,6 +5488,7 @@
       <c r="O154" s="5" t="n"/>
       <c r="P154" s="6" t="n"/>
       <c r="Q154" s="5" t="n"/>
+      <c r="R154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -5272,6 +5511,7 @@
       <c r="O155" s="5" t="n"/>
       <c r="P155" s="6" t="n"/>
       <c r="Q155" s="5" t="n"/>
+      <c r="R155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -5294,6 +5534,7 @@
       <c r="O156" s="5" t="n"/>
       <c r="P156" s="6" t="n"/>
       <c r="Q156" s="5" t="n"/>
+      <c r="R156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -5316,6 +5557,7 @@
       <c r="O157" s="5" t="n"/>
       <c r="P157" s="6" t="n"/>
       <c r="Q157" s="5" t="n"/>
+      <c r="R157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -5338,6 +5580,7 @@
       <c r="O158" s="5" t="n"/>
       <c r="P158" s="6" t="n"/>
       <c r="Q158" s="5" t="n"/>
+      <c r="R158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -5360,6 +5603,7 @@
       <c r="O159" s="5" t="n"/>
       <c r="P159" s="6" t="n"/>
       <c r="Q159" s="5" t="n"/>
+      <c r="R159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -5382,6 +5626,7 @@
       <c r="O160" s="5" t="n"/>
       <c r="P160" s="6" t="n"/>
       <c r="Q160" s="5" t="n"/>
+      <c r="R160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -5404,6 +5649,7 @@
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="6" t="n"/>
       <c r="Q161" s="5" t="n"/>
+      <c r="R161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -5426,6 +5672,7 @@
       <c r="O162" s="5" t="n"/>
       <c r="P162" s="6" t="n"/>
       <c r="Q162" s="5" t="n"/>
+      <c r="R162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -5448,6 +5695,7 @@
       <c r="O163" s="5" t="n"/>
       <c r="P163" s="6" t="n"/>
       <c r="Q163" s="5" t="n"/>
+      <c r="R163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -5470,6 +5718,7 @@
       <c r="O164" s="5" t="n"/>
       <c r="P164" s="6" t="n"/>
       <c r="Q164" s="5" t="n"/>
+      <c r="R164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -5492,6 +5741,7 @@
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="6" t="n"/>
       <c r="Q165" s="5" t="n"/>
+      <c r="R165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -5514,6 +5764,7 @@
       <c r="O166" s="5" t="n"/>
       <c r="P166" s="6" t="n"/>
       <c r="Q166" s="5" t="n"/>
+      <c r="R166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -5536,6 +5787,7 @@
       <c r="O167" s="5" t="n"/>
       <c r="P167" s="6" t="n"/>
       <c r="Q167" s="5" t="n"/>
+      <c r="R167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -5558,6 +5810,7 @@
       <c r="O168" s="5" t="n"/>
       <c r="P168" s="6" t="n"/>
       <c r="Q168" s="5" t="n"/>
+      <c r="R168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -5580,6 +5833,7 @@
       <c r="O169" s="5" t="n"/>
       <c r="P169" s="6" t="n"/>
       <c r="Q169" s="5" t="n"/>
+      <c r="R169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -5602,6 +5856,7 @@
       <c r="O170" s="5" t="n"/>
       <c r="P170" s="6" t="n"/>
       <c r="Q170" s="5" t="n"/>
+      <c r="R170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -5624,6 +5879,7 @@
       <c r="O171" s="5" t="n"/>
       <c r="P171" s="6" t="n"/>
       <c r="Q171" s="5" t="n"/>
+      <c r="R171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -5646,6 +5902,7 @@
       <c r="O172" s="5" t="n"/>
       <c r="P172" s="6" t="n"/>
       <c r="Q172" s="5" t="n"/>
+      <c r="R172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -5668,6 +5925,7 @@
       <c r="O173" s="5" t="n"/>
       <c r="P173" s="6" t="n"/>
       <c r="Q173" s="5" t="n"/>
+      <c r="R173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -5690,6 +5948,7 @@
       <c r="O174" s="5" t="n"/>
       <c r="P174" s="6" t="n"/>
       <c r="Q174" s="5" t="n"/>
+      <c r="R174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -5712,6 +5971,7 @@
       <c r="O175" s="5" t="n"/>
       <c r="P175" s="6" t="n"/>
       <c r="Q175" s="5" t="n"/>
+      <c r="R175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -5734,6 +5994,7 @@
       <c r="O176" s="5" t="n"/>
       <c r="P176" s="6" t="n"/>
       <c r="Q176" s="5" t="n"/>
+      <c r="R176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -5756,6 +6017,7 @@
       <c r="O177" s="5" t="n"/>
       <c r="P177" s="6" t="n"/>
       <c r="Q177" s="5" t="n"/>
+      <c r="R177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -5778,6 +6040,7 @@
       <c r="O178" s="5" t="n"/>
       <c r="P178" s="6" t="n"/>
       <c r="Q178" s="5" t="n"/>
+      <c r="R178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -5800,6 +6063,7 @@
       <c r="O179" s="5" t="n"/>
       <c r="P179" s="6" t="n"/>
       <c r="Q179" s="5" t="n"/>
+      <c r="R179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -5822,6 +6086,7 @@
       <c r="O180" s="5" t="n"/>
       <c r="P180" s="6" t="n"/>
       <c r="Q180" s="5" t="n"/>
+      <c r="R180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -5844,6 +6109,7 @@
       <c r="O181" s="5" t="n"/>
       <c r="P181" s="6" t="n"/>
       <c r="Q181" s="5" t="n"/>
+      <c r="R181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -5866,6 +6132,7 @@
       <c r="O182" s="5" t="n"/>
       <c r="P182" s="6" t="n"/>
       <c r="Q182" s="5" t="n"/>
+      <c r="R182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -5888,6 +6155,7 @@
       <c r="O183" s="5" t="n"/>
       <c r="P183" s="6" t="n"/>
       <c r="Q183" s="5" t="n"/>
+      <c r="R183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -5910,6 +6178,7 @@
       <c r="O184" s="5" t="n"/>
       <c r="P184" s="6" t="n"/>
       <c r="Q184" s="5" t="n"/>
+      <c r="R184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -5932,6 +6201,7 @@
       <c r="O185" s="5" t="n"/>
       <c r="P185" s="6" t="n"/>
       <c r="Q185" s="5" t="n"/>
+      <c r="R185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -5954,6 +6224,7 @@
       <c r="O186" s="5" t="n"/>
       <c r="P186" s="6" t="n"/>
       <c r="Q186" s="5" t="n"/>
+      <c r="R186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -5976,6 +6247,7 @@
       <c r="O187" s="5" t="n"/>
       <c r="P187" s="6" t="n"/>
       <c r="Q187" s="5" t="n"/>
+      <c r="R187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -5998,6 +6270,7 @@
       <c r="O188" s="5" t="n"/>
       <c r="P188" s="6" t="n"/>
       <c r="Q188" s="5" t="n"/>
+      <c r="R188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -6020,6 +6293,7 @@
       <c r="O189" s="5" t="n"/>
       <c r="P189" s="6" t="n"/>
       <c r="Q189" s="5" t="n"/>
+      <c r="R189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -6042,6 +6316,7 @@
       <c r="O190" s="5" t="n"/>
       <c r="P190" s="6" t="n"/>
       <c r="Q190" s="5" t="n"/>
+      <c r="R190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -6064,6 +6339,7 @@
       <c r="O191" s="5" t="n"/>
       <c r="P191" s="6" t="n"/>
       <c r="Q191" s="5" t="n"/>
+      <c r="R191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -6086,6 +6362,7 @@
       <c r="O192" s="5" t="n"/>
       <c r="P192" s="6" t="n"/>
       <c r="Q192" s="5" t="n"/>
+      <c r="R192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -6108,6 +6385,7 @@
       <c r="O193" s="5" t="n"/>
       <c r="P193" s="6" t="n"/>
       <c r="Q193" s="5" t="n"/>
+      <c r="R193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -6130,6 +6408,7 @@
       <c r="O194" s="5" t="n"/>
       <c r="P194" s="6" t="n"/>
       <c r="Q194" s="5" t="n"/>
+      <c r="R194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -6152,6 +6431,7 @@
       <c r="O195" s="5" t="n"/>
       <c r="P195" s="6" t="n"/>
       <c r="Q195" s="5" t="n"/>
+      <c r="R195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -6174,6 +6454,7 @@
       <c r="O196" s="5" t="n"/>
       <c r="P196" s="6" t="n"/>
       <c r="Q196" s="5" t="n"/>
+      <c r="R196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -6196,6 +6477,7 @@
       <c r="O197" s="5" t="n"/>
       <c r="P197" s="6" t="n"/>
       <c r="Q197" s="5" t="n"/>
+      <c r="R197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -6218,6 +6500,7 @@
       <c r="O198" s="5" t="n"/>
       <c r="P198" s="6" t="n"/>
       <c r="Q198" s="5" t="n"/>
+      <c r="R198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -6240,6 +6523,7 @@
       <c r="O199" s="5" t="n"/>
       <c r="P199" s="6" t="n"/>
       <c r="Q199" s="5" t="n"/>
+      <c r="R199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -6262,11 +6546,12 @@
       <c r="O200" s="5" t="n"/>
       <c r="P200" s="6" t="n"/>
       <c r="Q200" s="5" t="n"/>
+      <c r="R200" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="F2:F201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"New,Email 1 Sent,Follow-up 1 Sent,Follow-up 2 Sent,Replied,LinkedIn Connected,LinkedIn Msg Sent,Booked,Not Interested,Opted Out,Bounced,Cold"</formula1>
+      <formula1>"New,Email 1 Sent,Follow-up 1 Sent,Follow-up 2 Sent,Follow-up 3 Sent,Follow-up 4 Sent,Sequence Complete,Replied,LinkedIn Connected,LinkedIn Msg Sent,Booked,Not Interested,Opted Out,Bounced,Cold"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Send Initial Email,Send Follow-up Email,Send LinkedIn Connection Note,Send LinkedIn Follow-up,Wait,Mark Booked,None"</formula1>
@@ -6280,6 +6565,9 @@
     <dataValidation sqref="O2:O201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation sqref="Q2:Q201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"India,Gulf (UAE),Europe,Other,Unknown"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6291,7 +6579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6317,56 +6605,77 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>2. Stage tracks where each contact is in the sequence: New -&gt; Email 1 Sent -&gt; Follow-up 1 Sent -&gt; Follow-up 2 Sent -&gt; Replied / Booked / Not Interested.</t>
+          <t>2. Stage tracks where each contact is in the sequence: New -&gt; Email 1 Sent -&gt; Follow-up 1 Sent -&gt; Follow-up 2 Sent -&gt; Follow-up 3 Sent -&gt; Follow-up 4 Sent -&gt; Sequence Complete (or Replied / Booked / Not Interested / Opted Out / Bounced at any point).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>3. Next Action + Next Action Date tell you (or the automated weekly run) what to do and when.</t>
+          <t>3. Email cadence runs on a fixed Mon/Wed/Fri schedule, not day-counts: Email 1 (Monday, new leads only) -&gt; Follow-up 1 (Wednesday, same week) -&gt; Follow-up 2 (Friday, same week) -&gt; Follow-up 3 (Wednesday, following week) -&gt; Follow-up 4 (Friday, following week, final). Three separate scheduled routines drive this: Monday pulls fresh leads and sends Email 1 only; Wednesday and Friday only draft due follow-ups for existing contacts, no new leads.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>4. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
+          <t>4. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. LinkedIn messages are drafted for you but NOT sent automatically — LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
+          <t>5. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+          <t>6. Region groups each contact by rough timezone (India / Gulf (UAE) / Europe / Other) so the automation can order its draft digest to roughly match business hours in each region when you do your manual send pass. This does not control actual send time — nothing sends automatically, see note below.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+          <t>7. LinkedIn messages are drafted for you but NOT sent automatically — LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+          <t>8. IMPORTANT: emails are drafted, never auto-sent. The Gmail integration has no send capability, so nothing leaves your account until you personally open Gmail's Drafts folder and hit Send. Exact per-recipient local-time delivery isn't possible for this reason.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>9. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>12. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Drafted</t>
+          <t>Opted Out</t>
         </is>
       </c>
       <c r="G21" s="6" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
@@ -2106,10 +2106,12 @@
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>46248</v>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2123,7 +2125,7 @@
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
+          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software | Unsubscribe request received 2026-08-12 13:16 (missed in prior run, processed 2026-08-14). Permanently excluded.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -623,23 +623,23 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>46251</v>
+      </c>
       <c r="H2" s="4">
         <f>IF(G2="","",TODAY()-G2)</f>
         <v/>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Send Initial Email</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46253</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Met at a webinar in July</t>
+          <t>Met at a webinar in July | Service Interest predates current 4-service taxonomy; treated as closest match (Career Guidance) for Email 1 wording. Overdue row from prior run, swept up by Monday routine 2026-08-17.</t>
         </is>
       </c>
     </row>
@@ -2572,740 +2572,2398 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Sami Moukhalalati</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>sami.moukhalalati@earnix.com</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/moukhalalati</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H28" s="5">
         <f>IF(G28="","",TODAY()-G28)</f>
         <v/>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="n"/>
-      <c r="M28" s="5" t="n"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N28" s="6" t="n"/>
-      <c r="O28" s="5" t="n"/>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Sudheer</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>krishna.sudheer@orolabs.ai</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krishna-sudheer-9234aa124</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H29" s="5">
         <f>IF(G29="","",TODAY()-G29)</f>
         <v/>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L29" s="6" t="n"/>
-      <c r="M29" s="5" t="n"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N29" s="6" t="n"/>
-      <c r="O29" s="5" t="n"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Solutions Consultant role at ORO Labs</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Arun Venkadasubbu</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>arun.venkadasubbu@aspiresys.com</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/arunvenkadasubbu</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H30" s="5">
         <f>IF(G30="","",TODAY()-G30)</f>
         <v/>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="n"/>
-      <c r="M30" s="5" t="n"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N30" s="6" t="n"/>
-      <c r="O30" s="5" t="n"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Louise Scheibner</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>louise.scheibner@columbusglobal.com</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/louisescheibner</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H31" s="5">
         <f>IF(G31="","",TODAY()-G31)</f>
         <v/>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="n"/>
-      <c r="M31" s="5" t="n"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N31" s="6" t="n"/>
-      <c r="O31" s="5" t="n"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Keerthana Subramanian</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>keerthana.s@entomo.co</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/keerthana93</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H32" s="5">
         <f>IF(G32="","",TODAY()-G32)</f>
         <v/>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="n"/>
-      <c r="M32" s="5" t="n"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N32" s="6" t="n"/>
-      <c r="O32" s="5" t="n"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P32" s="6" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>Gulf (UAE)</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales and Solutions Consultant role at entomo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Subhabrata Bhattacharya</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>subhabrata.bhattacharya@tcs.com</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/subhabratabhattacharya</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H33" s="5">
         <f>IF(G33="","",TODAY()-G33)</f>
         <v/>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L33" s="6" t="n"/>
-      <c r="M33" s="5" t="n"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N33" s="6" t="n"/>
-      <c r="O33" s="5" t="n"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Yuxuan Wang</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>yuxuan1.wang@orangecyberdefense.com</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/yuxuan-wang-2429a9177</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H34" s="5">
         <f>IF(G34="","",TODAY()-G34)</f>
         <v/>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L34" s="6" t="n"/>
-      <c r="M34" s="5" t="n"/>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N34" s="6" t="n"/>
-      <c r="O34" s="5" t="n"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P34" s="6" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Antoine Demaille</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>antoine.demaille@haiilo.com</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/antoine-demaille-0b7882241</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H35" s="5">
         <f>IF(G35="","",TODAY()-G35)</f>
         <v/>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L35" s="6" t="n"/>
-      <c r="M35" s="5" t="n"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N35" s="6" t="n"/>
-      <c r="O35" s="5" t="n"/>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="6" t="n"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Buse Sen</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>buse@storyly.io</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/buse-%c5%9fen-aa894417b</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H36" s="5">
         <f>IF(G36="","",TODAY()-G36)</f>
         <v/>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L36" s="6" t="n"/>
-      <c r="M36" s="5" t="n"/>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N36" s="6" t="n"/>
-      <c r="O36" s="5" t="n"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="6" t="n"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Stanislav Minikaev</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>stanislav.minikaev@truelab.games</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/stanislav-minikaev-a92912282</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H37" s="5">
         <f>IF(G37="","",TODAY()-G37)</f>
         <v/>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L37" s="6" t="n"/>
-      <c r="M37" s="5" t="n"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N37" s="6" t="n"/>
-      <c r="O37" s="5" t="n"/>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="6" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Shaun Pearson</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>shaun@insure-smart.co.uk</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shaun-pearson-24294743</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H38" s="5">
         <f>IF(G38="","",TODAY()-G38)</f>
         <v/>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L38" s="6" t="n"/>
-      <c r="M38" s="5" t="n"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N38" s="6" t="n"/>
-      <c r="O38" s="5" t="n"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P38" s="6" t="n"/>
-      <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="n"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="6" t="n"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Taavi Ruudi</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>taavi.ruudi@cybexer.com</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/taaviruudi</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H39" s="5">
         <f>IF(G39="","",TODAY()-G39)</f>
         <v/>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L39" s="6" t="n"/>
-      <c r="M39" s="5" t="n"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N39" s="6" t="n"/>
-      <c r="O39" s="5" t="n"/>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P39" s="6" t="n"/>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="6" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Stefano Carsenzuola</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>stefano.carsenzuola@v-valley.com</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/carse</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H40" s="5">
         <f>IF(G40="","",TODAY()-G40)</f>
         <v/>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="6" t="n"/>
-      <c r="K40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L40" s="6" t="n"/>
-      <c r="M40" s="5" t="n"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N40" s="6" t="n"/>
-      <c r="O40" s="5" t="n"/>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P40" s="6" t="n"/>
-      <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Presales Consultant Manager role at V-Valley</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="6" t="n"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Nastassia Baravik</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>nb@alconost.com</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/nastassia-baravik</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H41" s="5">
         <f>IF(G41="","",TODAY()-G41)</f>
         <v/>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L41" s="6" t="n"/>
-      <c r="M41" s="5" t="n"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N41" s="6" t="n"/>
-      <c r="O41" s="5" t="n"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P41" s="6" t="n"/>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="6" t="n"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Romain Le Gousse</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>romain.le@supermetrics.com</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/romain-le-gousse-2a47b31a1</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H42" s="5">
         <f>IF(G42="","",TODAY()-G42)</f>
         <v/>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L42" s="6" t="n"/>
-      <c r="M42" s="5" t="n"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N42" s="6" t="n"/>
-      <c r="O42" s="5" t="n"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P42" s="6" t="n"/>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive (Sales Executive) role at Supermetrics</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="6" t="n"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Krutika Shukla</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>krutika.shukla@hexadroit.com</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krutika-shukla</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H43" s="5">
         <f>IF(G43="","",TODAY()-G43)</f>
         <v/>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="5" t="n"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L43" s="6" t="n"/>
-      <c r="M43" s="5" t="n"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N43" s="6" t="n"/>
-      <c r="O43" s="5" t="n"/>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P43" s="6" t="n"/>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="6" t="n"/>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Filippo Fazio</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>filippo.fazio@moduline.it</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/filippo-fazio-moduline</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H44" s="5">
         <f>IF(G44="","",TODAY()-G44)</f>
         <v/>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="5" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L44" s="6" t="n"/>
-      <c r="M44" s="5" t="n"/>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N44" s="6" t="n"/>
-      <c r="O44" s="5" t="n"/>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P44" s="6" t="n"/>
-      <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive Sales Manager role at Moduline s.r.l.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="6" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Philipp Stoll Franco</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>philipp.stollfranco@boomi.com</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/philipp-stoll-franco-97a348195</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H45" s="5">
         <f>IF(G45="","",TODAY()-G45)</f>
         <v/>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="5" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L45" s="6" t="n"/>
-      <c r="M45" s="5" t="n"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N45" s="6" t="n"/>
-      <c r="O45" s="5" t="n"/>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P45" s="6" t="n"/>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Commercial Account Manager role at Boomi</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="6" t="n"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Benedict Ortmeier</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>benedict.ortmeier@yoummday.com</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/benedict-ortmeier</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H46" s="5">
         <f>IF(G46="","",TODAY()-G46)</f>
         <v/>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="5" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L46" s="6" t="n"/>
-      <c r="M46" s="5" t="n"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N46" s="6" t="n"/>
-      <c r="O46" s="5" t="n"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P46" s="6" t="n"/>
-      <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Tanishq Saini</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>tanishq.saini@neeyamo.com</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/tanishq-saini24</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H47" s="5">
         <f>IF(G47="","",TODAY()-G47)</f>
         <v/>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="6" t="n"/>
-      <c r="K47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L47" s="6" t="n"/>
-      <c r="M47" s="5" t="n"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N47" s="6" t="n"/>
-      <c r="O47" s="5" t="n"/>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P47" s="6" t="n"/>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n"/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Vinoth Kumar</t>
+        </is>
+      </c>
       <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vinoth-kumar-332a31114</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="5">
         <f>IF(G48="","",TODAY()-G48)</f>
         <v/>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="5" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L48" s="6" t="n"/>
-      <c r="M48" s="5" t="n"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N48" s="6" t="n"/>
-      <c r="O48" s="5" t="n"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P48" s="6" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>No email available via Apollo enrichment — LinkedIn-only outreach. Hook: Saw your Account Executive Sales Manager role at adidas</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="6" t="n"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Magnus Garpedal</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>magnus.garpedal@spandex.se</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/magnus-garpedal-2530a584</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H49" s="5">
         <f>IF(G49="","",TODAY()-G49)</f>
         <v/>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="6" t="n"/>
-      <c r="K49" s="5" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L49" s="6" t="n"/>
-      <c r="M49" s="5" t="n"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N49" s="6" t="n"/>
-      <c r="O49" s="5" t="n"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P49" s="6" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive Sales Manager role at Spandex Sverige AB</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="6" t="n"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Matilda Schwarz</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>matilda.schwarz@kununu.com</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/matilda-schwarz-powerus</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H50" s="5">
         <f>IF(G50="","",TODAY()-G50)</f>
         <v/>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L50" s="6" t="n"/>
-      <c r="M50" s="5" t="n"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N50" s="6" t="n"/>
-      <c r="O50" s="5" t="n"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P50" s="6" t="n"/>
-      <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager | Account Executive role at kununu</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="6" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Dawid Vosloo</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>dawid.vosloo@dyad.net</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dawid-vosloo-695396235</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H51" s="5">
         <f>IF(G51="","",TODAY()-G51)</f>
         <v/>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="5" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L51" s="6" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N51" s="6" t="n"/>
-      <c r="O51" s="5" t="n"/>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P51" s="6" t="n"/>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager role at Dyad</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Steve Herd</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>steven.herd@muckrack.com</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/steven-herd-</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H52" s="5">
         <f>IF(G52="","",TODAY()-G52)</f>
         <v/>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="5" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L52" s="6" t="n"/>
-      <c r="M52" s="5" t="n"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N52" s="6" t="n"/>
-      <c r="O52" s="5" t="n"/>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P52" s="6" t="n"/>
-      <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="5" t="n"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="6" t="n"/>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Niklas Kugler</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>n.kugler@arivo.co</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/niklas-kugler-1b6a65224</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H53" s="5">
         <f>IF(G53="","",TODAY()-G53)</f>
         <v/>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="5" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L53" s="6" t="n"/>
-      <c r="M53" s="5" t="n"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N53" s="6" t="n"/>
-      <c r="O53" s="5" t="n"/>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P53" s="6" t="n"/>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="6" t="n"/>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Arthur Tilleul</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>atilleul@uptoo.fr</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/arthur-tilleul-recrutement-business-uptoo</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H54" s="5">
         <f>IF(G54="","",TODAY()-G54)</f>
         <v/>
       </c>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="5" t="n"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L54" s="6" t="n"/>
-      <c r="M54" s="5" t="n"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N54" s="6" t="n"/>
-      <c r="O54" s="5" t="n"/>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P54" s="6" t="n"/>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="6" t="n"/>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Sin</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>andrew.sin@epiuselabs.com</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/andrew-sin</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H55" s="5">
         <f>IF(G55="","",TODAY()-G55)</f>
         <v/>
       </c>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="5" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L55" s="6" t="n"/>
-      <c r="M55" s="5" t="n"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N55" s="6" t="n"/>
-      <c r="O55" s="5" t="n"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P55" s="6" t="n"/>
-      <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="5" t="n"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="6" t="n"/>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Sam Dinsi</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>sam.dinsi@dyad.net</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/samdinsi</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H56" s="5">
         <f>IF(G56="","",TODAY()-G56)</f>
         <v/>
       </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="5" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L56" s="6" t="n"/>
-      <c r="M56" s="5" t="n"/>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N56" s="6" t="n"/>
-      <c r="O56" s="5" t="n"/>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P56" s="6" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="6" t="n"/>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Jack Pearson</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>jack.pearson@tellimer.com</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jack-pearson-9a7589221</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H57" s="5">
         <f>IF(G57="","",TODAY()-G57)</f>
         <v/>
       </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="6" t="n"/>
-      <c r="K57" s="5" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L57" s="6" t="n"/>
-      <c r="M57" s="5" t="n"/>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N57" s="6" t="n"/>
-      <c r="O57" s="5" t="n"/>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P57" s="6" t="n"/>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="6" t="n"/>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Stephen Lyons</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>stephen.lyons@42gears.com</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/stephen-lyons-b497a1126</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H58" s="5">
         <f>IF(G58="","",TODAY()-G58)</f>
         <v/>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="5" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L58" s="6" t="n"/>
-      <c r="M58" s="5" t="n"/>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N58" s="6" t="n"/>
-      <c r="O58" s="5" t="n"/>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P58" s="6" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Rajeev M</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>rajeev@anakinhq.com</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rajeevem</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="H59" s="5">
         <f>IF(G59="","",TODAY()-G59)</f>
         <v/>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="5" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L59" s="6" t="n"/>
-      <c r="M59" s="5" t="n"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N59" s="6" t="n"/>
-      <c r="O59" s="5" t="n"/>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P59" s="6" t="n"/>
-      <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="5" t="n"/>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8226,7 +8226,7 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"India,Gulf (UAE),Europe,Other,Unknown"</formula1>
+      <formula1>"India,Gulf (UAE),Southeast Asia,United Kingdom,Europe,Other,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8239,7 +8239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8272,70 +8272,77 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>3. Email cadence runs on a fixed Mon/Wed/Fri schedule, not day-counts: Email 1 (Monday, new leads only) -&gt; Follow-up 1 (Wednesday, same week) -&gt; Follow-up 2 (Friday, same week) -&gt; Follow-up 3 (Wednesday, following week) -&gt; Follow-up 4 (Friday, following week, final). Three separate scheduled routines drive this: Monday pulls fresh leads and sends Email 1 only; Wednesday and Friday only draft due follow-ups for existing contacts, no new leads.</t>
+          <t>3. Email cadence runs on a fixed Mon/Wed/Fri schedule, not day-counts: Email 1 (Monday, new leads only) -&gt; Follow-up 1 (Wednesday, same week) -&gt; Follow-up 2 (Friday, same week) -&gt; Follow-up 3 (Wednesday, following week) -&gt; Follow-up 4 (Friday, following week, final). Three separate scheduled routines drive this: Monday pulls fresh leads and sends Email 1 only; Wednesday and Friday send due follow-ups for existing contacts, no new leads.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>4. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
+          <t>4. IMPORTANT: as of 2026-08-17, sending is fully automatic — there is no human review step. Every email a routine generates goes out live (send_message or reply, via the Gmail connector) the moment it's built. This was Abhineet's explicit, informed choice; the exclusion checks (Booked/Opted Out/Bounced) are what keep this safe, not a manual review pass.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
+          <t>5. Lead sourcing (Monday only) targets 6 countries: India, United Arab Emirates (Dubai), Malaysia, Singapore, Thailand, and the United Kingdom. It also rotates through 3 audience segments on a 3-week cycle — Segment A: Presales &amp; Sales Professionals, Segment B: Freshers &amp; Early Career (0-2 yrs, any field), Segment C: SDR/BDR &amp; Delivery people breaking in — one segment per Monday, cycling automatically forever based on the ISO week number.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6. Region groups each contact by rough timezone (India / Gulf (UAE) / Europe / Other) so the automation can order its draft digest to roughly match business hours in each region when you do your manual send pass. This does not control actual send time — nothing sends automatically, see note below.</t>
+          <t>6. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7. LinkedIn messages are drafted for you but NOT sent automatically — LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
+          <t>7. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8. IMPORTANT: emails are drafted, never auto-sent. The Gmail integration has no send capability, so nothing leaves your account until you personally open Gmail's Drafts folder and hit Send. Exact per-recipient local-time delivery isn't possible for this reason.</t>
+          <t>8. Region groups each contact by rough timezone (India / Gulf (UAE) / Southeast Asia / United Kingdom / Other / Unknown; "Europe" is a legacy value from before geography was narrowed, no longer assigned to new rows) — kept for your own visibility into what went out where. It does not control send timing.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+          <t>9. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>10. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+          <t>10. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>11. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+          <t>11. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>12. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>12. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>13. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
@@ -655,10 +655,12 @@
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>46251</v>
+      </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
           <t>India</t>
@@ -666,7 +668,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Met at a webinar in July | Service Interest predates current 4-service taxonomy; treated as closest match (Career Guidance) for Email 1 wording. Overdue row from prior run, swept up by Monday routine 2026-08-17.</t>
+          <t>EXAMPLE ROW, NOT A REAL CONTACT -- accidentally emailed by the automation on 2026-08-17 (jane@example.com bounced, domain not found). Neutralized (Next Action=None) so this never fires again. Root cause fixed in the routine prompt.</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2901,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Bounced</t>
         </is>
       </c>
       <c r="G32" s="6" t="n">
@@ -2911,11 +2913,11 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send LinkedIn Connection Request</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2931,10 +2933,12 @@
       <c r="N32" s="6" t="n"/>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>Gulf (UAE)</t>
@@ -2942,7 +2946,7 @@
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales and Solutions Consultant role at entomo</t>
+          <t>Hook: Saw your Presales and Solutions Consultant role at entomo | Email bounced 2026-08-17: Recipient Unknown (postmaster@entomo.co). Do not re-email; pivoted to LinkedIn.</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Bounced</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
@@ -3661,11 +3665,11 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send LinkedIn Connection Request</t>
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
@@ -3681,10 +3685,12 @@
       <c r="N42" s="6" t="n"/>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -3692,7 +3698,7 @@
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive (Sales Executive) role at Supermetrics</t>
+          <t>Hook: Saw your Account Executive (Sales Executive) role at Supermetrics | Email bounced 2026-08-17: auto-reply "email was not found in our system" (supermetrics.com). Do not re-email; pivoted to LinkedIn.</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3805,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Opted Out</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
@@ -3811,7 +3817,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
@@ -3825,10 +3831,12 @@
       <c r="L44" s="6" t="n"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N44" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3842,7 +3850,7 @@
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at Moduline s.r.l.</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at Moduline s.r.l. | Replied to Email 1 with Unsubscribe request (received 2026-08-17). Permanently excluded.</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4176,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Bounced</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
@@ -4180,11 +4188,11 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send LinkedIn Connection Request</t>
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -4200,10 +4208,12 @@
       <c r="N49" s="6" t="n"/>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P49" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>46251</v>
+      </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -4211,7 +4221,7 @@
       </c>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at Spandex Sverige AB</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at Spandex Sverige AB | Email bounced 2026-08-17: address not found (mailer-daemon). Do not re-email; pivoted to LinkedIn.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="How To Use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Apollo Archive" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8249,7 +8250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8356,6 +8357,9327 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>14. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L500"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Segment/Sub-group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Apollo Source</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date Pulled</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Added to Tracker?</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reason If Not Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Subhadeep Ghosh</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/subhadeep-ghosh-221b007</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Presales Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Anas Aljarrah</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>anas.aljarrah@motorolasolutions.com</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anas-aljarrah</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Annabi</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>hugo@edko.io</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/hugo-annabi</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Bedirhan Akay</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>bedirhan.akay@apollo.eco</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bedirhan-a-614b09105</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Sakshi Maheshwari</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>sakmahes@cisco.com</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sakshimaheshwari19</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mehdi Rabia</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>mehdi.rabia@flatpay.com</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/mehdi-rabia-346189389</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Nael Ayadi</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>nael.ayadi@papernest.com</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/nael-ayadi-sports-business-consulting</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Joel Masats</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>joel.masats@driverevel.com</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/joel-masats-81a035259</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Sales Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>REVEL</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Rohit Saha</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>rohit@ramd.am</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rohittsaha</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Suvendu Sutar</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>suvendu.sutar@wipro.com</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/suvendu-sutar-1b3360178</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Adrien Gagniere</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>adrien@in-leed.com</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/adrien-gagniere-902996263</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Boris-Mihail Todorov</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>boris.todorov@paynetics.digital</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/boris-mihail-todorov</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Souhaila Bouquoyoue</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>souhaila.bouquoyoue@berger-levrault.com</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/souhaila-bouquoyoue</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Paulina Nordgren</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>paulina.nordgren@wolterskluwer.com</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/paulinanordgren</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Tanishq Munjal</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>tanishq@speargrowth.com</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/tanishq-munjal</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Siddharth Srivastava</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>siddharth.srivastava@o9solutions.com</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/siddharth-srivastava-1b32b3202</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Presales Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>o9 Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Katie Collopy</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>katie@maverickmedia.eu</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/katie-collopy-37a0191a1</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Ines Diallo</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ines.diallo@infinit.com</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/in%c3%a8s-diallo-918447172</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Lin Ye</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>lin.ye@siemens.com</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/lin-ye-171224178</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Presales Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Siemens Digital Industries Software</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Samuel Sebban</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>samuel.sebban@pytheascapital.com</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/samuel-sebban-1b1054231</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Come Belmokadem</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/c%c3%b4me-melis-belmokadem-390094344</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Sales Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Luxiris</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Franco Rizzi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>franco.rizzi@siemens.com</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/frizzi</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Presales Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Siemens Digital Industries Software</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Dagmar Ilisson</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dagmar-ilisson-962358212</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Sales and Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Eversports</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Umut Ateș</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/umut-ate%c8%99-172743164</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>OPLOG</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Andreea Traistaru</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>andreea.traistaru@salespartner.app</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/andreea-tr%c4%83istaru-3347a7139</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Sami Moukhalalati</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>sami.moukhalalati@earnix.com</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/moukhalalati</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Presales - Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Earnix</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Sudheer</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>krishna.sudheer@orolabs.ai</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krishna-sudheer-9234aa124</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>ORO Labs</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Arun Venkadasubbu</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>arun.venkadasubbu@aspiresys.com</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/arunvenkadasubbu</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Presales and Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Aspire Systems</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Louise Scheibner</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>louise.scheibner@columbusglobal.com</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/louisescheibner</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Presales &amp; Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Keerthana Subramanian</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>keerthana.s@entomo.co</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/keerthana93</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Presales and Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>entomo</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Gulf (UAE)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Subhabrata Bhattacharya</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>subhabrata.bhattacharya@tcs.com</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/subhabratabhattacharya</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Presales &amp; Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Yuxuan Wang</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>yuxuan1.wang@orangecyberdefense.com</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/yuxuan-wang-2429a9177</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Presales Solutions Consultant, Bid Manager</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Orange Cyberdefense</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Antoine Demaille</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>antoine.demaille@haiilo.com</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/antoine-demaille-0b7882241</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive Sales Manager</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Haiilo</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Buse Sen</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>buse@storyly.io</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/buse-%c5%9fen-aa894417b</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive / Sales Manager</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Storyly</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Stanislav Minikaev</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>stanislav.minikaev@truelab.games</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/stanislav-minikaev-a92912282</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive Sales Manager</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>TRUE LABS</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Shaun Pearson</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>shaun@insure-smart.co.uk</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shaun-pearson-24294743</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Insure Smart Limited</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Taavi Ruudi</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>taavi.ruudi@cybexer.com</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/taaviruudi</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager / Account Executive</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>CybExer Technologies</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Stefano Carsenzuola</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>stefano.carsenzuola@v-valley.com</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/carse</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant Manager</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>V-Valley</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Nastassia Baravik</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>nb@alconost.com</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/nastassia-baravik</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager, Account Executive</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Alconost</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Romain Le Gousse</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>romain.le@supermetrics.com</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/romain-le-gousse-2a47b31a1</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive (Sales Executive)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Supermetrics</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Krutika Shukla</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>krutika.shukla@hexadroit.com</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krutika-shukla</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Senior Presales Consultant &amp; Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Hexadroit Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Filippo Fazio</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>filippo.fazio@moduline.it</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/filippo-fazio-moduline</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive Sales Manager</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Moduline s.r.l.</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Philipp Stoll Franco</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>philipp.stollfranco@boomi.com</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/philipp-stoll-franco-97a348195</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Commercial Account Manager</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Boomi</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Benedict Ortmeier</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>benedict.ortmeier@yoummday.com</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/benedict-ortmeier</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager / Account Executive</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>yoummday</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Tanishq Saini</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>tanishq.saini@neeyamo.com</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/tanishq-saini24</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive / Enterprise Sales</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Neeyamo</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Vinoth Kumar</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vinoth-kumar-332a31114</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive Sales Manager</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>adidas</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Magnus Garpedal</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>magnus.garpedal@spandex.se</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/magnus-garpedal-2530a584</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive Sales Manager</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Spandex Sverige AB</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Matilda Schwarz</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>matilda.schwarz@kununu.com</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/matilda-schwarz-powerus</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager | Account Executive</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>kununu</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Dawid Vosloo</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>dawid.vosloo@dyad.net</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dawid-vosloo-695396235</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Dyad</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Steve Herd</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>steven.herd@muckrack.com</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/steven-herd-</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Account Executive | Sales Manager</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Muck Rack</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Niklas Kugler</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>n.kugler@arivo.co</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/niklas-kugler-1b6a65224</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager - Account Executive</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Arivo</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Arthur Tilleul</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>atilleul@uptoo.fr</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/arthur-tilleul-recrutement-business-uptoo</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager - Account Executive</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>UPTOO</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Sin</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>andrew.sin@epiuselabs.com</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/andrew-sin</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>SAP Partner Sales Manager &amp; Enterprise Account Executive</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>EPI-USE Labs</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Sam Dinsi</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>sam.dinsi@dyad.net</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/samdinsi</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager &amp; Account Executive</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Dyad</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Jack Pearson</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>jack.pearson@tellimer.com</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jack-pearson-9a7589221</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager / Account Executive</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Tellimer</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Stephen Lyons</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>stephen.lyons@42gears.com</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/stephen-lyons-b497a1126</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise Account Manager &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>42Gears</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Rajeev M</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>rajeev@anakinhq.com</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rajeevem</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise Sales Manager / Account Executive</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Anakin (YC S21)</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Segment A</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>apollo_agent_find_prospects</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="6" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="6" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="6" t="n"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="6" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="6" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="6" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="6" t="n"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="6" t="n"/>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="6" t="n"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="6" t="n"/>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="6" t="n"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="6" t="n"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="6" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="6" t="n"/>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="6" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="6" t="n"/>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="6" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="6" t="n"/>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="6" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="6" t="n"/>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="6" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="6" t="n"/>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
+      <c r="J103" s="6" t="n"/>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
+      <c r="J104" s="6" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="6" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5" t="n"/>
+      <c r="I106" s="5" t="n"/>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n"/>
+      <c r="J107" s="6" t="n"/>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n"/>
+      <c r="J108" s="6" t="n"/>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
+      <c r="J109" s="6" t="n"/>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="6" t="n"/>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="5" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="5" t="n"/>
+      <c r="I111" s="5" t="n"/>
+      <c r="J111" s="6" t="n"/>
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="5" t="n"/>
+      <c r="I112" s="5" t="n"/>
+      <c r="J112" s="6" t="n"/>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n"/>
+      <c r="J113" s="6" t="n"/>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="6" t="n"/>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="5" t="n"/>
+      <c r="I115" s="5" t="n"/>
+      <c r="J115" s="6" t="n"/>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="5" t="n"/>
+      <c r="I116" s="5" t="n"/>
+      <c r="J116" s="6" t="n"/>
+      <c r="K116" s="5" t="n"/>
+      <c r="L116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="5" t="n"/>
+      <c r="I117" s="5" t="n"/>
+      <c r="J117" s="6" t="n"/>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n"/>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="5" t="n"/>
+      <c r="I118" s="5" t="n"/>
+      <c r="J118" s="6" t="n"/>
+      <c r="K118" s="5" t="n"/>
+      <c r="L118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="6" t="n"/>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
+      <c r="I120" s="5" t="n"/>
+      <c r="J120" s="6" t="n"/>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="5" t="n"/>
+      <c r="I121" s="5" t="n"/>
+      <c r="J121" s="6" t="n"/>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n"/>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="5" t="n"/>
+      <c r="I122" s="5" t="n"/>
+      <c r="J122" s="6" t="n"/>
+      <c r="K122" s="5" t="n"/>
+      <c r="L122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="5" t="n"/>
+      <c r="I123" s="5" t="n"/>
+      <c r="J123" s="6" t="n"/>
+      <c r="K123" s="5" t="n"/>
+      <c r="L123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="5" t="n"/>
+      <c r="I124" s="5" t="n"/>
+      <c r="J124" s="6" t="n"/>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n"/>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="5" t="n"/>
+      <c r="I125" s="5" t="n"/>
+      <c r="J125" s="6" t="n"/>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n"/>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n"/>
+      <c r="I126" s="5" t="n"/>
+      <c r="J126" s="6" t="n"/>
+      <c r="K126" s="5" t="n"/>
+      <c r="L126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n"/>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="5" t="n"/>
+      <c r="J127" s="6" t="n"/>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="5" t="n"/>
+      <c r="J128" s="6" t="n"/>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="5" t="n"/>
+      <c r="I129" s="5" t="n"/>
+      <c r="J129" s="6" t="n"/>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n"/>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="5" t="n"/>
+      <c r="I130" s="5" t="n"/>
+      <c r="J130" s="6" t="n"/>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
+      <c r="I131" s="5" t="n"/>
+      <c r="J131" s="6" t="n"/>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="5" t="n"/>
+      <c r="I132" s="5" t="n"/>
+      <c r="J132" s="6" t="n"/>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n"/>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="5" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="5" t="n"/>
+      <c r="I133" s="5" t="n"/>
+      <c r="J133" s="6" t="n"/>
+      <c r="K133" s="5" t="n"/>
+      <c r="L133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n"/>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="5" t="n"/>
+      <c r="I134" s="5" t="n"/>
+      <c r="J134" s="6" t="n"/>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
+      <c r="I135" s="5" t="n"/>
+      <c r="J135" s="6" t="n"/>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="5" t="n"/>
+      <c r="I136" s="5" t="n"/>
+      <c r="J136" s="6" t="n"/>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n"/>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="5" t="n"/>
+      <c r="I137" s="5" t="n"/>
+      <c r="J137" s="6" t="n"/>
+      <c r="K137" s="5" t="n"/>
+      <c r="L137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n"/>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="5" t="n"/>
+      <c r="I138" s="5" t="n"/>
+      <c r="J138" s="6" t="n"/>
+      <c r="K138" s="5" t="n"/>
+      <c r="L138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="5" t="n"/>
+      <c r="I139" s="5" t="n"/>
+      <c r="J139" s="6" t="n"/>
+      <c r="K139" s="5" t="n"/>
+      <c r="L139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="5" t="n"/>
+      <c r="I140" s="5" t="n"/>
+      <c r="J140" s="6" t="n"/>
+      <c r="K140" s="5" t="n"/>
+      <c r="L140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n"/>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="5" t="n"/>
+      <c r="I141" s="5" t="n"/>
+      <c r="J141" s="6" t="n"/>
+      <c r="K141" s="5" t="n"/>
+      <c r="L141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n"/>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="5" t="n"/>
+      <c r="I142" s="5" t="n"/>
+      <c r="J142" s="6" t="n"/>
+      <c r="K142" s="5" t="n"/>
+      <c r="L142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="5" t="n"/>
+      <c r="I143" s="5" t="n"/>
+      <c r="J143" s="6" t="n"/>
+      <c r="K143" s="5" t="n"/>
+      <c r="L143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="5" t="n"/>
+      <c r="I144" s="5" t="n"/>
+      <c r="J144" s="6" t="n"/>
+      <c r="K144" s="5" t="n"/>
+      <c r="L144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n"/>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="5" t="n"/>
+      <c r="I145" s="5" t="n"/>
+      <c r="J145" s="6" t="n"/>
+      <c r="K145" s="5" t="n"/>
+      <c r="L145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n"/>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="5" t="n"/>
+      <c r="I146" s="5" t="n"/>
+      <c r="J146" s="6" t="n"/>
+      <c r="K146" s="5" t="n"/>
+      <c r="L146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n"/>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="5" t="n"/>
+      <c r="I147" s="5" t="n"/>
+      <c r="J147" s="6" t="n"/>
+      <c r="K147" s="5" t="n"/>
+      <c r="L147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="5" t="n"/>
+      <c r="I148" s="5" t="n"/>
+      <c r="J148" s="6" t="n"/>
+      <c r="K148" s="5" t="n"/>
+      <c r="L148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n"/>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="5" t="n"/>
+      <c r="I149" s="5" t="n"/>
+      <c r="J149" s="6" t="n"/>
+      <c r="K149" s="5" t="n"/>
+      <c r="L149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="5" t="n"/>
+      <c r="I150" s="5" t="n"/>
+      <c r="J150" s="6" t="n"/>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="5" t="n"/>
+      <c r="I151" s="5" t="n"/>
+      <c r="J151" s="6" t="n"/>
+      <c r="K151" s="5" t="n"/>
+      <c r="L151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n"/>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="5" t="n"/>
+      <c r="I152" s="5" t="n"/>
+      <c r="J152" s="6" t="n"/>
+      <c r="K152" s="5" t="n"/>
+      <c r="L152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n"/>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="5" t="n"/>
+      <c r="I153" s="5" t="n"/>
+      <c r="J153" s="6" t="n"/>
+      <c r="K153" s="5" t="n"/>
+      <c r="L153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n"/>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="n"/>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="5" t="n"/>
+      <c r="I154" s="5" t="n"/>
+      <c r="J154" s="6" t="n"/>
+      <c r="K154" s="5" t="n"/>
+      <c r="L154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="5" t="n"/>
+      <c r="I155" s="5" t="n"/>
+      <c r="J155" s="6" t="n"/>
+      <c r="K155" s="5" t="n"/>
+      <c r="L155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="5" t="n"/>
+      <c r="I156" s="5" t="n"/>
+      <c r="J156" s="6" t="n"/>
+      <c r="K156" s="5" t="n"/>
+      <c r="L156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n"/>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="5" t="n"/>
+      <c r="I157" s="5" t="n"/>
+      <c r="J157" s="6" t="n"/>
+      <c r="K157" s="5" t="n"/>
+      <c r="L157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n"/>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
+      <c r="J158" s="6" t="n"/>
+      <c r="K158" s="5" t="n"/>
+      <c r="L158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="5" t="n"/>
+      <c r="I159" s="5" t="n"/>
+      <c r="J159" s="6" t="n"/>
+      <c r="K159" s="5" t="n"/>
+      <c r="L159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="5" t="n"/>
+      <c r="J160" s="6" t="n"/>
+      <c r="K160" s="5" t="n"/>
+      <c r="L160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="5" t="n"/>
+      <c r="I161" s="5" t="n"/>
+      <c r="J161" s="6" t="n"/>
+      <c r="K161" s="5" t="n"/>
+      <c r="L161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="5" t="n"/>
+      <c r="I162" s="5" t="n"/>
+      <c r="J162" s="6" t="n"/>
+      <c r="K162" s="5" t="n"/>
+      <c r="L162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n"/>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="5" t="n"/>
+      <c r="I163" s="5" t="n"/>
+      <c r="J163" s="6" t="n"/>
+      <c r="K163" s="5" t="n"/>
+      <c r="L163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n"/>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="5" t="n"/>
+      <c r="I164" s="5" t="n"/>
+      <c r="J164" s="6" t="n"/>
+      <c r="K164" s="5" t="n"/>
+      <c r="L164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n"/>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="5" t="n"/>
+      <c r="I165" s="5" t="n"/>
+      <c r="J165" s="6" t="n"/>
+      <c r="K165" s="5" t="n"/>
+      <c r="L165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n"/>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="5" t="n"/>
+      <c r="I166" s="5" t="n"/>
+      <c r="J166" s="6" t="n"/>
+      <c r="K166" s="5" t="n"/>
+      <c r="L166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n"/>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="5" t="n"/>
+      <c r="I167" s="5" t="n"/>
+      <c r="J167" s="6" t="n"/>
+      <c r="K167" s="5" t="n"/>
+      <c r="L167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
+      <c r="I168" s="5" t="n"/>
+      <c r="J168" s="6" t="n"/>
+      <c r="K168" s="5" t="n"/>
+      <c r="L168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n"/>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5" t="n"/>
+      <c r="I169" s="5" t="n"/>
+      <c r="J169" s="6" t="n"/>
+      <c r="K169" s="5" t="n"/>
+      <c r="L169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n"/>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="5" t="n"/>
+      <c r="I170" s="5" t="n"/>
+      <c r="J170" s="6" t="n"/>
+      <c r="K170" s="5" t="n"/>
+      <c r="L170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n"/>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="5" t="n"/>
+      <c r="I171" s="5" t="n"/>
+      <c r="J171" s="6" t="n"/>
+      <c r="K171" s="5" t="n"/>
+      <c r="L171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="5" t="n"/>
+      <c r="I172" s="5" t="n"/>
+      <c r="J172" s="6" t="n"/>
+      <c r="K172" s="5" t="n"/>
+      <c r="L172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n"/>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="5" t="n"/>
+      <c r="I173" s="5" t="n"/>
+      <c r="J173" s="6" t="n"/>
+      <c r="K173" s="5" t="n"/>
+      <c r="L173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5" t="n"/>
+      <c r="I174" s="5" t="n"/>
+      <c r="J174" s="6" t="n"/>
+      <c r="K174" s="5" t="n"/>
+      <c r="L174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n"/>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="5" t="n"/>
+      <c r="I175" s="5" t="n"/>
+      <c r="J175" s="6" t="n"/>
+      <c r="K175" s="5" t="n"/>
+      <c r="L175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n"/>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
+      <c r="I176" s="5" t="n"/>
+      <c r="J176" s="6" t="n"/>
+      <c r="K176" s="5" t="n"/>
+      <c r="L176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n"/>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="5" t="n"/>
+      <c r="I177" s="5" t="n"/>
+      <c r="J177" s="6" t="n"/>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n"/>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="5" t="n"/>
+      <c r="I178" s="5" t="n"/>
+      <c r="J178" s="6" t="n"/>
+      <c r="K178" s="5" t="n"/>
+      <c r="L178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
+      <c r="J179" s="6" t="n"/>
+      <c r="K179" s="5" t="n"/>
+      <c r="L179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="5" t="n"/>
+      <c r="I180" s="5" t="n"/>
+      <c r="J180" s="6" t="n"/>
+      <c r="K180" s="5" t="n"/>
+      <c r="L180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="5" t="n"/>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="5" t="n"/>
+      <c r="I181" s="5" t="n"/>
+      <c r="J181" s="6" t="n"/>
+      <c r="K181" s="5" t="n"/>
+      <c r="L181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n"/>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="5" t="n"/>
+      <c r="I182" s="5" t="n"/>
+      <c r="J182" s="6" t="n"/>
+      <c r="K182" s="5" t="n"/>
+      <c r="L182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n"/>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="5" t="n"/>
+      <c r="I183" s="5" t="n"/>
+      <c r="J183" s="6" t="n"/>
+      <c r="K183" s="5" t="n"/>
+      <c r="L183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="5" t="n"/>
+      <c r="I184" s="5" t="n"/>
+      <c r="J184" s="6" t="n"/>
+      <c r="K184" s="5" t="n"/>
+      <c r="L184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n"/>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="n"/>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="5" t="n"/>
+      <c r="I185" s="5" t="n"/>
+      <c r="J185" s="6" t="n"/>
+      <c r="K185" s="5" t="n"/>
+      <c r="L185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="5" t="n"/>
+      <c r="I186" s="5" t="n"/>
+      <c r="J186" s="6" t="n"/>
+      <c r="K186" s="5" t="n"/>
+      <c r="L186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="5" t="n"/>
+      <c r="I187" s="5" t="n"/>
+      <c r="J187" s="6" t="n"/>
+      <c r="K187" s="5" t="n"/>
+      <c r="L187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="5" t="n"/>
+      <c r="I188" s="5" t="n"/>
+      <c r="J188" s="6" t="n"/>
+      <c r="K188" s="5" t="n"/>
+      <c r="L188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="5" t="n"/>
+      <c r="E189" s="5" t="n"/>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="5" t="n"/>
+      <c r="I189" s="5" t="n"/>
+      <c r="J189" s="6" t="n"/>
+      <c r="K189" s="5" t="n"/>
+      <c r="L189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n"/>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
+      <c r="E190" s="5" t="n"/>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="5" t="n"/>
+      <c r="I190" s="5" t="n"/>
+      <c r="J190" s="6" t="n"/>
+      <c r="K190" s="5" t="n"/>
+      <c r="L190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="5" t="n"/>
+      <c r="I191" s="5" t="n"/>
+      <c r="J191" s="6" t="n"/>
+      <c r="K191" s="5" t="n"/>
+      <c r="L191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n"/>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="5" t="n"/>
+      <c r="I192" s="5" t="n"/>
+      <c r="J192" s="6" t="n"/>
+      <c r="K192" s="5" t="n"/>
+      <c r="L192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="5" t="n"/>
+      <c r="I193" s="5" t="n"/>
+      <c r="J193" s="6" t="n"/>
+      <c r="K193" s="5" t="n"/>
+      <c r="L193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n"/>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="5" t="n"/>
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5" t="n"/>
+      <c r="H194" s="5" t="n"/>
+      <c r="I194" s="5" t="n"/>
+      <c r="J194" s="6" t="n"/>
+      <c r="K194" s="5" t="n"/>
+      <c r="L194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="5" t="n"/>
+      <c r="I195" s="5" t="n"/>
+      <c r="J195" s="6" t="n"/>
+      <c r="K195" s="5" t="n"/>
+      <c r="L195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="5" t="n"/>
+      <c r="I196" s="5" t="n"/>
+      <c r="J196" s="6" t="n"/>
+      <c r="K196" s="5" t="n"/>
+      <c r="L196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
+      <c r="E197" s="5" t="n"/>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="5" t="n"/>
+      <c r="I197" s="5" t="n"/>
+      <c r="J197" s="6" t="n"/>
+      <c r="K197" s="5" t="n"/>
+      <c r="L197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n"/>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="5" t="n"/>
+      <c r="I198" s="5" t="n"/>
+      <c r="J198" s="6" t="n"/>
+      <c r="K198" s="5" t="n"/>
+      <c r="L198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="5" t="n"/>
+      <c r="I199" s="5" t="n"/>
+      <c r="J199" s="6" t="n"/>
+      <c r="K199" s="5" t="n"/>
+      <c r="L199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="5" t="n"/>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="5" t="n"/>
+      <c r="I200" s="5" t="n"/>
+      <c r="J200" s="6" t="n"/>
+      <c r="K200" s="5" t="n"/>
+      <c r="L200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+      <c r="J201" s="6" t="n"/>
+      <c r="K201" s="5" t="n"/>
+      <c r="L201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
+      <c r="J202" s="6" t="n"/>
+      <c r="K202" s="5" t="n"/>
+      <c r="L202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+      <c r="J203" s="6" t="n"/>
+      <c r="K203" s="5" t="n"/>
+      <c r="L203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
+      <c r="J204" s="6" t="n"/>
+      <c r="K204" s="5" t="n"/>
+      <c r="L204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+      <c r="J205" s="6" t="n"/>
+      <c r="K205" s="5" t="n"/>
+      <c r="L205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
+      <c r="J206" s="6" t="n"/>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
+      <c r="J207" s="6" t="n"/>
+      <c r="K207" s="5" t="n"/>
+      <c r="L207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+      <c r="J208" s="6" t="n"/>
+      <c r="K208" s="5" t="n"/>
+      <c r="L208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+      <c r="J209" s="6" t="n"/>
+      <c r="K209" s="5" t="n"/>
+      <c r="L209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="5" t="n"/>
+      <c r="J210" s="6" t="n"/>
+      <c r="K210" s="5" t="n"/>
+      <c r="L210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
+      <c r="J211" s="6" t="n"/>
+      <c r="K211" s="5" t="n"/>
+      <c r="L211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+      <c r="J212" s="6" t="n"/>
+      <c r="K212" s="5" t="n"/>
+      <c r="L212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
+      <c r="J213" s="6" t="n"/>
+      <c r="K213" s="5" t="n"/>
+      <c r="L213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
+      <c r="J214" s="6" t="n"/>
+      <c r="K214" s="5" t="n"/>
+      <c r="L214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="5" t="n"/>
+      <c r="I215" s="5" t="n"/>
+      <c r="J215" s="6" t="n"/>
+      <c r="K215" s="5" t="n"/>
+      <c r="L215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="5" t="n"/>
+      <c r="I216" s="5" t="n"/>
+      <c r="J216" s="6" t="n"/>
+      <c r="K216" s="5" t="n"/>
+      <c r="L216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
+      <c r="I217" s="5" t="n"/>
+      <c r="J217" s="6" t="n"/>
+      <c r="K217" s="5" t="n"/>
+      <c r="L217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="5" t="n"/>
+      <c r="I218" s="5" t="n"/>
+      <c r="J218" s="6" t="n"/>
+      <c r="K218" s="5" t="n"/>
+      <c r="L218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
+      <c r="J219" s="6" t="n"/>
+      <c r="K219" s="5" t="n"/>
+      <c r="L219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="5" t="n"/>
+      <c r="I220" s="5" t="n"/>
+      <c r="J220" s="6" t="n"/>
+      <c r="K220" s="5" t="n"/>
+      <c r="L220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
+      <c r="J221" s="6" t="n"/>
+      <c r="K221" s="5" t="n"/>
+      <c r="L221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
+      <c r="J222" s="6" t="n"/>
+      <c r="K222" s="5" t="n"/>
+      <c r="L222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="5" t="n"/>
+      <c r="I223" s="5" t="n"/>
+      <c r="J223" s="6" t="n"/>
+      <c r="K223" s="5" t="n"/>
+      <c r="L223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="5" t="n"/>
+      <c r="I224" s="5" t="n"/>
+      <c r="J224" s="6" t="n"/>
+      <c r="K224" s="5" t="n"/>
+      <c r="L224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="5" t="n"/>
+      <c r="I225" s="5" t="n"/>
+      <c r="J225" s="6" t="n"/>
+      <c r="K225" s="5" t="n"/>
+      <c r="L225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="6" t="n"/>
+      <c r="K226" s="5" t="n"/>
+      <c r="L226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
+      <c r="J227" s="6" t="n"/>
+      <c r="K227" s="5" t="n"/>
+      <c r="L227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
+      <c r="J228" s="6" t="n"/>
+      <c r="K228" s="5" t="n"/>
+      <c r="L228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="6" t="n"/>
+      <c r="K229" s="5" t="n"/>
+      <c r="L229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="6" t="n"/>
+      <c r="K230" s="5" t="n"/>
+      <c r="L230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="6" t="n"/>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
+      <c r="J232" s="6" t="n"/>
+      <c r="K232" s="5" t="n"/>
+      <c r="L232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="5" t="n"/>
+      <c r="I233" s="5" t="n"/>
+      <c r="J233" s="6" t="n"/>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="5" t="n"/>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="6" t="n"/>
+      <c r="K234" s="5" t="n"/>
+      <c r="L234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="6" t="n"/>
+      <c r="K235" s="5" t="n"/>
+      <c r="L235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="6" t="n"/>
+      <c r="K236" s="5" t="n"/>
+      <c r="L236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
+      <c r="J237" s="6" t="n"/>
+      <c r="K237" s="5" t="n"/>
+      <c r="L237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
+      <c r="J238" s="6" t="n"/>
+      <c r="K238" s="5" t="n"/>
+      <c r="L238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="6" t="n"/>
+      <c r="K239" s="5" t="n"/>
+      <c r="L239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
+      <c r="J240" s="6" t="n"/>
+      <c r="K240" s="5" t="n"/>
+      <c r="L240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
+      <c r="J241" s="6" t="n"/>
+      <c r="K241" s="5" t="n"/>
+      <c r="L241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
+      <c r="J242" s="6" t="n"/>
+      <c r="K242" s="5" t="n"/>
+      <c r="L242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="5" t="n"/>
+      <c r="I243" s="5" t="n"/>
+      <c r="J243" s="6" t="n"/>
+      <c r="K243" s="5" t="n"/>
+      <c r="L243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
+      <c r="J244" s="6" t="n"/>
+      <c r="K244" s="5" t="n"/>
+      <c r="L244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
+      <c r="J245" s="6" t="n"/>
+      <c r="K245" s="5" t="n"/>
+      <c r="L245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
+      <c r="J246" s="6" t="n"/>
+      <c r="K246" s="5" t="n"/>
+      <c r="L246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="5" t="n"/>
+      <c r="I247" s="5" t="n"/>
+      <c r="J247" s="6" t="n"/>
+      <c r="K247" s="5" t="n"/>
+      <c r="L247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="5" t="n"/>
+      <c r="I248" s="5" t="n"/>
+      <c r="J248" s="6" t="n"/>
+      <c r="K248" s="5" t="n"/>
+      <c r="L248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
+      <c r="J249" s="6" t="n"/>
+      <c r="K249" s="5" t="n"/>
+      <c r="L249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+      <c r="J250" s="6" t="n"/>
+      <c r="K250" s="5" t="n"/>
+      <c r="L250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
+      <c r="J251" s="6" t="n"/>
+      <c r="K251" s="5" t="n"/>
+      <c r="L251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="5" t="n"/>
+      <c r="I252" s="5" t="n"/>
+      <c r="J252" s="6" t="n"/>
+      <c r="K252" s="5" t="n"/>
+      <c r="L252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+      <c r="J253" s="6" t="n"/>
+      <c r="K253" s="5" t="n"/>
+      <c r="L253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5" t="n"/>
+      <c r="I254" s="5" t="n"/>
+      <c r="J254" s="6" t="n"/>
+      <c r="K254" s="5" t="n"/>
+      <c r="L254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="5" t="n"/>
+      <c r="I255" s="5" t="n"/>
+      <c r="J255" s="6" t="n"/>
+      <c r="K255" s="5" t="n"/>
+      <c r="L255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
+      <c r="J256" s="6" t="n"/>
+      <c r="K256" s="5" t="n"/>
+      <c r="L256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="5" t="n"/>
+      <c r="I257" s="5" t="n"/>
+      <c r="J257" s="6" t="n"/>
+      <c r="K257" s="5" t="n"/>
+      <c r="L257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+      <c r="J258" s="6" t="n"/>
+      <c r="K258" s="5" t="n"/>
+      <c r="L258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="5" t="n"/>
+      <c r="I259" s="5" t="n"/>
+      <c r="J259" s="6" t="n"/>
+      <c r="K259" s="5" t="n"/>
+      <c r="L259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="6" t="n"/>
+      <c r="K260" s="5" t="n"/>
+      <c r="L260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="5" t="n"/>
+      <c r="I261" s="5" t="n"/>
+      <c r="J261" s="6" t="n"/>
+      <c r="K261" s="5" t="n"/>
+      <c r="L261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
+      <c r="J262" s="6" t="n"/>
+      <c r="K262" s="5" t="n"/>
+      <c r="L262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
+      <c r="J263" s="6" t="n"/>
+      <c r="K263" s="5" t="n"/>
+      <c r="L263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="5" t="n"/>
+      <c r="I264" s="5" t="n"/>
+      <c r="J264" s="6" t="n"/>
+      <c r="K264" s="5" t="n"/>
+      <c r="L264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
+      <c r="J265" s="6" t="n"/>
+      <c r="K265" s="5" t="n"/>
+      <c r="L265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="5" t="n"/>
+      <c r="I266" s="5" t="n"/>
+      <c r="J266" s="6" t="n"/>
+      <c r="K266" s="5" t="n"/>
+      <c r="L266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
+      <c r="J267" s="6" t="n"/>
+      <c r="K267" s="5" t="n"/>
+      <c r="L267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
+      <c r="J268" s="6" t="n"/>
+      <c r="K268" s="5" t="n"/>
+      <c r="L268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
+      <c r="J269" s="6" t="n"/>
+      <c r="K269" s="5" t="n"/>
+      <c r="L269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
+      <c r="J270" s="6" t="n"/>
+      <c r="K270" s="5" t="n"/>
+      <c r="L270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
+      <c r="J271" s="6" t="n"/>
+      <c r="K271" s="5" t="n"/>
+      <c r="L271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="6" t="n"/>
+      <c r="K272" s="5" t="n"/>
+      <c r="L272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
+      <c r="J273" s="6" t="n"/>
+      <c r="K273" s="5" t="n"/>
+      <c r="L273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5" t="n"/>
+      <c r="I274" s="5" t="n"/>
+      <c r="J274" s="6" t="n"/>
+      <c r="K274" s="5" t="n"/>
+      <c r="L274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
+      <c r="J275" s="6" t="n"/>
+      <c r="K275" s="5" t="n"/>
+      <c r="L275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
+      <c r="J276" s="6" t="n"/>
+      <c r="K276" s="5" t="n"/>
+      <c r="L276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
+      <c r="J277" s="6" t="n"/>
+      <c r="K277" s="5" t="n"/>
+      <c r="L277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+      <c r="J278" s="6" t="n"/>
+      <c r="K278" s="5" t="n"/>
+      <c r="L278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="5" t="n"/>
+      <c r="I279" s="5" t="n"/>
+      <c r="J279" s="6" t="n"/>
+      <c r="K279" s="5" t="n"/>
+      <c r="L279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="5" t="n"/>
+      <c r="I280" s="5" t="n"/>
+      <c r="J280" s="6" t="n"/>
+      <c r="K280" s="5" t="n"/>
+      <c r="L280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
+      <c r="J281" s="6" t="n"/>
+      <c r="K281" s="5" t="n"/>
+      <c r="L281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="5" t="n"/>
+      <c r="I282" s="5" t="n"/>
+      <c r="J282" s="6" t="n"/>
+      <c r="K282" s="5" t="n"/>
+      <c r="L282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="5" t="n"/>
+      <c r="I283" s="5" t="n"/>
+      <c r="J283" s="6" t="n"/>
+      <c r="K283" s="5" t="n"/>
+      <c r="L283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
+      <c r="J284" s="6" t="n"/>
+      <c r="K284" s="5" t="n"/>
+      <c r="L284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="5" t="n"/>
+      <c r="I285" s="5" t="n"/>
+      <c r="J285" s="6" t="n"/>
+      <c r="K285" s="5" t="n"/>
+      <c r="L285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="5" t="n"/>
+      <c r="I286" s="5" t="n"/>
+      <c r="J286" s="6" t="n"/>
+      <c r="K286" s="5" t="n"/>
+      <c r="L286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="5" t="n"/>
+      <c r="I287" s="5" t="n"/>
+      <c r="J287" s="6" t="n"/>
+      <c r="K287" s="5" t="n"/>
+      <c r="L287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
+      <c r="J288" s="6" t="n"/>
+      <c r="K288" s="5" t="n"/>
+      <c r="L288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="5" t="n"/>
+      <c r="I289" s="5" t="n"/>
+      <c r="J289" s="6" t="n"/>
+      <c r="K289" s="5" t="n"/>
+      <c r="L289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
+      <c r="J290" s="6" t="n"/>
+      <c r="K290" s="5" t="n"/>
+      <c r="L290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="5" t="n"/>
+      <c r="I291" s="5" t="n"/>
+      <c r="J291" s="6" t="n"/>
+      <c r="K291" s="5" t="n"/>
+      <c r="L291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="5" t="n"/>
+      <c r="I292" s="5" t="n"/>
+      <c r="J292" s="6" t="n"/>
+      <c r="K292" s="5" t="n"/>
+      <c r="L292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="5" t="n"/>
+      <c r="I293" s="5" t="n"/>
+      <c r="J293" s="6" t="n"/>
+      <c r="K293" s="5" t="n"/>
+      <c r="L293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="5" t="n"/>
+      <c r="I294" s="5" t="n"/>
+      <c r="J294" s="6" t="n"/>
+      <c r="K294" s="5" t="n"/>
+      <c r="L294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="5" t="n"/>
+      <c r="I295" s="5" t="n"/>
+      <c r="J295" s="6" t="n"/>
+      <c r="K295" s="5" t="n"/>
+      <c r="L295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="5" t="n"/>
+      <c r="I296" s="5" t="n"/>
+      <c r="J296" s="6" t="n"/>
+      <c r="K296" s="5" t="n"/>
+      <c r="L296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
+      <c r="J297" s="6" t="n"/>
+      <c r="K297" s="5" t="n"/>
+      <c r="L297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
+      <c r="J298" s="6" t="n"/>
+      <c r="K298" s="5" t="n"/>
+      <c r="L298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="5" t="n"/>
+      <c r="I299" s="5" t="n"/>
+      <c r="J299" s="6" t="n"/>
+      <c r="K299" s="5" t="n"/>
+      <c r="L299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
+      <c r="J300" s="6" t="n"/>
+      <c r="K300" s="5" t="n"/>
+      <c r="L300" s="5" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="n"/>
+      <c r="B301" s="5" t="n"/>
+      <c r="C301" s="5" t="n"/>
+      <c r="D301" s="5" t="n"/>
+      <c r="E301" s="5" t="n"/>
+      <c r="F301" s="5" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="5" t="n"/>
+      <c r="I301" s="5" t="n"/>
+      <c r="J301" s="6" t="n"/>
+      <c r="K301" s="5" t="n"/>
+      <c r="L301" s="5" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="n"/>
+      <c r="B302" s="5" t="n"/>
+      <c r="C302" s="5" t="n"/>
+      <c r="D302" s="5" t="n"/>
+      <c r="E302" s="5" t="n"/>
+      <c r="F302" s="5" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="5" t="n"/>
+      <c r="I302" s="5" t="n"/>
+      <c r="J302" s="6" t="n"/>
+      <c r="K302" s="5" t="n"/>
+      <c r="L302" s="5" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="n"/>
+      <c r="B303" s="5" t="n"/>
+      <c r="C303" s="5" t="n"/>
+      <c r="D303" s="5" t="n"/>
+      <c r="E303" s="5" t="n"/>
+      <c r="F303" s="5" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="5" t="n"/>
+      <c r="I303" s="5" t="n"/>
+      <c r="J303" s="6" t="n"/>
+      <c r="K303" s="5" t="n"/>
+      <c r="L303" s="5" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="n"/>
+      <c r="B304" s="5" t="n"/>
+      <c r="C304" s="5" t="n"/>
+      <c r="D304" s="5" t="n"/>
+      <c r="E304" s="5" t="n"/>
+      <c r="F304" s="5" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="5" t="n"/>
+      <c r="I304" s="5" t="n"/>
+      <c r="J304" s="6" t="n"/>
+      <c r="K304" s="5" t="n"/>
+      <c r="L304" s="5" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="n"/>
+      <c r="B305" s="5" t="n"/>
+      <c r="C305" s="5" t="n"/>
+      <c r="D305" s="5" t="n"/>
+      <c r="E305" s="5" t="n"/>
+      <c r="F305" s="5" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="5" t="n"/>
+      <c r="I305" s="5" t="n"/>
+      <c r="J305" s="6" t="n"/>
+      <c r="K305" s="5" t="n"/>
+      <c r="L305" s="5" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="n"/>
+      <c r="B306" s="5" t="n"/>
+      <c r="C306" s="5" t="n"/>
+      <c r="D306" s="5" t="n"/>
+      <c r="E306" s="5" t="n"/>
+      <c r="F306" s="5" t="n"/>
+      <c r="G306" s="5" t="n"/>
+      <c r="H306" s="5" t="n"/>
+      <c r="I306" s="5" t="n"/>
+      <c r="J306" s="6" t="n"/>
+      <c r="K306" s="5" t="n"/>
+      <c r="L306" s="5" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="n"/>
+      <c r="B307" s="5" t="n"/>
+      <c r="C307" s="5" t="n"/>
+      <c r="D307" s="5" t="n"/>
+      <c r="E307" s="5" t="n"/>
+      <c r="F307" s="5" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="5" t="n"/>
+      <c r="I307" s="5" t="n"/>
+      <c r="J307" s="6" t="n"/>
+      <c r="K307" s="5" t="n"/>
+      <c r="L307" s="5" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="n"/>
+      <c r="B308" s="5" t="n"/>
+      <c r="C308" s="5" t="n"/>
+      <c r="D308" s="5" t="n"/>
+      <c r="E308" s="5" t="n"/>
+      <c r="F308" s="5" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="5" t="n"/>
+      <c r="I308" s="5" t="n"/>
+      <c r="J308" s="6" t="n"/>
+      <c r="K308" s="5" t="n"/>
+      <c r="L308" s="5" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="n"/>
+      <c r="B309" s="5" t="n"/>
+      <c r="C309" s="5" t="n"/>
+      <c r="D309" s="5" t="n"/>
+      <c r="E309" s="5" t="n"/>
+      <c r="F309" s="5" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="5" t="n"/>
+      <c r="I309" s="5" t="n"/>
+      <c r="J309" s="6" t="n"/>
+      <c r="K309" s="5" t="n"/>
+      <c r="L309" s="5" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="n"/>
+      <c r="B310" s="5" t="n"/>
+      <c r="C310" s="5" t="n"/>
+      <c r="D310" s="5" t="n"/>
+      <c r="E310" s="5" t="n"/>
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="5" t="n"/>
+      <c r="I310" s="5" t="n"/>
+      <c r="J310" s="6" t="n"/>
+      <c r="K310" s="5" t="n"/>
+      <c r="L310" s="5" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="n"/>
+      <c r="B311" s="5" t="n"/>
+      <c r="C311" s="5" t="n"/>
+      <c r="D311" s="5" t="n"/>
+      <c r="E311" s="5" t="n"/>
+      <c r="F311" s="5" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="5" t="n"/>
+      <c r="I311" s="5" t="n"/>
+      <c r="J311" s="6" t="n"/>
+      <c r="K311" s="5" t="n"/>
+      <c r="L311" s="5" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="n"/>
+      <c r="B312" s="5" t="n"/>
+      <c r="C312" s="5" t="n"/>
+      <c r="D312" s="5" t="n"/>
+      <c r="E312" s="5" t="n"/>
+      <c r="F312" s="5" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="5" t="n"/>
+      <c r="I312" s="5" t="n"/>
+      <c r="J312" s="6" t="n"/>
+      <c r="K312" s="5" t="n"/>
+      <c r="L312" s="5" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="n"/>
+      <c r="B313" s="5" t="n"/>
+      <c r="C313" s="5" t="n"/>
+      <c r="D313" s="5" t="n"/>
+      <c r="E313" s="5" t="n"/>
+      <c r="F313" s="5" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="5" t="n"/>
+      <c r="I313" s="5" t="n"/>
+      <c r="J313" s="6" t="n"/>
+      <c r="K313" s="5" t="n"/>
+      <c r="L313" s="5" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="n"/>
+      <c r="B314" s="5" t="n"/>
+      <c r="C314" s="5" t="n"/>
+      <c r="D314" s="5" t="n"/>
+      <c r="E314" s="5" t="n"/>
+      <c r="F314" s="5" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="5" t="n"/>
+      <c r="I314" s="5" t="n"/>
+      <c r="J314" s="6" t="n"/>
+      <c r="K314" s="5" t="n"/>
+      <c r="L314" s="5" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="n"/>
+      <c r="B315" s="5" t="n"/>
+      <c r="C315" s="5" t="n"/>
+      <c r="D315" s="5" t="n"/>
+      <c r="E315" s="5" t="n"/>
+      <c r="F315" s="5" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="5" t="n"/>
+      <c r="I315" s="5" t="n"/>
+      <c r="J315" s="6" t="n"/>
+      <c r="K315" s="5" t="n"/>
+      <c r="L315" s="5" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="n"/>
+      <c r="B316" s="5" t="n"/>
+      <c r="C316" s="5" t="n"/>
+      <c r="D316" s="5" t="n"/>
+      <c r="E316" s="5" t="n"/>
+      <c r="F316" s="5" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="5" t="n"/>
+      <c r="I316" s="5" t="n"/>
+      <c r="J316" s="6" t="n"/>
+      <c r="K316" s="5" t="n"/>
+      <c r="L316" s="5" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="n"/>
+      <c r="B317" s="5" t="n"/>
+      <c r="C317" s="5" t="n"/>
+      <c r="D317" s="5" t="n"/>
+      <c r="E317" s="5" t="n"/>
+      <c r="F317" s="5" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="5" t="n"/>
+      <c r="I317" s="5" t="n"/>
+      <c r="J317" s="6" t="n"/>
+      <c r="K317" s="5" t="n"/>
+      <c r="L317" s="5" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="n"/>
+      <c r="B318" s="5" t="n"/>
+      <c r="C318" s="5" t="n"/>
+      <c r="D318" s="5" t="n"/>
+      <c r="E318" s="5" t="n"/>
+      <c r="F318" s="5" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="5" t="n"/>
+      <c r="I318" s="5" t="n"/>
+      <c r="J318" s="6" t="n"/>
+      <c r="K318" s="5" t="n"/>
+      <c r="L318" s="5" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="n"/>
+      <c r="B319" s="5" t="n"/>
+      <c r="C319" s="5" t="n"/>
+      <c r="D319" s="5" t="n"/>
+      <c r="E319" s="5" t="n"/>
+      <c r="F319" s="5" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="5" t="n"/>
+      <c r="I319" s="5" t="n"/>
+      <c r="J319" s="6" t="n"/>
+      <c r="K319" s="5" t="n"/>
+      <c r="L319" s="5" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="n"/>
+      <c r="B320" s="5" t="n"/>
+      <c r="C320" s="5" t="n"/>
+      <c r="D320" s="5" t="n"/>
+      <c r="E320" s="5" t="n"/>
+      <c r="F320" s="5" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="5" t="n"/>
+      <c r="I320" s="5" t="n"/>
+      <c r="J320" s="6" t="n"/>
+      <c r="K320" s="5" t="n"/>
+      <c r="L320" s="5" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="n"/>
+      <c r="B321" s="5" t="n"/>
+      <c r="C321" s="5" t="n"/>
+      <c r="D321" s="5" t="n"/>
+      <c r="E321" s="5" t="n"/>
+      <c r="F321" s="5" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="5" t="n"/>
+      <c r="I321" s="5" t="n"/>
+      <c r="J321" s="6" t="n"/>
+      <c r="K321" s="5" t="n"/>
+      <c r="L321" s="5" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="n"/>
+      <c r="B322" s="5" t="n"/>
+      <c r="C322" s="5" t="n"/>
+      <c r="D322" s="5" t="n"/>
+      <c r="E322" s="5" t="n"/>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="5" t="n"/>
+      <c r="I322" s="5" t="n"/>
+      <c r="J322" s="6" t="n"/>
+      <c r="K322" s="5" t="n"/>
+      <c r="L322" s="5" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="n"/>
+      <c r="B323" s="5" t="n"/>
+      <c r="C323" s="5" t="n"/>
+      <c r="D323" s="5" t="n"/>
+      <c r="E323" s="5" t="n"/>
+      <c r="F323" s="5" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="5" t="n"/>
+      <c r="I323" s="5" t="n"/>
+      <c r="J323" s="6" t="n"/>
+      <c r="K323" s="5" t="n"/>
+      <c r="L323" s="5" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="n"/>
+      <c r="B324" s="5" t="n"/>
+      <c r="C324" s="5" t="n"/>
+      <c r="D324" s="5" t="n"/>
+      <c r="E324" s="5" t="n"/>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="5" t="n"/>
+      <c r="I324" s="5" t="n"/>
+      <c r="J324" s="6" t="n"/>
+      <c r="K324" s="5" t="n"/>
+      <c r="L324" s="5" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="n"/>
+      <c r="B325" s="5" t="n"/>
+      <c r="C325" s="5" t="n"/>
+      <c r="D325" s="5" t="n"/>
+      <c r="E325" s="5" t="n"/>
+      <c r="F325" s="5" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="5" t="n"/>
+      <c r="I325" s="5" t="n"/>
+      <c r="J325" s="6" t="n"/>
+      <c r="K325" s="5" t="n"/>
+      <c r="L325" s="5" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="n"/>
+      <c r="B326" s="5" t="n"/>
+      <c r="C326" s="5" t="n"/>
+      <c r="D326" s="5" t="n"/>
+      <c r="E326" s="5" t="n"/>
+      <c r="F326" s="5" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="5" t="n"/>
+      <c r="I326" s="5" t="n"/>
+      <c r="J326" s="6" t="n"/>
+      <c r="K326" s="5" t="n"/>
+      <c r="L326" s="5" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="n"/>
+      <c r="B327" s="5" t="n"/>
+      <c r="C327" s="5" t="n"/>
+      <c r="D327" s="5" t="n"/>
+      <c r="E327" s="5" t="n"/>
+      <c r="F327" s="5" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="5" t="n"/>
+      <c r="I327" s="5" t="n"/>
+      <c r="J327" s="6" t="n"/>
+      <c r="K327" s="5" t="n"/>
+      <c r="L327" s="5" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="n"/>
+      <c r="B328" s="5" t="n"/>
+      <c r="C328" s="5" t="n"/>
+      <c r="D328" s="5" t="n"/>
+      <c r="E328" s="5" t="n"/>
+      <c r="F328" s="5" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="5" t="n"/>
+      <c r="I328" s="5" t="n"/>
+      <c r="J328" s="6" t="n"/>
+      <c r="K328" s="5" t="n"/>
+      <c r="L328" s="5" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="n"/>
+      <c r="B329" s="5" t="n"/>
+      <c r="C329" s="5" t="n"/>
+      <c r="D329" s="5" t="n"/>
+      <c r="E329" s="5" t="n"/>
+      <c r="F329" s="5" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="5" t="n"/>
+      <c r="I329" s="5" t="n"/>
+      <c r="J329" s="6" t="n"/>
+      <c r="K329" s="5" t="n"/>
+      <c r="L329" s="5" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="n"/>
+      <c r="B330" s="5" t="n"/>
+      <c r="C330" s="5" t="n"/>
+      <c r="D330" s="5" t="n"/>
+      <c r="E330" s="5" t="n"/>
+      <c r="F330" s="5" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="5" t="n"/>
+      <c r="I330" s="5" t="n"/>
+      <c r="J330" s="6" t="n"/>
+      <c r="K330" s="5" t="n"/>
+      <c r="L330" s="5" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="n"/>
+      <c r="B331" s="5" t="n"/>
+      <c r="C331" s="5" t="n"/>
+      <c r="D331" s="5" t="n"/>
+      <c r="E331" s="5" t="n"/>
+      <c r="F331" s="5" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="5" t="n"/>
+      <c r="I331" s="5" t="n"/>
+      <c r="J331" s="6" t="n"/>
+      <c r="K331" s="5" t="n"/>
+      <c r="L331" s="5" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="n"/>
+      <c r="B332" s="5" t="n"/>
+      <c r="C332" s="5" t="n"/>
+      <c r="D332" s="5" t="n"/>
+      <c r="E332" s="5" t="n"/>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="5" t="n"/>
+      <c r="I332" s="5" t="n"/>
+      <c r="J332" s="6" t="n"/>
+      <c r="K332" s="5" t="n"/>
+      <c r="L332" s="5" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="n"/>
+      <c r="B333" s="5" t="n"/>
+      <c r="C333" s="5" t="n"/>
+      <c r="D333" s="5" t="n"/>
+      <c r="E333" s="5" t="n"/>
+      <c r="F333" s="5" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="5" t="n"/>
+      <c r="I333" s="5" t="n"/>
+      <c r="J333" s="6" t="n"/>
+      <c r="K333" s="5" t="n"/>
+      <c r="L333" s="5" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="n"/>
+      <c r="B334" s="5" t="n"/>
+      <c r="C334" s="5" t="n"/>
+      <c r="D334" s="5" t="n"/>
+      <c r="E334" s="5" t="n"/>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="5" t="n"/>
+      <c r="I334" s="5" t="n"/>
+      <c r="J334" s="6" t="n"/>
+      <c r="K334" s="5" t="n"/>
+      <c r="L334" s="5" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="n"/>
+      <c r="B335" s="5" t="n"/>
+      <c r="C335" s="5" t="n"/>
+      <c r="D335" s="5" t="n"/>
+      <c r="E335" s="5" t="n"/>
+      <c r="F335" s="5" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="5" t="n"/>
+      <c r="I335" s="5" t="n"/>
+      <c r="J335" s="6" t="n"/>
+      <c r="K335" s="5" t="n"/>
+      <c r="L335" s="5" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="n"/>
+      <c r="B336" s="5" t="n"/>
+      <c r="C336" s="5" t="n"/>
+      <c r="D336" s="5" t="n"/>
+      <c r="E336" s="5" t="n"/>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="5" t="n"/>
+      <c r="I336" s="5" t="n"/>
+      <c r="J336" s="6" t="n"/>
+      <c r="K336" s="5" t="n"/>
+      <c r="L336" s="5" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="n"/>
+      <c r="B337" s="5" t="n"/>
+      <c r="C337" s="5" t="n"/>
+      <c r="D337" s="5" t="n"/>
+      <c r="E337" s="5" t="n"/>
+      <c r="F337" s="5" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="5" t="n"/>
+      <c r="I337" s="5" t="n"/>
+      <c r="J337" s="6" t="n"/>
+      <c r="K337" s="5" t="n"/>
+      <c r="L337" s="5" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="n"/>
+      <c r="B338" s="5" t="n"/>
+      <c r="C338" s="5" t="n"/>
+      <c r="D338" s="5" t="n"/>
+      <c r="E338" s="5" t="n"/>
+      <c r="F338" s="5" t="n"/>
+      <c r="G338" s="5" t="n"/>
+      <c r="H338" s="5" t="n"/>
+      <c r="I338" s="5" t="n"/>
+      <c r="J338" s="6" t="n"/>
+      <c r="K338" s="5" t="n"/>
+      <c r="L338" s="5" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="n"/>
+      <c r="B339" s="5" t="n"/>
+      <c r="C339" s="5" t="n"/>
+      <c r="D339" s="5" t="n"/>
+      <c r="E339" s="5" t="n"/>
+      <c r="F339" s="5" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="5" t="n"/>
+      <c r="I339" s="5" t="n"/>
+      <c r="J339" s="6" t="n"/>
+      <c r="K339" s="5" t="n"/>
+      <c r="L339" s="5" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="n"/>
+      <c r="B340" s="5" t="n"/>
+      <c r="C340" s="5" t="n"/>
+      <c r="D340" s="5" t="n"/>
+      <c r="E340" s="5" t="n"/>
+      <c r="F340" s="5" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="5" t="n"/>
+      <c r="I340" s="5" t="n"/>
+      <c r="J340" s="6" t="n"/>
+      <c r="K340" s="5" t="n"/>
+      <c r="L340" s="5" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="n"/>
+      <c r="B341" s="5" t="n"/>
+      <c r="C341" s="5" t="n"/>
+      <c r="D341" s="5" t="n"/>
+      <c r="E341" s="5" t="n"/>
+      <c r="F341" s="5" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="5" t="n"/>
+      <c r="I341" s="5" t="n"/>
+      <c r="J341" s="6" t="n"/>
+      <c r="K341" s="5" t="n"/>
+      <c r="L341" s="5" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="n"/>
+      <c r="B342" s="5" t="n"/>
+      <c r="C342" s="5" t="n"/>
+      <c r="D342" s="5" t="n"/>
+      <c r="E342" s="5" t="n"/>
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="5" t="n"/>
+      <c r="H342" s="5" t="n"/>
+      <c r="I342" s="5" t="n"/>
+      <c r="J342" s="6" t="n"/>
+      <c r="K342" s="5" t="n"/>
+      <c r="L342" s="5" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="n"/>
+      <c r="B343" s="5" t="n"/>
+      <c r="C343" s="5" t="n"/>
+      <c r="D343" s="5" t="n"/>
+      <c r="E343" s="5" t="n"/>
+      <c r="F343" s="5" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="5" t="n"/>
+      <c r="I343" s="5" t="n"/>
+      <c r="J343" s="6" t="n"/>
+      <c r="K343" s="5" t="n"/>
+      <c r="L343" s="5" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="n"/>
+      <c r="B344" s="5" t="n"/>
+      <c r="C344" s="5" t="n"/>
+      <c r="D344" s="5" t="n"/>
+      <c r="E344" s="5" t="n"/>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="5" t="n"/>
+      <c r="I344" s="5" t="n"/>
+      <c r="J344" s="6" t="n"/>
+      <c r="K344" s="5" t="n"/>
+      <c r="L344" s="5" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="n"/>
+      <c r="B345" s="5" t="n"/>
+      <c r="C345" s="5" t="n"/>
+      <c r="D345" s="5" t="n"/>
+      <c r="E345" s="5" t="n"/>
+      <c r="F345" s="5" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="5" t="n"/>
+      <c r="I345" s="5" t="n"/>
+      <c r="J345" s="6" t="n"/>
+      <c r="K345" s="5" t="n"/>
+      <c r="L345" s="5" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="n"/>
+      <c r="B346" s="5" t="n"/>
+      <c r="C346" s="5" t="n"/>
+      <c r="D346" s="5" t="n"/>
+      <c r="E346" s="5" t="n"/>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="5" t="n"/>
+      <c r="I346" s="5" t="n"/>
+      <c r="J346" s="6" t="n"/>
+      <c r="K346" s="5" t="n"/>
+      <c r="L346" s="5" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="n"/>
+      <c r="B347" s="5" t="n"/>
+      <c r="C347" s="5" t="n"/>
+      <c r="D347" s="5" t="n"/>
+      <c r="E347" s="5" t="n"/>
+      <c r="F347" s="5" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="5" t="n"/>
+      <c r="I347" s="5" t="n"/>
+      <c r="J347" s="6" t="n"/>
+      <c r="K347" s="5" t="n"/>
+      <c r="L347" s="5" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="n"/>
+      <c r="B348" s="5" t="n"/>
+      <c r="C348" s="5" t="n"/>
+      <c r="D348" s="5" t="n"/>
+      <c r="E348" s="5" t="n"/>
+      <c r="F348" s="5" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="5" t="n"/>
+      <c r="I348" s="5" t="n"/>
+      <c r="J348" s="6" t="n"/>
+      <c r="K348" s="5" t="n"/>
+      <c r="L348" s="5" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="n"/>
+      <c r="B349" s="5" t="n"/>
+      <c r="C349" s="5" t="n"/>
+      <c r="D349" s="5" t="n"/>
+      <c r="E349" s="5" t="n"/>
+      <c r="F349" s="5" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="5" t="n"/>
+      <c r="I349" s="5" t="n"/>
+      <c r="J349" s="6" t="n"/>
+      <c r="K349" s="5" t="n"/>
+      <c r="L349" s="5" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="n"/>
+      <c r="B350" s="5" t="n"/>
+      <c r="C350" s="5" t="n"/>
+      <c r="D350" s="5" t="n"/>
+      <c r="E350" s="5" t="n"/>
+      <c r="F350" s="5" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="5" t="n"/>
+      <c r="I350" s="5" t="n"/>
+      <c r="J350" s="6" t="n"/>
+      <c r="K350" s="5" t="n"/>
+      <c r="L350" s="5" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="n"/>
+      <c r="B351" s="5" t="n"/>
+      <c r="C351" s="5" t="n"/>
+      <c r="D351" s="5" t="n"/>
+      <c r="E351" s="5" t="n"/>
+      <c r="F351" s="5" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="5" t="n"/>
+      <c r="I351" s="5" t="n"/>
+      <c r="J351" s="6" t="n"/>
+      <c r="K351" s="5" t="n"/>
+      <c r="L351" s="5" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="n"/>
+      <c r="B352" s="5" t="n"/>
+      <c r="C352" s="5" t="n"/>
+      <c r="D352" s="5" t="n"/>
+      <c r="E352" s="5" t="n"/>
+      <c r="F352" s="5" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="5" t="n"/>
+      <c r="I352" s="5" t="n"/>
+      <c r="J352" s="6" t="n"/>
+      <c r="K352" s="5" t="n"/>
+      <c r="L352" s="5" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="n"/>
+      <c r="B353" s="5" t="n"/>
+      <c r="C353" s="5" t="n"/>
+      <c r="D353" s="5" t="n"/>
+      <c r="E353" s="5" t="n"/>
+      <c r="F353" s="5" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="5" t="n"/>
+      <c r="I353" s="5" t="n"/>
+      <c r="J353" s="6" t="n"/>
+      <c r="K353" s="5" t="n"/>
+      <c r="L353" s="5" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="n"/>
+      <c r="B354" s="5" t="n"/>
+      <c r="C354" s="5" t="n"/>
+      <c r="D354" s="5" t="n"/>
+      <c r="E354" s="5" t="n"/>
+      <c r="F354" s="5" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="5" t="n"/>
+      <c r="I354" s="5" t="n"/>
+      <c r="J354" s="6" t="n"/>
+      <c r="K354" s="5" t="n"/>
+      <c r="L354" s="5" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="n"/>
+      <c r="B355" s="5" t="n"/>
+      <c r="C355" s="5" t="n"/>
+      <c r="D355" s="5" t="n"/>
+      <c r="E355" s="5" t="n"/>
+      <c r="F355" s="5" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="5" t="n"/>
+      <c r="I355" s="5" t="n"/>
+      <c r="J355" s="6" t="n"/>
+      <c r="K355" s="5" t="n"/>
+      <c r="L355" s="5" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="n"/>
+      <c r="B356" s="5" t="n"/>
+      <c r="C356" s="5" t="n"/>
+      <c r="D356" s="5" t="n"/>
+      <c r="E356" s="5" t="n"/>
+      <c r="F356" s="5" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="5" t="n"/>
+      <c r="I356" s="5" t="n"/>
+      <c r="J356" s="6" t="n"/>
+      <c r="K356" s="5" t="n"/>
+      <c r="L356" s="5" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="n"/>
+      <c r="B357" s="5" t="n"/>
+      <c r="C357" s="5" t="n"/>
+      <c r="D357" s="5" t="n"/>
+      <c r="E357" s="5" t="n"/>
+      <c r="F357" s="5" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="5" t="n"/>
+      <c r="I357" s="5" t="n"/>
+      <c r="J357" s="6" t="n"/>
+      <c r="K357" s="5" t="n"/>
+      <c r="L357" s="5" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="5" t="n"/>
+      <c r="B358" s="5" t="n"/>
+      <c r="C358" s="5" t="n"/>
+      <c r="D358" s="5" t="n"/>
+      <c r="E358" s="5" t="n"/>
+      <c r="F358" s="5" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="5" t="n"/>
+      <c r="I358" s="5" t="n"/>
+      <c r="J358" s="6" t="n"/>
+      <c r="K358" s="5" t="n"/>
+      <c r="L358" s="5" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="n"/>
+      <c r="B359" s="5" t="n"/>
+      <c r="C359" s="5" t="n"/>
+      <c r="D359" s="5" t="n"/>
+      <c r="E359" s="5" t="n"/>
+      <c r="F359" s="5" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="5" t="n"/>
+      <c r="I359" s="5" t="n"/>
+      <c r="J359" s="6" t="n"/>
+      <c r="K359" s="5" t="n"/>
+      <c r="L359" s="5" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="n"/>
+      <c r="B360" s="5" t="n"/>
+      <c r="C360" s="5" t="n"/>
+      <c r="D360" s="5" t="n"/>
+      <c r="E360" s="5" t="n"/>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="5" t="n"/>
+      <c r="I360" s="5" t="n"/>
+      <c r="J360" s="6" t="n"/>
+      <c r="K360" s="5" t="n"/>
+      <c r="L360" s="5" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="n"/>
+      <c r="B361" s="5" t="n"/>
+      <c r="C361" s="5" t="n"/>
+      <c r="D361" s="5" t="n"/>
+      <c r="E361" s="5" t="n"/>
+      <c r="F361" s="5" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="5" t="n"/>
+      <c r="I361" s="5" t="n"/>
+      <c r="J361" s="6" t="n"/>
+      <c r="K361" s="5" t="n"/>
+      <c r="L361" s="5" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="n"/>
+      <c r="B362" s="5" t="n"/>
+      <c r="C362" s="5" t="n"/>
+      <c r="D362" s="5" t="n"/>
+      <c r="E362" s="5" t="n"/>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="5" t="n"/>
+      <c r="I362" s="5" t="n"/>
+      <c r="J362" s="6" t="n"/>
+      <c r="K362" s="5" t="n"/>
+      <c r="L362" s="5" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="n"/>
+      <c r="B363" s="5" t="n"/>
+      <c r="C363" s="5" t="n"/>
+      <c r="D363" s="5" t="n"/>
+      <c r="E363" s="5" t="n"/>
+      <c r="F363" s="5" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="5" t="n"/>
+      <c r="I363" s="5" t="n"/>
+      <c r="J363" s="6" t="n"/>
+      <c r="K363" s="5" t="n"/>
+      <c r="L363" s="5" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="n"/>
+      <c r="B364" s="5" t="n"/>
+      <c r="C364" s="5" t="n"/>
+      <c r="D364" s="5" t="n"/>
+      <c r="E364" s="5" t="n"/>
+      <c r="F364" s="5" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="5" t="n"/>
+      <c r="I364" s="5" t="n"/>
+      <c r="J364" s="6" t="n"/>
+      <c r="K364" s="5" t="n"/>
+      <c r="L364" s="5" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="n"/>
+      <c r="B365" s="5" t="n"/>
+      <c r="C365" s="5" t="n"/>
+      <c r="D365" s="5" t="n"/>
+      <c r="E365" s="5" t="n"/>
+      <c r="F365" s="5" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="5" t="n"/>
+      <c r="I365" s="5" t="n"/>
+      <c r="J365" s="6" t="n"/>
+      <c r="K365" s="5" t="n"/>
+      <c r="L365" s="5" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="n"/>
+      <c r="B366" s="5" t="n"/>
+      <c r="C366" s="5" t="n"/>
+      <c r="D366" s="5" t="n"/>
+      <c r="E366" s="5" t="n"/>
+      <c r="F366" s="5" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="5" t="n"/>
+      <c r="I366" s="5" t="n"/>
+      <c r="J366" s="6" t="n"/>
+      <c r="K366" s="5" t="n"/>
+      <c r="L366" s="5" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="n"/>
+      <c r="B367" s="5" t="n"/>
+      <c r="C367" s="5" t="n"/>
+      <c r="D367" s="5" t="n"/>
+      <c r="E367" s="5" t="n"/>
+      <c r="F367" s="5" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="5" t="n"/>
+      <c r="I367" s="5" t="n"/>
+      <c r="J367" s="6" t="n"/>
+      <c r="K367" s="5" t="n"/>
+      <c r="L367" s="5" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="n"/>
+      <c r="B368" s="5" t="n"/>
+      <c r="C368" s="5" t="n"/>
+      <c r="D368" s="5" t="n"/>
+      <c r="E368" s="5" t="n"/>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="5" t="n"/>
+      <c r="I368" s="5" t="n"/>
+      <c r="J368" s="6" t="n"/>
+      <c r="K368" s="5" t="n"/>
+      <c r="L368" s="5" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="n"/>
+      <c r="B369" s="5" t="n"/>
+      <c r="C369" s="5" t="n"/>
+      <c r="D369" s="5" t="n"/>
+      <c r="E369" s="5" t="n"/>
+      <c r="F369" s="5" t="n"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="5" t="n"/>
+      <c r="I369" s="5" t="n"/>
+      <c r="J369" s="6" t="n"/>
+      <c r="K369" s="5" t="n"/>
+      <c r="L369" s="5" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="n"/>
+      <c r="B370" s="5" t="n"/>
+      <c r="C370" s="5" t="n"/>
+      <c r="D370" s="5" t="n"/>
+      <c r="E370" s="5" t="n"/>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="5" t="n"/>
+      <c r="I370" s="5" t="n"/>
+      <c r="J370" s="6" t="n"/>
+      <c r="K370" s="5" t="n"/>
+      <c r="L370" s="5" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="n"/>
+      <c r="B371" s="5" t="n"/>
+      <c r="C371" s="5" t="n"/>
+      <c r="D371" s="5" t="n"/>
+      <c r="E371" s="5" t="n"/>
+      <c r="F371" s="5" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="5" t="n"/>
+      <c r="I371" s="5" t="n"/>
+      <c r="J371" s="6" t="n"/>
+      <c r="K371" s="5" t="n"/>
+      <c r="L371" s="5" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="n"/>
+      <c r="B372" s="5" t="n"/>
+      <c r="C372" s="5" t="n"/>
+      <c r="D372" s="5" t="n"/>
+      <c r="E372" s="5" t="n"/>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="5" t="n"/>
+      <c r="I372" s="5" t="n"/>
+      <c r="J372" s="6" t="n"/>
+      <c r="K372" s="5" t="n"/>
+      <c r="L372" s="5" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="n"/>
+      <c r="B373" s="5" t="n"/>
+      <c r="C373" s="5" t="n"/>
+      <c r="D373" s="5" t="n"/>
+      <c r="E373" s="5" t="n"/>
+      <c r="F373" s="5" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="5" t="n"/>
+      <c r="I373" s="5" t="n"/>
+      <c r="J373" s="6" t="n"/>
+      <c r="K373" s="5" t="n"/>
+      <c r="L373" s="5" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="n"/>
+      <c r="B374" s="5" t="n"/>
+      <c r="C374" s="5" t="n"/>
+      <c r="D374" s="5" t="n"/>
+      <c r="E374" s="5" t="n"/>
+      <c r="F374" s="5" t="n"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="5" t="n"/>
+      <c r="I374" s="5" t="n"/>
+      <c r="J374" s="6" t="n"/>
+      <c r="K374" s="5" t="n"/>
+      <c r="L374" s="5" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="n"/>
+      <c r="B375" s="5" t="n"/>
+      <c r="C375" s="5" t="n"/>
+      <c r="D375" s="5" t="n"/>
+      <c r="E375" s="5" t="n"/>
+      <c r="F375" s="5" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="5" t="n"/>
+      <c r="I375" s="5" t="n"/>
+      <c r="J375" s="6" t="n"/>
+      <c r="K375" s="5" t="n"/>
+      <c r="L375" s="5" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="n"/>
+      <c r="B376" s="5" t="n"/>
+      <c r="C376" s="5" t="n"/>
+      <c r="D376" s="5" t="n"/>
+      <c r="E376" s="5" t="n"/>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="5" t="n"/>
+      <c r="I376" s="5" t="n"/>
+      <c r="J376" s="6" t="n"/>
+      <c r="K376" s="5" t="n"/>
+      <c r="L376" s="5" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="n"/>
+      <c r="B377" s="5" t="n"/>
+      <c r="C377" s="5" t="n"/>
+      <c r="D377" s="5" t="n"/>
+      <c r="E377" s="5" t="n"/>
+      <c r="F377" s="5" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="5" t="n"/>
+      <c r="I377" s="5" t="n"/>
+      <c r="J377" s="6" t="n"/>
+      <c r="K377" s="5" t="n"/>
+      <c r="L377" s="5" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="n"/>
+      <c r="B378" s="5" t="n"/>
+      <c r="C378" s="5" t="n"/>
+      <c r="D378" s="5" t="n"/>
+      <c r="E378" s="5" t="n"/>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="5" t="n"/>
+      <c r="I378" s="5" t="n"/>
+      <c r="J378" s="6" t="n"/>
+      <c r="K378" s="5" t="n"/>
+      <c r="L378" s="5" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="n"/>
+      <c r="B379" s="5" t="n"/>
+      <c r="C379" s="5" t="n"/>
+      <c r="D379" s="5" t="n"/>
+      <c r="E379" s="5" t="n"/>
+      <c r="F379" s="5" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="5" t="n"/>
+      <c r="I379" s="5" t="n"/>
+      <c r="J379" s="6" t="n"/>
+      <c r="K379" s="5" t="n"/>
+      <c r="L379" s="5" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="n"/>
+      <c r="B380" s="5" t="n"/>
+      <c r="C380" s="5" t="n"/>
+      <c r="D380" s="5" t="n"/>
+      <c r="E380" s="5" t="n"/>
+      <c r="F380" s="5" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="5" t="n"/>
+      <c r="I380" s="5" t="n"/>
+      <c r="J380" s="6" t="n"/>
+      <c r="K380" s="5" t="n"/>
+      <c r="L380" s="5" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="n"/>
+      <c r="B381" s="5" t="n"/>
+      <c r="C381" s="5" t="n"/>
+      <c r="D381" s="5" t="n"/>
+      <c r="E381" s="5" t="n"/>
+      <c r="F381" s="5" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="5" t="n"/>
+      <c r="I381" s="5" t="n"/>
+      <c r="J381" s="6" t="n"/>
+      <c r="K381" s="5" t="n"/>
+      <c r="L381" s="5" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="n"/>
+      <c r="B382" s="5" t="n"/>
+      <c r="C382" s="5" t="n"/>
+      <c r="D382" s="5" t="n"/>
+      <c r="E382" s="5" t="n"/>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="5" t="n"/>
+      <c r="H382" s="5" t="n"/>
+      <c r="I382" s="5" t="n"/>
+      <c r="J382" s="6" t="n"/>
+      <c r="K382" s="5" t="n"/>
+      <c r="L382" s="5" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="5" t="n"/>
+      <c r="B383" s="5" t="n"/>
+      <c r="C383" s="5" t="n"/>
+      <c r="D383" s="5" t="n"/>
+      <c r="E383" s="5" t="n"/>
+      <c r="F383" s="5" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="5" t="n"/>
+      <c r="I383" s="5" t="n"/>
+      <c r="J383" s="6" t="n"/>
+      <c r="K383" s="5" t="n"/>
+      <c r="L383" s="5" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="n"/>
+      <c r="B384" s="5" t="n"/>
+      <c r="C384" s="5" t="n"/>
+      <c r="D384" s="5" t="n"/>
+      <c r="E384" s="5" t="n"/>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="5" t="n"/>
+      <c r="I384" s="5" t="n"/>
+      <c r="J384" s="6" t="n"/>
+      <c r="K384" s="5" t="n"/>
+      <c r="L384" s="5" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="5" t="n"/>
+      <c r="B385" s="5" t="n"/>
+      <c r="C385" s="5" t="n"/>
+      <c r="D385" s="5" t="n"/>
+      <c r="E385" s="5" t="n"/>
+      <c r="F385" s="5" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="5" t="n"/>
+      <c r="I385" s="5" t="n"/>
+      <c r="J385" s="6" t="n"/>
+      <c r="K385" s="5" t="n"/>
+      <c r="L385" s="5" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="5" t="n"/>
+      <c r="B386" s="5" t="n"/>
+      <c r="C386" s="5" t="n"/>
+      <c r="D386" s="5" t="n"/>
+      <c r="E386" s="5" t="n"/>
+      <c r="F386" s="5" t="n"/>
+      <c r="G386" s="5" t="n"/>
+      <c r="H386" s="5" t="n"/>
+      <c r="I386" s="5" t="n"/>
+      <c r="J386" s="6" t="n"/>
+      <c r="K386" s="5" t="n"/>
+      <c r="L386" s="5" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="5" t="n"/>
+      <c r="B387" s="5" t="n"/>
+      <c r="C387" s="5" t="n"/>
+      <c r="D387" s="5" t="n"/>
+      <c r="E387" s="5" t="n"/>
+      <c r="F387" s="5" t="n"/>
+      <c r="G387" s="5" t="n"/>
+      <c r="H387" s="5" t="n"/>
+      <c r="I387" s="5" t="n"/>
+      <c r="J387" s="6" t="n"/>
+      <c r="K387" s="5" t="n"/>
+      <c r="L387" s="5" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="n"/>
+      <c r="B388" s="5" t="n"/>
+      <c r="C388" s="5" t="n"/>
+      <c r="D388" s="5" t="n"/>
+      <c r="E388" s="5" t="n"/>
+      <c r="F388" s="5" t="n"/>
+      <c r="G388" s="5" t="n"/>
+      <c r="H388" s="5" t="n"/>
+      <c r="I388" s="5" t="n"/>
+      <c r="J388" s="6" t="n"/>
+      <c r="K388" s="5" t="n"/>
+      <c r="L388" s="5" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="5" t="n"/>
+      <c r="B389" s="5" t="n"/>
+      <c r="C389" s="5" t="n"/>
+      <c r="D389" s="5" t="n"/>
+      <c r="E389" s="5" t="n"/>
+      <c r="F389" s="5" t="n"/>
+      <c r="G389" s="5" t="n"/>
+      <c r="H389" s="5" t="n"/>
+      <c r="I389" s="5" t="n"/>
+      <c r="J389" s="6" t="n"/>
+      <c r="K389" s="5" t="n"/>
+      <c r="L389" s="5" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="5" t="n"/>
+      <c r="B390" s="5" t="n"/>
+      <c r="C390" s="5" t="n"/>
+      <c r="D390" s="5" t="n"/>
+      <c r="E390" s="5" t="n"/>
+      <c r="F390" s="5" t="n"/>
+      <c r="G390" s="5" t="n"/>
+      <c r="H390" s="5" t="n"/>
+      <c r="I390" s="5" t="n"/>
+      <c r="J390" s="6" t="n"/>
+      <c r="K390" s="5" t="n"/>
+      <c r="L390" s="5" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="5" t="n"/>
+      <c r="B391" s="5" t="n"/>
+      <c r="C391" s="5" t="n"/>
+      <c r="D391" s="5" t="n"/>
+      <c r="E391" s="5" t="n"/>
+      <c r="F391" s="5" t="n"/>
+      <c r="G391" s="5" t="n"/>
+      <c r="H391" s="5" t="n"/>
+      <c r="I391" s="5" t="n"/>
+      <c r="J391" s="6" t="n"/>
+      <c r="K391" s="5" t="n"/>
+      <c r="L391" s="5" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="5" t="n"/>
+      <c r="B392" s="5" t="n"/>
+      <c r="C392" s="5" t="n"/>
+      <c r="D392" s="5" t="n"/>
+      <c r="E392" s="5" t="n"/>
+      <c r="F392" s="5" t="n"/>
+      <c r="G392" s="5" t="n"/>
+      <c r="H392" s="5" t="n"/>
+      <c r="I392" s="5" t="n"/>
+      <c r="J392" s="6" t="n"/>
+      <c r="K392" s="5" t="n"/>
+      <c r="L392" s="5" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="n"/>
+      <c r="B393" s="5" t="n"/>
+      <c r="C393" s="5" t="n"/>
+      <c r="D393" s="5" t="n"/>
+      <c r="E393" s="5" t="n"/>
+      <c r="F393" s="5" t="n"/>
+      <c r="G393" s="5" t="n"/>
+      <c r="H393" s="5" t="n"/>
+      <c r="I393" s="5" t="n"/>
+      <c r="J393" s="6" t="n"/>
+      <c r="K393" s="5" t="n"/>
+      <c r="L393" s="5" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="n"/>
+      <c r="B394" s="5" t="n"/>
+      <c r="C394" s="5" t="n"/>
+      <c r="D394" s="5" t="n"/>
+      <c r="E394" s="5" t="n"/>
+      <c r="F394" s="5" t="n"/>
+      <c r="G394" s="5" t="n"/>
+      <c r="H394" s="5" t="n"/>
+      <c r="I394" s="5" t="n"/>
+      <c r="J394" s="6" t="n"/>
+      <c r="K394" s="5" t="n"/>
+      <c r="L394" s="5" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="n"/>
+      <c r="B395" s="5" t="n"/>
+      <c r="C395" s="5" t="n"/>
+      <c r="D395" s="5" t="n"/>
+      <c r="E395" s="5" t="n"/>
+      <c r="F395" s="5" t="n"/>
+      <c r="G395" s="5" t="n"/>
+      <c r="H395" s="5" t="n"/>
+      <c r="I395" s="5" t="n"/>
+      <c r="J395" s="6" t="n"/>
+      <c r="K395" s="5" t="n"/>
+      <c r="L395" s="5" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="n"/>
+      <c r="B396" s="5" t="n"/>
+      <c r="C396" s="5" t="n"/>
+      <c r="D396" s="5" t="n"/>
+      <c r="E396" s="5" t="n"/>
+      <c r="F396" s="5" t="n"/>
+      <c r="G396" s="5" t="n"/>
+      <c r="H396" s="5" t="n"/>
+      <c r="I396" s="5" t="n"/>
+      <c r="J396" s="6" t="n"/>
+      <c r="K396" s="5" t="n"/>
+      <c r="L396" s="5" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="n"/>
+      <c r="B397" s="5" t="n"/>
+      <c r="C397" s="5" t="n"/>
+      <c r="D397" s="5" t="n"/>
+      <c r="E397" s="5" t="n"/>
+      <c r="F397" s="5" t="n"/>
+      <c r="G397" s="5" t="n"/>
+      <c r="H397" s="5" t="n"/>
+      <c r="I397" s="5" t="n"/>
+      <c r="J397" s="6" t="n"/>
+      <c r="K397" s="5" t="n"/>
+      <c r="L397" s="5" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="5" t="n"/>
+      <c r="B398" s="5" t="n"/>
+      <c r="C398" s="5" t="n"/>
+      <c r="D398" s="5" t="n"/>
+      <c r="E398" s="5" t="n"/>
+      <c r="F398" s="5" t="n"/>
+      <c r="G398" s="5" t="n"/>
+      <c r="H398" s="5" t="n"/>
+      <c r="I398" s="5" t="n"/>
+      <c r="J398" s="6" t="n"/>
+      <c r="K398" s="5" t="n"/>
+      <c r="L398" s="5" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="5" t="n"/>
+      <c r="B399" s="5" t="n"/>
+      <c r="C399" s="5" t="n"/>
+      <c r="D399" s="5" t="n"/>
+      <c r="E399" s="5" t="n"/>
+      <c r="F399" s="5" t="n"/>
+      <c r="G399" s="5" t="n"/>
+      <c r="H399" s="5" t="n"/>
+      <c r="I399" s="5" t="n"/>
+      <c r="J399" s="6" t="n"/>
+      <c r="K399" s="5" t="n"/>
+      <c r="L399" s="5" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="5" t="n"/>
+      <c r="B400" s="5" t="n"/>
+      <c r="C400" s="5" t="n"/>
+      <c r="D400" s="5" t="n"/>
+      <c r="E400" s="5" t="n"/>
+      <c r="F400" s="5" t="n"/>
+      <c r="G400" s="5" t="n"/>
+      <c r="H400" s="5" t="n"/>
+      <c r="I400" s="5" t="n"/>
+      <c r="J400" s="6" t="n"/>
+      <c r="K400" s="5" t="n"/>
+      <c r="L400" s="5" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="5" t="n"/>
+      <c r="B401" s="5" t="n"/>
+      <c r="C401" s="5" t="n"/>
+      <c r="D401" s="5" t="n"/>
+      <c r="E401" s="5" t="n"/>
+      <c r="F401" s="5" t="n"/>
+      <c r="G401" s="5" t="n"/>
+      <c r="H401" s="5" t="n"/>
+      <c r="I401" s="5" t="n"/>
+      <c r="J401" s="6" t="n"/>
+      <c r="K401" s="5" t="n"/>
+      <c r="L401" s="5" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="n"/>
+      <c r="B402" s="5" t="n"/>
+      <c r="C402" s="5" t="n"/>
+      <c r="D402" s="5" t="n"/>
+      <c r="E402" s="5" t="n"/>
+      <c r="F402" s="5" t="n"/>
+      <c r="G402" s="5" t="n"/>
+      <c r="H402" s="5" t="n"/>
+      <c r="I402" s="5" t="n"/>
+      <c r="J402" s="6" t="n"/>
+      <c r="K402" s="5" t="n"/>
+      <c r="L402" s="5" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="n"/>
+      <c r="B403" s="5" t="n"/>
+      <c r="C403" s="5" t="n"/>
+      <c r="D403" s="5" t="n"/>
+      <c r="E403" s="5" t="n"/>
+      <c r="F403" s="5" t="n"/>
+      <c r="G403" s="5" t="n"/>
+      <c r="H403" s="5" t="n"/>
+      <c r="I403" s="5" t="n"/>
+      <c r="J403" s="6" t="n"/>
+      <c r="K403" s="5" t="n"/>
+      <c r="L403" s="5" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="n"/>
+      <c r="B404" s="5" t="n"/>
+      <c r="C404" s="5" t="n"/>
+      <c r="D404" s="5" t="n"/>
+      <c r="E404" s="5" t="n"/>
+      <c r="F404" s="5" t="n"/>
+      <c r="G404" s="5" t="n"/>
+      <c r="H404" s="5" t="n"/>
+      <c r="I404" s="5" t="n"/>
+      <c r="J404" s="6" t="n"/>
+      <c r="K404" s="5" t="n"/>
+      <c r="L404" s="5" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="5" t="n"/>
+      <c r="B405" s="5" t="n"/>
+      <c r="C405" s="5" t="n"/>
+      <c r="D405" s="5" t="n"/>
+      <c r="E405" s="5" t="n"/>
+      <c r="F405" s="5" t="n"/>
+      <c r="G405" s="5" t="n"/>
+      <c r="H405" s="5" t="n"/>
+      <c r="I405" s="5" t="n"/>
+      <c r="J405" s="6" t="n"/>
+      <c r="K405" s="5" t="n"/>
+      <c r="L405" s="5" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="n"/>
+      <c r="B406" s="5" t="n"/>
+      <c r="C406" s="5" t="n"/>
+      <c r="D406" s="5" t="n"/>
+      <c r="E406" s="5" t="n"/>
+      <c r="F406" s="5" t="n"/>
+      <c r="G406" s="5" t="n"/>
+      <c r="H406" s="5" t="n"/>
+      <c r="I406" s="5" t="n"/>
+      <c r="J406" s="6" t="n"/>
+      <c r="K406" s="5" t="n"/>
+      <c r="L406" s="5" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="5" t="n"/>
+      <c r="B407" s="5" t="n"/>
+      <c r="C407" s="5" t="n"/>
+      <c r="D407" s="5" t="n"/>
+      <c r="E407" s="5" t="n"/>
+      <c r="F407" s="5" t="n"/>
+      <c r="G407" s="5" t="n"/>
+      <c r="H407" s="5" t="n"/>
+      <c r="I407" s="5" t="n"/>
+      <c r="J407" s="6" t="n"/>
+      <c r="K407" s="5" t="n"/>
+      <c r="L407" s="5" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="n"/>
+      <c r="B408" s="5" t="n"/>
+      <c r="C408" s="5" t="n"/>
+      <c r="D408" s="5" t="n"/>
+      <c r="E408" s="5" t="n"/>
+      <c r="F408" s="5" t="n"/>
+      <c r="G408" s="5" t="n"/>
+      <c r="H408" s="5" t="n"/>
+      <c r="I408" s="5" t="n"/>
+      <c r="J408" s="6" t="n"/>
+      <c r="K408" s="5" t="n"/>
+      <c r="L408" s="5" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="5" t="n"/>
+      <c r="B409" s="5" t="n"/>
+      <c r="C409" s="5" t="n"/>
+      <c r="D409" s="5" t="n"/>
+      <c r="E409" s="5" t="n"/>
+      <c r="F409" s="5" t="n"/>
+      <c r="G409" s="5" t="n"/>
+      <c r="H409" s="5" t="n"/>
+      <c r="I409" s="5" t="n"/>
+      <c r="J409" s="6" t="n"/>
+      <c r="K409" s="5" t="n"/>
+      <c r="L409" s="5" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="n"/>
+      <c r="B410" s="5" t="n"/>
+      <c r="C410" s="5" t="n"/>
+      <c r="D410" s="5" t="n"/>
+      <c r="E410" s="5" t="n"/>
+      <c r="F410" s="5" t="n"/>
+      <c r="G410" s="5" t="n"/>
+      <c r="H410" s="5" t="n"/>
+      <c r="I410" s="5" t="n"/>
+      <c r="J410" s="6" t="n"/>
+      <c r="K410" s="5" t="n"/>
+      <c r="L410" s="5" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="5" t="n"/>
+      <c r="B411" s="5" t="n"/>
+      <c r="C411" s="5" t="n"/>
+      <c r="D411" s="5" t="n"/>
+      <c r="E411" s="5" t="n"/>
+      <c r="F411" s="5" t="n"/>
+      <c r="G411" s="5" t="n"/>
+      <c r="H411" s="5" t="n"/>
+      <c r="I411" s="5" t="n"/>
+      <c r="J411" s="6" t="n"/>
+      <c r="K411" s="5" t="n"/>
+      <c r="L411" s="5" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="5" t="n"/>
+      <c r="B412" s="5" t="n"/>
+      <c r="C412" s="5" t="n"/>
+      <c r="D412" s="5" t="n"/>
+      <c r="E412" s="5" t="n"/>
+      <c r="F412" s="5" t="n"/>
+      <c r="G412" s="5" t="n"/>
+      <c r="H412" s="5" t="n"/>
+      <c r="I412" s="5" t="n"/>
+      <c r="J412" s="6" t="n"/>
+      <c r="K412" s="5" t="n"/>
+      <c r="L412" s="5" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="5" t="n"/>
+      <c r="B413" s="5" t="n"/>
+      <c r="C413" s="5" t="n"/>
+      <c r="D413" s="5" t="n"/>
+      <c r="E413" s="5" t="n"/>
+      <c r="F413" s="5" t="n"/>
+      <c r="G413" s="5" t="n"/>
+      <c r="H413" s="5" t="n"/>
+      <c r="I413" s="5" t="n"/>
+      <c r="J413" s="6" t="n"/>
+      <c r="K413" s="5" t="n"/>
+      <c r="L413" s="5" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="5" t="n"/>
+      <c r="B414" s="5" t="n"/>
+      <c r="C414" s="5" t="n"/>
+      <c r="D414" s="5" t="n"/>
+      <c r="E414" s="5" t="n"/>
+      <c r="F414" s="5" t="n"/>
+      <c r="G414" s="5" t="n"/>
+      <c r="H414" s="5" t="n"/>
+      <c r="I414" s="5" t="n"/>
+      <c r="J414" s="6" t="n"/>
+      <c r="K414" s="5" t="n"/>
+      <c r="L414" s="5" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="5" t="n"/>
+      <c r="B415" s="5" t="n"/>
+      <c r="C415" s="5" t="n"/>
+      <c r="D415" s="5" t="n"/>
+      <c r="E415" s="5" t="n"/>
+      <c r="F415" s="5" t="n"/>
+      <c r="G415" s="5" t="n"/>
+      <c r="H415" s="5" t="n"/>
+      <c r="I415" s="5" t="n"/>
+      <c r="J415" s="6" t="n"/>
+      <c r="K415" s="5" t="n"/>
+      <c r="L415" s="5" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="5" t="n"/>
+      <c r="B416" s="5" t="n"/>
+      <c r="C416" s="5" t="n"/>
+      <c r="D416" s="5" t="n"/>
+      <c r="E416" s="5" t="n"/>
+      <c r="F416" s="5" t="n"/>
+      <c r="G416" s="5" t="n"/>
+      <c r="H416" s="5" t="n"/>
+      <c r="I416" s="5" t="n"/>
+      <c r="J416" s="6" t="n"/>
+      <c r="K416" s="5" t="n"/>
+      <c r="L416" s="5" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="5" t="n"/>
+      <c r="B417" s="5" t="n"/>
+      <c r="C417" s="5" t="n"/>
+      <c r="D417" s="5" t="n"/>
+      <c r="E417" s="5" t="n"/>
+      <c r="F417" s="5" t="n"/>
+      <c r="G417" s="5" t="n"/>
+      <c r="H417" s="5" t="n"/>
+      <c r="I417" s="5" t="n"/>
+      <c r="J417" s="6" t="n"/>
+      <c r="K417" s="5" t="n"/>
+      <c r="L417" s="5" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="5" t="n"/>
+      <c r="B418" s="5" t="n"/>
+      <c r="C418" s="5" t="n"/>
+      <c r="D418" s="5" t="n"/>
+      <c r="E418" s="5" t="n"/>
+      <c r="F418" s="5" t="n"/>
+      <c r="G418" s="5" t="n"/>
+      <c r="H418" s="5" t="n"/>
+      <c r="I418" s="5" t="n"/>
+      <c r="J418" s="6" t="n"/>
+      <c r="K418" s="5" t="n"/>
+      <c r="L418" s="5" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="5" t="n"/>
+      <c r="B419" s="5" t="n"/>
+      <c r="C419" s="5" t="n"/>
+      <c r="D419" s="5" t="n"/>
+      <c r="E419" s="5" t="n"/>
+      <c r="F419" s="5" t="n"/>
+      <c r="G419" s="5" t="n"/>
+      <c r="H419" s="5" t="n"/>
+      <c r="I419" s="5" t="n"/>
+      <c r="J419" s="6" t="n"/>
+      <c r="K419" s="5" t="n"/>
+      <c r="L419" s="5" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="5" t="n"/>
+      <c r="B420" s="5" t="n"/>
+      <c r="C420" s="5" t="n"/>
+      <c r="D420" s="5" t="n"/>
+      <c r="E420" s="5" t="n"/>
+      <c r="F420" s="5" t="n"/>
+      <c r="G420" s="5" t="n"/>
+      <c r="H420" s="5" t="n"/>
+      <c r="I420" s="5" t="n"/>
+      <c r="J420" s="6" t="n"/>
+      <c r="K420" s="5" t="n"/>
+      <c r="L420" s="5" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="5" t="n"/>
+      <c r="B421" s="5" t="n"/>
+      <c r="C421" s="5" t="n"/>
+      <c r="D421" s="5" t="n"/>
+      <c r="E421" s="5" t="n"/>
+      <c r="F421" s="5" t="n"/>
+      <c r="G421" s="5" t="n"/>
+      <c r="H421" s="5" t="n"/>
+      <c r="I421" s="5" t="n"/>
+      <c r="J421" s="6" t="n"/>
+      <c r="K421" s="5" t="n"/>
+      <c r="L421" s="5" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="5" t="n"/>
+      <c r="B422" s="5" t="n"/>
+      <c r="C422" s="5" t="n"/>
+      <c r="D422" s="5" t="n"/>
+      <c r="E422" s="5" t="n"/>
+      <c r="F422" s="5" t="n"/>
+      <c r="G422" s="5" t="n"/>
+      <c r="H422" s="5" t="n"/>
+      <c r="I422" s="5" t="n"/>
+      <c r="J422" s="6" t="n"/>
+      <c r="K422" s="5" t="n"/>
+      <c r="L422" s="5" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="5" t="n"/>
+      <c r="B423" s="5" t="n"/>
+      <c r="C423" s="5" t="n"/>
+      <c r="D423" s="5" t="n"/>
+      <c r="E423" s="5" t="n"/>
+      <c r="F423" s="5" t="n"/>
+      <c r="G423" s="5" t="n"/>
+      <c r="H423" s="5" t="n"/>
+      <c r="I423" s="5" t="n"/>
+      <c r="J423" s="6" t="n"/>
+      <c r="K423" s="5" t="n"/>
+      <c r="L423" s="5" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="5" t="n"/>
+      <c r="B424" s="5" t="n"/>
+      <c r="C424" s="5" t="n"/>
+      <c r="D424" s="5" t="n"/>
+      <c r="E424" s="5" t="n"/>
+      <c r="F424" s="5" t="n"/>
+      <c r="G424" s="5" t="n"/>
+      <c r="H424" s="5" t="n"/>
+      <c r="I424" s="5" t="n"/>
+      <c r="J424" s="6" t="n"/>
+      <c r="K424" s="5" t="n"/>
+      <c r="L424" s="5" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="n"/>
+      <c r="B425" s="5" t="n"/>
+      <c r="C425" s="5" t="n"/>
+      <c r="D425" s="5" t="n"/>
+      <c r="E425" s="5" t="n"/>
+      <c r="F425" s="5" t="n"/>
+      <c r="G425" s="5" t="n"/>
+      <c r="H425" s="5" t="n"/>
+      <c r="I425" s="5" t="n"/>
+      <c r="J425" s="6" t="n"/>
+      <c r="K425" s="5" t="n"/>
+      <c r="L425" s="5" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="5" t="n"/>
+      <c r="B426" s="5" t="n"/>
+      <c r="C426" s="5" t="n"/>
+      <c r="D426" s="5" t="n"/>
+      <c r="E426" s="5" t="n"/>
+      <c r="F426" s="5" t="n"/>
+      <c r="G426" s="5" t="n"/>
+      <c r="H426" s="5" t="n"/>
+      <c r="I426" s="5" t="n"/>
+      <c r="J426" s="6" t="n"/>
+      <c r="K426" s="5" t="n"/>
+      <c r="L426" s="5" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="5" t="n"/>
+      <c r="B427" s="5" t="n"/>
+      <c r="C427" s="5" t="n"/>
+      <c r="D427" s="5" t="n"/>
+      <c r="E427" s="5" t="n"/>
+      <c r="F427" s="5" t="n"/>
+      <c r="G427" s="5" t="n"/>
+      <c r="H427" s="5" t="n"/>
+      <c r="I427" s="5" t="n"/>
+      <c r="J427" s="6" t="n"/>
+      <c r="K427" s="5" t="n"/>
+      <c r="L427" s="5" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="5" t="n"/>
+      <c r="B428" s="5" t="n"/>
+      <c r="C428" s="5" t="n"/>
+      <c r="D428" s="5" t="n"/>
+      <c r="E428" s="5" t="n"/>
+      <c r="F428" s="5" t="n"/>
+      <c r="G428" s="5" t="n"/>
+      <c r="H428" s="5" t="n"/>
+      <c r="I428" s="5" t="n"/>
+      <c r="J428" s="6" t="n"/>
+      <c r="K428" s="5" t="n"/>
+      <c r="L428" s="5" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="5" t="n"/>
+      <c r="B429" s="5" t="n"/>
+      <c r="C429" s="5" t="n"/>
+      <c r="D429" s="5" t="n"/>
+      <c r="E429" s="5" t="n"/>
+      <c r="F429" s="5" t="n"/>
+      <c r="G429" s="5" t="n"/>
+      <c r="H429" s="5" t="n"/>
+      <c r="I429" s="5" t="n"/>
+      <c r="J429" s="6" t="n"/>
+      <c r="K429" s="5" t="n"/>
+      <c r="L429" s="5" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="5" t="n"/>
+      <c r="B430" s="5" t="n"/>
+      <c r="C430" s="5" t="n"/>
+      <c r="D430" s="5" t="n"/>
+      <c r="E430" s="5" t="n"/>
+      <c r="F430" s="5" t="n"/>
+      <c r="G430" s="5" t="n"/>
+      <c r="H430" s="5" t="n"/>
+      <c r="I430" s="5" t="n"/>
+      <c r="J430" s="6" t="n"/>
+      <c r="K430" s="5" t="n"/>
+      <c r="L430" s="5" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="5" t="n"/>
+      <c r="B431" s="5" t="n"/>
+      <c r="C431" s="5" t="n"/>
+      <c r="D431" s="5" t="n"/>
+      <c r="E431" s="5" t="n"/>
+      <c r="F431" s="5" t="n"/>
+      <c r="G431" s="5" t="n"/>
+      <c r="H431" s="5" t="n"/>
+      <c r="I431" s="5" t="n"/>
+      <c r="J431" s="6" t="n"/>
+      <c r="K431" s="5" t="n"/>
+      <c r="L431" s="5" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="5" t="n"/>
+      <c r="B432" s="5" t="n"/>
+      <c r="C432" s="5" t="n"/>
+      <c r="D432" s="5" t="n"/>
+      <c r="E432" s="5" t="n"/>
+      <c r="F432" s="5" t="n"/>
+      <c r="G432" s="5" t="n"/>
+      <c r="H432" s="5" t="n"/>
+      <c r="I432" s="5" t="n"/>
+      <c r="J432" s="6" t="n"/>
+      <c r="K432" s="5" t="n"/>
+      <c r="L432" s="5" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="5" t="n"/>
+      <c r="B433" s="5" t="n"/>
+      <c r="C433" s="5" t="n"/>
+      <c r="D433" s="5" t="n"/>
+      <c r="E433" s="5" t="n"/>
+      <c r="F433" s="5" t="n"/>
+      <c r="G433" s="5" t="n"/>
+      <c r="H433" s="5" t="n"/>
+      <c r="I433" s="5" t="n"/>
+      <c r="J433" s="6" t="n"/>
+      <c r="K433" s="5" t="n"/>
+      <c r="L433" s="5" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="5" t="n"/>
+      <c r="B434" s="5" t="n"/>
+      <c r="C434" s="5" t="n"/>
+      <c r="D434" s="5" t="n"/>
+      <c r="E434" s="5" t="n"/>
+      <c r="F434" s="5" t="n"/>
+      <c r="G434" s="5" t="n"/>
+      <c r="H434" s="5" t="n"/>
+      <c r="I434" s="5" t="n"/>
+      <c r="J434" s="6" t="n"/>
+      <c r="K434" s="5" t="n"/>
+      <c r="L434" s="5" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="5" t="n"/>
+      <c r="B435" s="5" t="n"/>
+      <c r="C435" s="5" t="n"/>
+      <c r="D435" s="5" t="n"/>
+      <c r="E435" s="5" t="n"/>
+      <c r="F435" s="5" t="n"/>
+      <c r="G435" s="5" t="n"/>
+      <c r="H435" s="5" t="n"/>
+      <c r="I435" s="5" t="n"/>
+      <c r="J435" s="6" t="n"/>
+      <c r="K435" s="5" t="n"/>
+      <c r="L435" s="5" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="5" t="n"/>
+      <c r="B436" s="5" t="n"/>
+      <c r="C436" s="5" t="n"/>
+      <c r="D436" s="5" t="n"/>
+      <c r="E436" s="5" t="n"/>
+      <c r="F436" s="5" t="n"/>
+      <c r="G436" s="5" t="n"/>
+      <c r="H436" s="5" t="n"/>
+      <c r="I436" s="5" t="n"/>
+      <c r="J436" s="6" t="n"/>
+      <c r="K436" s="5" t="n"/>
+      <c r="L436" s="5" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="5" t="n"/>
+      <c r="B437" s="5" t="n"/>
+      <c r="C437" s="5" t="n"/>
+      <c r="D437" s="5" t="n"/>
+      <c r="E437" s="5" t="n"/>
+      <c r="F437" s="5" t="n"/>
+      <c r="G437" s="5" t="n"/>
+      <c r="H437" s="5" t="n"/>
+      <c r="I437" s="5" t="n"/>
+      <c r="J437" s="6" t="n"/>
+      <c r="K437" s="5" t="n"/>
+      <c r="L437" s="5" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="5" t="n"/>
+      <c r="B438" s="5" t="n"/>
+      <c r="C438" s="5" t="n"/>
+      <c r="D438" s="5" t="n"/>
+      <c r="E438" s="5" t="n"/>
+      <c r="F438" s="5" t="n"/>
+      <c r="G438" s="5" t="n"/>
+      <c r="H438" s="5" t="n"/>
+      <c r="I438" s="5" t="n"/>
+      <c r="J438" s="6" t="n"/>
+      <c r="K438" s="5" t="n"/>
+      <c r="L438" s="5" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="5" t="n"/>
+      <c r="B439" s="5" t="n"/>
+      <c r="C439" s="5" t="n"/>
+      <c r="D439" s="5" t="n"/>
+      <c r="E439" s="5" t="n"/>
+      <c r="F439" s="5" t="n"/>
+      <c r="G439" s="5" t="n"/>
+      <c r="H439" s="5" t="n"/>
+      <c r="I439" s="5" t="n"/>
+      <c r="J439" s="6" t="n"/>
+      <c r="K439" s="5" t="n"/>
+      <c r="L439" s="5" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="5" t="n"/>
+      <c r="B440" s="5" t="n"/>
+      <c r="C440" s="5" t="n"/>
+      <c r="D440" s="5" t="n"/>
+      <c r="E440" s="5" t="n"/>
+      <c r="F440" s="5" t="n"/>
+      <c r="G440" s="5" t="n"/>
+      <c r="H440" s="5" t="n"/>
+      <c r="I440" s="5" t="n"/>
+      <c r="J440" s="6" t="n"/>
+      <c r="K440" s="5" t="n"/>
+      <c r="L440" s="5" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="5" t="n"/>
+      <c r="B441" s="5" t="n"/>
+      <c r="C441" s="5" t="n"/>
+      <c r="D441" s="5" t="n"/>
+      <c r="E441" s="5" t="n"/>
+      <c r="F441" s="5" t="n"/>
+      <c r="G441" s="5" t="n"/>
+      <c r="H441" s="5" t="n"/>
+      <c r="I441" s="5" t="n"/>
+      <c r="J441" s="6" t="n"/>
+      <c r="K441" s="5" t="n"/>
+      <c r="L441" s="5" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="5" t="n"/>
+      <c r="B442" s="5" t="n"/>
+      <c r="C442" s="5" t="n"/>
+      <c r="D442" s="5" t="n"/>
+      <c r="E442" s="5" t="n"/>
+      <c r="F442" s="5" t="n"/>
+      <c r="G442" s="5" t="n"/>
+      <c r="H442" s="5" t="n"/>
+      <c r="I442" s="5" t="n"/>
+      <c r="J442" s="6" t="n"/>
+      <c r="K442" s="5" t="n"/>
+      <c r="L442" s="5" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="5" t="n"/>
+      <c r="B443" s="5" t="n"/>
+      <c r="C443" s="5" t="n"/>
+      <c r="D443" s="5" t="n"/>
+      <c r="E443" s="5" t="n"/>
+      <c r="F443" s="5" t="n"/>
+      <c r="G443" s="5" t="n"/>
+      <c r="H443" s="5" t="n"/>
+      <c r="I443" s="5" t="n"/>
+      <c r="J443" s="6" t="n"/>
+      <c r="K443" s="5" t="n"/>
+      <c r="L443" s="5" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="5" t="n"/>
+      <c r="B444" s="5" t="n"/>
+      <c r="C444" s="5" t="n"/>
+      <c r="D444" s="5" t="n"/>
+      <c r="E444" s="5" t="n"/>
+      <c r="F444" s="5" t="n"/>
+      <c r="G444" s="5" t="n"/>
+      <c r="H444" s="5" t="n"/>
+      <c r="I444" s="5" t="n"/>
+      <c r="J444" s="6" t="n"/>
+      <c r="K444" s="5" t="n"/>
+      <c r="L444" s="5" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="5" t="n"/>
+      <c r="B445" s="5" t="n"/>
+      <c r="C445" s="5" t="n"/>
+      <c r="D445" s="5" t="n"/>
+      <c r="E445" s="5" t="n"/>
+      <c r="F445" s="5" t="n"/>
+      <c r="G445" s="5" t="n"/>
+      <c r="H445" s="5" t="n"/>
+      <c r="I445" s="5" t="n"/>
+      <c r="J445" s="6" t="n"/>
+      <c r="K445" s="5" t="n"/>
+      <c r="L445" s="5" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="5" t="n"/>
+      <c r="B446" s="5" t="n"/>
+      <c r="C446" s="5" t="n"/>
+      <c r="D446" s="5" t="n"/>
+      <c r="E446" s="5" t="n"/>
+      <c r="F446" s="5" t="n"/>
+      <c r="G446" s="5" t="n"/>
+      <c r="H446" s="5" t="n"/>
+      <c r="I446" s="5" t="n"/>
+      <c r="J446" s="6" t="n"/>
+      <c r="K446" s="5" t="n"/>
+      <c r="L446" s="5" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="n"/>
+      <c r="B447" s="5" t="n"/>
+      <c r="C447" s="5" t="n"/>
+      <c r="D447" s="5" t="n"/>
+      <c r="E447" s="5" t="n"/>
+      <c r="F447" s="5" t="n"/>
+      <c r="G447" s="5" t="n"/>
+      <c r="H447" s="5" t="n"/>
+      <c r="I447" s="5" t="n"/>
+      <c r="J447" s="6" t="n"/>
+      <c r="K447" s="5" t="n"/>
+      <c r="L447" s="5" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="n"/>
+      <c r="B448" s="5" t="n"/>
+      <c r="C448" s="5" t="n"/>
+      <c r="D448" s="5" t="n"/>
+      <c r="E448" s="5" t="n"/>
+      <c r="F448" s="5" t="n"/>
+      <c r="G448" s="5" t="n"/>
+      <c r="H448" s="5" t="n"/>
+      <c r="I448" s="5" t="n"/>
+      <c r="J448" s="6" t="n"/>
+      <c r="K448" s="5" t="n"/>
+      <c r="L448" s="5" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="n"/>
+      <c r="B449" s="5" t="n"/>
+      <c r="C449" s="5" t="n"/>
+      <c r="D449" s="5" t="n"/>
+      <c r="E449" s="5" t="n"/>
+      <c r="F449" s="5" t="n"/>
+      <c r="G449" s="5" t="n"/>
+      <c r="H449" s="5" t="n"/>
+      <c r="I449" s="5" t="n"/>
+      <c r="J449" s="6" t="n"/>
+      <c r="K449" s="5" t="n"/>
+      <c r="L449" s="5" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="n"/>
+      <c r="B450" s="5" t="n"/>
+      <c r="C450" s="5" t="n"/>
+      <c r="D450" s="5" t="n"/>
+      <c r="E450" s="5" t="n"/>
+      <c r="F450" s="5" t="n"/>
+      <c r="G450" s="5" t="n"/>
+      <c r="H450" s="5" t="n"/>
+      <c r="I450" s="5" t="n"/>
+      <c r="J450" s="6" t="n"/>
+      <c r="K450" s="5" t="n"/>
+      <c r="L450" s="5" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="5" t="n"/>
+      <c r="B451" s="5" t="n"/>
+      <c r="C451" s="5" t="n"/>
+      <c r="D451" s="5" t="n"/>
+      <c r="E451" s="5" t="n"/>
+      <c r="F451" s="5" t="n"/>
+      <c r="G451" s="5" t="n"/>
+      <c r="H451" s="5" t="n"/>
+      <c r="I451" s="5" t="n"/>
+      <c r="J451" s="6" t="n"/>
+      <c r="K451" s="5" t="n"/>
+      <c r="L451" s="5" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="5" t="n"/>
+      <c r="B452" s="5" t="n"/>
+      <c r="C452" s="5" t="n"/>
+      <c r="D452" s="5" t="n"/>
+      <c r="E452" s="5" t="n"/>
+      <c r="F452" s="5" t="n"/>
+      <c r="G452" s="5" t="n"/>
+      <c r="H452" s="5" t="n"/>
+      <c r="I452" s="5" t="n"/>
+      <c r="J452" s="6" t="n"/>
+      <c r="K452" s="5" t="n"/>
+      <c r="L452" s="5" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="n"/>
+      <c r="B453" s="5" t="n"/>
+      <c r="C453" s="5" t="n"/>
+      <c r="D453" s="5" t="n"/>
+      <c r="E453" s="5" t="n"/>
+      <c r="F453" s="5" t="n"/>
+      <c r="G453" s="5" t="n"/>
+      <c r="H453" s="5" t="n"/>
+      <c r="I453" s="5" t="n"/>
+      <c r="J453" s="6" t="n"/>
+      <c r="K453" s="5" t="n"/>
+      <c r="L453" s="5" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="5" t="n"/>
+      <c r="B454" s="5" t="n"/>
+      <c r="C454" s="5" t="n"/>
+      <c r="D454" s="5" t="n"/>
+      <c r="E454" s="5" t="n"/>
+      <c r="F454" s="5" t="n"/>
+      <c r="G454" s="5" t="n"/>
+      <c r="H454" s="5" t="n"/>
+      <c r="I454" s="5" t="n"/>
+      <c r="J454" s="6" t="n"/>
+      <c r="K454" s="5" t="n"/>
+      <c r="L454" s="5" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="5" t="n"/>
+      <c r="B455" s="5" t="n"/>
+      <c r="C455" s="5" t="n"/>
+      <c r="D455" s="5" t="n"/>
+      <c r="E455" s="5" t="n"/>
+      <c r="F455" s="5" t="n"/>
+      <c r="G455" s="5" t="n"/>
+      <c r="H455" s="5" t="n"/>
+      <c r="I455" s="5" t="n"/>
+      <c r="J455" s="6" t="n"/>
+      <c r="K455" s="5" t="n"/>
+      <c r="L455" s="5" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="5" t="n"/>
+      <c r="B456" s="5" t="n"/>
+      <c r="C456" s="5" t="n"/>
+      <c r="D456" s="5" t="n"/>
+      <c r="E456" s="5" t="n"/>
+      <c r="F456" s="5" t="n"/>
+      <c r="G456" s="5" t="n"/>
+      <c r="H456" s="5" t="n"/>
+      <c r="I456" s="5" t="n"/>
+      <c r="J456" s="6" t="n"/>
+      <c r="K456" s="5" t="n"/>
+      <c r="L456" s="5" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="5" t="n"/>
+      <c r="B457" s="5" t="n"/>
+      <c r="C457" s="5" t="n"/>
+      <c r="D457" s="5" t="n"/>
+      <c r="E457" s="5" t="n"/>
+      <c r="F457" s="5" t="n"/>
+      <c r="G457" s="5" t="n"/>
+      <c r="H457" s="5" t="n"/>
+      <c r="I457" s="5" t="n"/>
+      <c r="J457" s="6" t="n"/>
+      <c r="K457" s="5" t="n"/>
+      <c r="L457" s="5" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="5" t="n"/>
+      <c r="B458" s="5" t="n"/>
+      <c r="C458" s="5" t="n"/>
+      <c r="D458" s="5" t="n"/>
+      <c r="E458" s="5" t="n"/>
+      <c r="F458" s="5" t="n"/>
+      <c r="G458" s="5" t="n"/>
+      <c r="H458" s="5" t="n"/>
+      <c r="I458" s="5" t="n"/>
+      <c r="J458" s="6" t="n"/>
+      <c r="K458" s="5" t="n"/>
+      <c r="L458" s="5" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="5" t="n"/>
+      <c r="B459" s="5" t="n"/>
+      <c r="C459" s="5" t="n"/>
+      <c r="D459" s="5" t="n"/>
+      <c r="E459" s="5" t="n"/>
+      <c r="F459" s="5" t="n"/>
+      <c r="G459" s="5" t="n"/>
+      <c r="H459" s="5" t="n"/>
+      <c r="I459" s="5" t="n"/>
+      <c r="J459" s="6" t="n"/>
+      <c r="K459" s="5" t="n"/>
+      <c r="L459" s="5" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="5" t="n"/>
+      <c r="B460" s="5" t="n"/>
+      <c r="C460" s="5" t="n"/>
+      <c r="D460" s="5" t="n"/>
+      <c r="E460" s="5" t="n"/>
+      <c r="F460" s="5" t="n"/>
+      <c r="G460" s="5" t="n"/>
+      <c r="H460" s="5" t="n"/>
+      <c r="I460" s="5" t="n"/>
+      <c r="J460" s="6" t="n"/>
+      <c r="K460" s="5" t="n"/>
+      <c r="L460" s="5" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="5" t="n"/>
+      <c r="B461" s="5" t="n"/>
+      <c r="C461" s="5" t="n"/>
+      <c r="D461" s="5" t="n"/>
+      <c r="E461" s="5" t="n"/>
+      <c r="F461" s="5" t="n"/>
+      <c r="G461" s="5" t="n"/>
+      <c r="H461" s="5" t="n"/>
+      <c r="I461" s="5" t="n"/>
+      <c r="J461" s="6" t="n"/>
+      <c r="K461" s="5" t="n"/>
+      <c r="L461" s="5" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="5" t="n"/>
+      <c r="B462" s="5" t="n"/>
+      <c r="C462" s="5" t="n"/>
+      <c r="D462" s="5" t="n"/>
+      <c r="E462" s="5" t="n"/>
+      <c r="F462" s="5" t="n"/>
+      <c r="G462" s="5" t="n"/>
+      <c r="H462" s="5" t="n"/>
+      <c r="I462" s="5" t="n"/>
+      <c r="J462" s="6" t="n"/>
+      <c r="K462" s="5" t="n"/>
+      <c r="L462" s="5" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="5" t="n"/>
+      <c r="B463" s="5" t="n"/>
+      <c r="C463" s="5" t="n"/>
+      <c r="D463" s="5" t="n"/>
+      <c r="E463" s="5" t="n"/>
+      <c r="F463" s="5" t="n"/>
+      <c r="G463" s="5" t="n"/>
+      <c r="H463" s="5" t="n"/>
+      <c r="I463" s="5" t="n"/>
+      <c r="J463" s="6" t="n"/>
+      <c r="K463" s="5" t="n"/>
+      <c r="L463" s="5" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="5" t="n"/>
+      <c r="B464" s="5" t="n"/>
+      <c r="C464" s="5" t="n"/>
+      <c r="D464" s="5" t="n"/>
+      <c r="E464" s="5" t="n"/>
+      <c r="F464" s="5" t="n"/>
+      <c r="G464" s="5" t="n"/>
+      <c r="H464" s="5" t="n"/>
+      <c r="I464" s="5" t="n"/>
+      <c r="J464" s="6" t="n"/>
+      <c r="K464" s="5" t="n"/>
+      <c r="L464" s="5" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="5" t="n"/>
+      <c r="B465" s="5" t="n"/>
+      <c r="C465" s="5" t="n"/>
+      <c r="D465" s="5" t="n"/>
+      <c r="E465" s="5" t="n"/>
+      <c r="F465" s="5" t="n"/>
+      <c r="G465" s="5" t="n"/>
+      <c r="H465" s="5" t="n"/>
+      <c r="I465" s="5" t="n"/>
+      <c r="J465" s="6" t="n"/>
+      <c r="K465" s="5" t="n"/>
+      <c r="L465" s="5" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="5" t="n"/>
+      <c r="B466" s="5" t="n"/>
+      <c r="C466" s="5" t="n"/>
+      <c r="D466" s="5" t="n"/>
+      <c r="E466" s="5" t="n"/>
+      <c r="F466" s="5" t="n"/>
+      <c r="G466" s="5" t="n"/>
+      <c r="H466" s="5" t="n"/>
+      <c r="I466" s="5" t="n"/>
+      <c r="J466" s="6" t="n"/>
+      <c r="K466" s="5" t="n"/>
+      <c r="L466" s="5" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="n"/>
+      <c r="B467" s="5" t="n"/>
+      <c r="C467" s="5" t="n"/>
+      <c r="D467" s="5" t="n"/>
+      <c r="E467" s="5" t="n"/>
+      <c r="F467" s="5" t="n"/>
+      <c r="G467" s="5" t="n"/>
+      <c r="H467" s="5" t="n"/>
+      <c r="I467" s="5" t="n"/>
+      <c r="J467" s="6" t="n"/>
+      <c r="K467" s="5" t="n"/>
+      <c r="L467" s="5" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="5" t="n"/>
+      <c r="B468" s="5" t="n"/>
+      <c r="C468" s="5" t="n"/>
+      <c r="D468" s="5" t="n"/>
+      <c r="E468" s="5" t="n"/>
+      <c r="F468" s="5" t="n"/>
+      <c r="G468" s="5" t="n"/>
+      <c r="H468" s="5" t="n"/>
+      <c r="I468" s="5" t="n"/>
+      <c r="J468" s="6" t="n"/>
+      <c r="K468" s="5" t="n"/>
+      <c r="L468" s="5" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="n"/>
+      <c r="B469" s="5" t="n"/>
+      <c r="C469" s="5" t="n"/>
+      <c r="D469" s="5" t="n"/>
+      <c r="E469" s="5" t="n"/>
+      <c r="F469" s="5" t="n"/>
+      <c r="G469" s="5" t="n"/>
+      <c r="H469" s="5" t="n"/>
+      <c r="I469" s="5" t="n"/>
+      <c r="J469" s="6" t="n"/>
+      <c r="K469" s="5" t="n"/>
+      <c r="L469" s="5" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="n"/>
+      <c r="B470" s="5" t="n"/>
+      <c r="C470" s="5" t="n"/>
+      <c r="D470" s="5" t="n"/>
+      <c r="E470" s="5" t="n"/>
+      <c r="F470" s="5" t="n"/>
+      <c r="G470" s="5" t="n"/>
+      <c r="H470" s="5" t="n"/>
+      <c r="I470" s="5" t="n"/>
+      <c r="J470" s="6" t="n"/>
+      <c r="K470" s="5" t="n"/>
+      <c r="L470" s="5" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="5" t="n"/>
+      <c r="B471" s="5" t="n"/>
+      <c r="C471" s="5" t="n"/>
+      <c r="D471" s="5" t="n"/>
+      <c r="E471" s="5" t="n"/>
+      <c r="F471" s="5" t="n"/>
+      <c r="G471" s="5" t="n"/>
+      <c r="H471" s="5" t="n"/>
+      <c r="I471" s="5" t="n"/>
+      <c r="J471" s="6" t="n"/>
+      <c r="K471" s="5" t="n"/>
+      <c r="L471" s="5" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="5" t="n"/>
+      <c r="B472" s="5" t="n"/>
+      <c r="C472" s="5" t="n"/>
+      <c r="D472" s="5" t="n"/>
+      <c r="E472" s="5" t="n"/>
+      <c r="F472" s="5" t="n"/>
+      <c r="G472" s="5" t="n"/>
+      <c r="H472" s="5" t="n"/>
+      <c r="I472" s="5" t="n"/>
+      <c r="J472" s="6" t="n"/>
+      <c r="K472" s="5" t="n"/>
+      <c r="L472" s="5" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="5" t="n"/>
+      <c r="B473" s="5" t="n"/>
+      <c r="C473" s="5" t="n"/>
+      <c r="D473" s="5" t="n"/>
+      <c r="E473" s="5" t="n"/>
+      <c r="F473" s="5" t="n"/>
+      <c r="G473" s="5" t="n"/>
+      <c r="H473" s="5" t="n"/>
+      <c r="I473" s="5" t="n"/>
+      <c r="J473" s="6" t="n"/>
+      <c r="K473" s="5" t="n"/>
+      <c r="L473" s="5" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="5" t="n"/>
+      <c r="B474" s="5" t="n"/>
+      <c r="C474" s="5" t="n"/>
+      <c r="D474" s="5" t="n"/>
+      <c r="E474" s="5" t="n"/>
+      <c r="F474" s="5" t="n"/>
+      <c r="G474" s="5" t="n"/>
+      <c r="H474" s="5" t="n"/>
+      <c r="I474" s="5" t="n"/>
+      <c r="J474" s="6" t="n"/>
+      <c r="K474" s="5" t="n"/>
+      <c r="L474" s="5" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="5" t="n"/>
+      <c r="B475" s="5" t="n"/>
+      <c r="C475" s="5" t="n"/>
+      <c r="D475" s="5" t="n"/>
+      <c r="E475" s="5" t="n"/>
+      <c r="F475" s="5" t="n"/>
+      <c r="G475" s="5" t="n"/>
+      <c r="H475" s="5" t="n"/>
+      <c r="I475" s="5" t="n"/>
+      <c r="J475" s="6" t="n"/>
+      <c r="K475" s="5" t="n"/>
+      <c r="L475" s="5" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="5" t="n"/>
+      <c r="B476" s="5" t="n"/>
+      <c r="C476" s="5" t="n"/>
+      <c r="D476" s="5" t="n"/>
+      <c r="E476" s="5" t="n"/>
+      <c r="F476" s="5" t="n"/>
+      <c r="G476" s="5" t="n"/>
+      <c r="H476" s="5" t="n"/>
+      <c r="I476" s="5" t="n"/>
+      <c r="J476" s="6" t="n"/>
+      <c r="K476" s="5" t="n"/>
+      <c r="L476" s="5" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="5" t="n"/>
+      <c r="B477" s="5" t="n"/>
+      <c r="C477" s="5" t="n"/>
+      <c r="D477" s="5" t="n"/>
+      <c r="E477" s="5" t="n"/>
+      <c r="F477" s="5" t="n"/>
+      <c r="G477" s="5" t="n"/>
+      <c r="H477" s="5" t="n"/>
+      <c r="I477" s="5" t="n"/>
+      <c r="J477" s="6" t="n"/>
+      <c r="K477" s="5" t="n"/>
+      <c r="L477" s="5" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="5" t="n"/>
+      <c r="B478" s="5" t="n"/>
+      <c r="C478" s="5" t="n"/>
+      <c r="D478" s="5" t="n"/>
+      <c r="E478" s="5" t="n"/>
+      <c r="F478" s="5" t="n"/>
+      <c r="G478" s="5" t="n"/>
+      <c r="H478" s="5" t="n"/>
+      <c r="I478" s="5" t="n"/>
+      <c r="J478" s="6" t="n"/>
+      <c r="K478" s="5" t="n"/>
+      <c r="L478" s="5" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="5" t="n"/>
+      <c r="B479" s="5" t="n"/>
+      <c r="C479" s="5" t="n"/>
+      <c r="D479" s="5" t="n"/>
+      <c r="E479" s="5" t="n"/>
+      <c r="F479" s="5" t="n"/>
+      <c r="G479" s="5" t="n"/>
+      <c r="H479" s="5" t="n"/>
+      <c r="I479" s="5" t="n"/>
+      <c r="J479" s="6" t="n"/>
+      <c r="K479" s="5" t="n"/>
+      <c r="L479" s="5" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="5" t="n"/>
+      <c r="B480" s="5" t="n"/>
+      <c r="C480" s="5" t="n"/>
+      <c r="D480" s="5" t="n"/>
+      <c r="E480" s="5" t="n"/>
+      <c r="F480" s="5" t="n"/>
+      <c r="G480" s="5" t="n"/>
+      <c r="H480" s="5" t="n"/>
+      <c r="I480" s="5" t="n"/>
+      <c r="J480" s="6" t="n"/>
+      <c r="K480" s="5" t="n"/>
+      <c r="L480" s="5" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="n"/>
+      <c r="B481" s="5" t="n"/>
+      <c r="C481" s="5" t="n"/>
+      <c r="D481" s="5" t="n"/>
+      <c r="E481" s="5" t="n"/>
+      <c r="F481" s="5" t="n"/>
+      <c r="G481" s="5" t="n"/>
+      <c r="H481" s="5" t="n"/>
+      <c r="I481" s="5" t="n"/>
+      <c r="J481" s="6" t="n"/>
+      <c r="K481" s="5" t="n"/>
+      <c r="L481" s="5" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="5" t="n"/>
+      <c r="B482" s="5" t="n"/>
+      <c r="C482" s="5" t="n"/>
+      <c r="D482" s="5" t="n"/>
+      <c r="E482" s="5" t="n"/>
+      <c r="F482" s="5" t="n"/>
+      <c r="G482" s="5" t="n"/>
+      <c r="H482" s="5" t="n"/>
+      <c r="I482" s="5" t="n"/>
+      <c r="J482" s="6" t="n"/>
+      <c r="K482" s="5" t="n"/>
+      <c r="L482" s="5" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="5" t="n"/>
+      <c r="B483" s="5" t="n"/>
+      <c r="C483" s="5" t="n"/>
+      <c r="D483" s="5" t="n"/>
+      <c r="E483" s="5" t="n"/>
+      <c r="F483" s="5" t="n"/>
+      <c r="G483" s="5" t="n"/>
+      <c r="H483" s="5" t="n"/>
+      <c r="I483" s="5" t="n"/>
+      <c r="J483" s="6" t="n"/>
+      <c r="K483" s="5" t="n"/>
+      <c r="L483" s="5" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="5" t="n"/>
+      <c r="B484" s="5" t="n"/>
+      <c r="C484" s="5" t="n"/>
+      <c r="D484" s="5" t="n"/>
+      <c r="E484" s="5" t="n"/>
+      <c r="F484" s="5" t="n"/>
+      <c r="G484" s="5" t="n"/>
+      <c r="H484" s="5" t="n"/>
+      <c r="I484" s="5" t="n"/>
+      <c r="J484" s="6" t="n"/>
+      <c r="K484" s="5" t="n"/>
+      <c r="L484" s="5" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="5" t="n"/>
+      <c r="B485" s="5" t="n"/>
+      <c r="C485" s="5" t="n"/>
+      <c r="D485" s="5" t="n"/>
+      <c r="E485" s="5" t="n"/>
+      <c r="F485" s="5" t="n"/>
+      <c r="G485" s="5" t="n"/>
+      <c r="H485" s="5" t="n"/>
+      <c r="I485" s="5" t="n"/>
+      <c r="J485" s="6" t="n"/>
+      <c r="K485" s="5" t="n"/>
+      <c r="L485" s="5" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="5" t="n"/>
+      <c r="B486" s="5" t="n"/>
+      <c r="C486" s="5" t="n"/>
+      <c r="D486" s="5" t="n"/>
+      <c r="E486" s="5" t="n"/>
+      <c r="F486" s="5" t="n"/>
+      <c r="G486" s="5" t="n"/>
+      <c r="H486" s="5" t="n"/>
+      <c r="I486" s="5" t="n"/>
+      <c r="J486" s="6" t="n"/>
+      <c r="K486" s="5" t="n"/>
+      <c r="L486" s="5" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="n"/>
+      <c r="B487" s="5" t="n"/>
+      <c r="C487" s="5" t="n"/>
+      <c r="D487" s="5" t="n"/>
+      <c r="E487" s="5" t="n"/>
+      <c r="F487" s="5" t="n"/>
+      <c r="G487" s="5" t="n"/>
+      <c r="H487" s="5" t="n"/>
+      <c r="I487" s="5" t="n"/>
+      <c r="J487" s="6" t="n"/>
+      <c r="K487" s="5" t="n"/>
+      <c r="L487" s="5" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="5" t="n"/>
+      <c r="B488" s="5" t="n"/>
+      <c r="C488" s="5" t="n"/>
+      <c r="D488" s="5" t="n"/>
+      <c r="E488" s="5" t="n"/>
+      <c r="F488" s="5" t="n"/>
+      <c r="G488" s="5" t="n"/>
+      <c r="H488" s="5" t="n"/>
+      <c r="I488" s="5" t="n"/>
+      <c r="J488" s="6" t="n"/>
+      <c r="K488" s="5" t="n"/>
+      <c r="L488" s="5" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="5" t="n"/>
+      <c r="B489" s="5" t="n"/>
+      <c r="C489" s="5" t="n"/>
+      <c r="D489" s="5" t="n"/>
+      <c r="E489" s="5" t="n"/>
+      <c r="F489" s="5" t="n"/>
+      <c r="G489" s="5" t="n"/>
+      <c r="H489" s="5" t="n"/>
+      <c r="I489" s="5" t="n"/>
+      <c r="J489" s="6" t="n"/>
+      <c r="K489" s="5" t="n"/>
+      <c r="L489" s="5" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="5" t="n"/>
+      <c r="B490" s="5" t="n"/>
+      <c r="C490" s="5" t="n"/>
+      <c r="D490" s="5" t="n"/>
+      <c r="E490" s="5" t="n"/>
+      <c r="F490" s="5" t="n"/>
+      <c r="G490" s="5" t="n"/>
+      <c r="H490" s="5" t="n"/>
+      <c r="I490" s="5" t="n"/>
+      <c r="J490" s="6" t="n"/>
+      <c r="K490" s="5" t="n"/>
+      <c r="L490" s="5" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="5" t="n"/>
+      <c r="B491" s="5" t="n"/>
+      <c r="C491" s="5" t="n"/>
+      <c r="D491" s="5" t="n"/>
+      <c r="E491" s="5" t="n"/>
+      <c r="F491" s="5" t="n"/>
+      <c r="G491" s="5" t="n"/>
+      <c r="H491" s="5" t="n"/>
+      <c r="I491" s="5" t="n"/>
+      <c r="J491" s="6" t="n"/>
+      <c r="K491" s="5" t="n"/>
+      <c r="L491" s="5" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="5" t="n"/>
+      <c r="B492" s="5" t="n"/>
+      <c r="C492" s="5" t="n"/>
+      <c r="D492" s="5" t="n"/>
+      <c r="E492" s="5" t="n"/>
+      <c r="F492" s="5" t="n"/>
+      <c r="G492" s="5" t="n"/>
+      <c r="H492" s="5" t="n"/>
+      <c r="I492" s="5" t="n"/>
+      <c r="J492" s="6" t="n"/>
+      <c r="K492" s="5" t="n"/>
+      <c r="L492" s="5" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="5" t="n"/>
+      <c r="B493" s="5" t="n"/>
+      <c r="C493" s="5" t="n"/>
+      <c r="D493" s="5" t="n"/>
+      <c r="E493" s="5" t="n"/>
+      <c r="F493" s="5" t="n"/>
+      <c r="G493" s="5" t="n"/>
+      <c r="H493" s="5" t="n"/>
+      <c r="I493" s="5" t="n"/>
+      <c r="J493" s="6" t="n"/>
+      <c r="K493" s="5" t="n"/>
+      <c r="L493" s="5" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="5" t="n"/>
+      <c r="B494" s="5" t="n"/>
+      <c r="C494" s="5" t="n"/>
+      <c r="D494" s="5" t="n"/>
+      <c r="E494" s="5" t="n"/>
+      <c r="F494" s="5" t="n"/>
+      <c r="G494" s="5" t="n"/>
+      <c r="H494" s="5" t="n"/>
+      <c r="I494" s="5" t="n"/>
+      <c r="J494" s="6" t="n"/>
+      <c r="K494" s="5" t="n"/>
+      <c r="L494" s="5" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="5" t="n"/>
+      <c r="B495" s="5" t="n"/>
+      <c r="C495" s="5" t="n"/>
+      <c r="D495" s="5" t="n"/>
+      <c r="E495" s="5" t="n"/>
+      <c r="F495" s="5" t="n"/>
+      <c r="G495" s="5" t="n"/>
+      <c r="H495" s="5" t="n"/>
+      <c r="I495" s="5" t="n"/>
+      <c r="J495" s="6" t="n"/>
+      <c r="K495" s="5" t="n"/>
+      <c r="L495" s="5" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="5" t="n"/>
+      <c r="B496" s="5" t="n"/>
+      <c r="C496" s="5" t="n"/>
+      <c r="D496" s="5" t="n"/>
+      <c r="E496" s="5" t="n"/>
+      <c r="F496" s="5" t="n"/>
+      <c r="G496" s="5" t="n"/>
+      <c r="H496" s="5" t="n"/>
+      <c r="I496" s="5" t="n"/>
+      <c r="J496" s="6" t="n"/>
+      <c r="K496" s="5" t="n"/>
+      <c r="L496" s="5" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="5" t="n"/>
+      <c r="B497" s="5" t="n"/>
+      <c r="C497" s="5" t="n"/>
+      <c r="D497" s="5" t="n"/>
+      <c r="E497" s="5" t="n"/>
+      <c r="F497" s="5" t="n"/>
+      <c r="G497" s="5" t="n"/>
+      <c r="H497" s="5" t="n"/>
+      <c r="I497" s="5" t="n"/>
+      <c r="J497" s="6" t="n"/>
+      <c r="K497" s="5" t="n"/>
+      <c r="L497" s="5" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="5" t="n"/>
+      <c r="B498" s="5" t="n"/>
+      <c r="C498" s="5" t="n"/>
+      <c r="D498" s="5" t="n"/>
+      <c r="E498" s="5" t="n"/>
+      <c r="F498" s="5" t="n"/>
+      <c r="G498" s="5" t="n"/>
+      <c r="H498" s="5" t="n"/>
+      <c r="I498" s="5" t="n"/>
+      <c r="J498" s="6" t="n"/>
+      <c r="K498" s="5" t="n"/>
+      <c r="L498" s="5" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="5" t="n"/>
+      <c r="B499" s="5" t="n"/>
+      <c r="C499" s="5" t="n"/>
+      <c r="D499" s="5" t="n"/>
+      <c r="E499" s="5" t="n"/>
+      <c r="F499" s="5" t="n"/>
+      <c r="G499" s="5" t="n"/>
+      <c r="H499" s="5" t="n"/>
+      <c r="I499" s="5" t="n"/>
+      <c r="J499" s="6" t="n"/>
+      <c r="K499" s="5" t="n"/>
+      <c r="L499" s="5" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="5" t="n"/>
+      <c r="B500" s="5" t="n"/>
+      <c r="C500" s="5" t="n"/>
+      <c r="D500" s="5" t="n"/>
+      <c r="E500" s="5" t="n"/>
+      <c r="F500" s="5" t="n"/>
+      <c r="G500" s="5" t="n"/>
+      <c r="H500" s="5" t="n"/>
+      <c r="I500" s="5" t="n"/>
+      <c r="J500" s="6" t="n"/>
+      <c r="K500" s="5" t="n"/>
+      <c r="L500" s="5" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -772,13 +772,11 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H4" s="5">
         <f>IF(G4="","",TODAY()-G4)</f>
@@ -786,11 +784,11 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -849,13 +847,11 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H5" s="5">
         <f>IF(G5="","",TODAY()-G5)</f>
@@ -863,11 +859,11 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -926,13 +922,11 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H6" s="5">
         <f>IF(G6="","",TODAY()-G6)</f>
@@ -940,11 +934,11 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -1003,13 +997,11 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H7" s="5">
         <f>IF(G7="","",TODAY()-G7)</f>
@@ -1017,11 +1009,11 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1159,13 +1151,11 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H9" s="5">
         <f>IF(G9="","",TODAY()-G9)</f>
@@ -1173,11 +1163,11 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1311,13 +1301,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H11" s="5">
         <f>IF(G11="","",TODAY()-G11)</f>
@@ -1325,11 +1313,11 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1388,13 +1376,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H12" s="5">
         <f>IF(G12="","",TODAY()-G12)</f>
@@ -1402,11 +1388,11 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1544,13 +1530,11 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H14" s="5">
         <f>IF(G14="","",TODAY()-G14)</f>
@@ -1558,11 +1542,11 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1621,13 +1605,11 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H15" s="5">
         <f>IF(G15="","",TODAY()-G15)</f>
@@ -1635,11 +1617,11 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -2006,13 +1988,11 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H20" s="5">
         <f>IF(G20="","",TODAY()-G20)</f>
@@ -2020,11 +2000,11 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -2160,13 +2140,11 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H22" s="5">
         <f>IF(G22="","",TODAY()-G22)</f>
@@ -2174,11 +2152,11 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -2525,13 +2503,11 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+          <t>Follow-up 1 Sent</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>46253</v>
       </c>
       <c r="H27" s="5">
         <f>IF(G27="","",TODAY()-G27)</f>
@@ -2539,11 +2515,11 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2602,11 +2578,11 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H28" s="5">
         <f>IF(G28="","",TODAY()-G28)</f>
@@ -2614,11 +2590,11 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2677,11 +2653,11 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H29" s="5">
         <f>IF(G29="","",TODAY()-G29)</f>
@@ -2689,11 +2665,11 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -2752,11 +2728,11 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H30" s="5">
         <f>IF(G30="","",TODAY()-G30)</f>
@@ -2764,11 +2740,11 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2827,11 +2803,11 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H31" s="5">
         <f>IF(G31="","",TODAY()-G31)</f>
@@ -2839,11 +2815,11 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2979,11 +2955,11 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H33" s="5">
         <f>IF(G33="","",TODAY()-G33)</f>
@@ -2991,11 +2967,11 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -3054,11 +3030,11 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H34" s="5">
         <f>IF(G34="","",TODAY()-G34)</f>
@@ -3066,11 +3042,11 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -3129,11 +3105,11 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H35" s="5">
         <f>IF(G35="","",TODAY()-G35)</f>
@@ -3141,11 +3117,11 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
@@ -3204,11 +3180,11 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H36" s="5">
         <f>IF(G36="","",TODAY()-G36)</f>
@@ -3216,11 +3192,11 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -3279,11 +3255,11 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H37" s="5">
         <f>IF(G37="","",TODAY()-G37)</f>
@@ -3291,11 +3267,11 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -3354,11 +3330,11 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H38" s="5">
         <f>IF(G38="","",TODAY()-G38)</f>
@@ -3366,11 +3342,11 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -3429,11 +3405,11 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H39" s="5">
         <f>IF(G39="","",TODAY()-G39)</f>
@@ -3441,11 +3417,11 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
@@ -3504,11 +3480,11 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H40" s="5">
         <f>IF(G40="","",TODAY()-G40)</f>
@@ -3516,11 +3492,11 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3579,11 +3555,11 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H41" s="5">
         <f>IF(G41="","",TODAY()-G41)</f>
@@ -3591,11 +3567,11 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -3731,11 +3707,11 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H43" s="5">
         <f>IF(G43="","",TODAY()-G43)</f>
@@ -3743,11 +3719,11 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3883,11 +3859,11 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H45" s="5">
         <f>IF(G45="","",TODAY()-G45)</f>
@@ -3895,11 +3871,11 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -3958,11 +3934,11 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H46" s="5">
         <f>IF(G46="","",TODAY()-G46)</f>
@@ -3970,11 +3946,11 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -4033,11 +4009,11 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H47" s="5">
         <f>IF(G47="","",TODAY()-G47)</f>
@@ -4045,11 +4021,11 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -4254,11 +4230,11 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H50" s="5">
         <f>IF(G50="","",TODAY()-G50)</f>
@@ -4266,11 +4242,11 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -4329,11 +4305,11 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H51" s="5">
         <f>IF(G51="","",TODAY()-G51)</f>
@@ -4341,11 +4317,11 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -4404,11 +4380,11 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H52" s="5">
         <f>IF(G52="","",TODAY()-G52)</f>
@@ -4416,11 +4392,11 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -4479,11 +4455,11 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H53" s="5">
         <f>IF(G53="","",TODAY()-G53)</f>
@@ -4491,11 +4467,11 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -4554,11 +4530,11 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H54" s="5">
         <f>IF(G54="","",TODAY()-G54)</f>
@@ -4566,11 +4542,11 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -4629,11 +4605,11 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H55" s="5">
         <f>IF(G55="","",TODAY()-G55)</f>
@@ -4641,11 +4617,11 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
@@ -4704,11 +4680,11 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H56" s="5">
         <f>IF(G56="","",TODAY()-G56)</f>
@@ -4716,11 +4692,11 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -4779,11 +4755,11 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H57" s="5">
         <f>IF(G57="","",TODAY()-G57)</f>
@@ -4791,11 +4767,11 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4854,11 +4830,11 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H58" s="5">
         <f>IF(G58="","",TODAY()-G58)</f>
@@ -4866,11 +4842,11 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
@@ -4929,11 +4905,11 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="H59" s="5">
         <f>IF(G59="","",TODAY()-G59)</f>
@@ -4941,11 +4917,11 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -772,11 +772,11 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H4" s="5">
         <f>IF(G4="","",TODAY()-G4)</f>
@@ -784,11 +784,11 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -847,11 +847,11 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H5" s="5">
         <f>IF(G5="","",TODAY()-G5)</f>
@@ -859,11 +859,11 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H6" s="5">
         <f>IF(G6="","",TODAY()-G6)</f>
@@ -934,11 +934,11 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -997,11 +997,11 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H7" s="5">
         <f>IF(G7="","",TODAY()-G7)</f>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H9" s="5">
         <f>IF(G9="","",TODAY()-G9)</f>
@@ -1163,11 +1163,11 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H11" s="5">
         <f>IF(G11="","",TODAY()-G11)</f>
@@ -1313,11 +1313,11 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1376,11 +1376,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H12" s="5">
         <f>IF(G12="","",TODAY()-G12)</f>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1530,11 +1530,11 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H14" s="5">
         <f>IF(G14="","",TODAY()-G14)</f>
@@ -1542,11 +1542,11 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1605,11 +1605,11 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H15" s="5">
         <f>IF(G15="","",TODAY()-G15)</f>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1988,11 +1988,11 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H20" s="5">
         <f>IF(G20="","",TODAY()-G20)</f>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -2140,11 +2140,11 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H22" s="5">
         <f>IF(G22="","",TODAY()-G22)</f>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -2503,11 +2503,11 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H27" s="5">
         <f>IF(G27="","",TODAY()-G27)</f>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2578,11 +2578,11 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H28" s="5">
         <f>IF(G28="","",TODAY()-G28)</f>
@@ -2590,11 +2590,11 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H29" s="5">
         <f>IF(G29="","",TODAY()-G29)</f>
@@ -2665,11 +2665,11 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -2728,11 +2728,11 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H30" s="5">
         <f>IF(G30="","",TODAY()-G30)</f>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H31" s="5">
         <f>IF(G31="","",TODAY()-G31)</f>
@@ -2815,11 +2815,11 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H33" s="5">
         <f>IF(G33="","",TODAY()-G33)</f>
@@ -2967,11 +2967,11 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -3030,11 +3030,11 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H34" s="5">
         <f>IF(G34="","",TODAY()-G34)</f>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -3105,11 +3105,11 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H35" s="5">
         <f>IF(G35="","",TODAY()-G35)</f>
@@ -3117,11 +3117,11 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
@@ -3180,11 +3180,11 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H36" s="5">
         <f>IF(G36="","",TODAY()-G36)</f>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -3255,11 +3255,11 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H37" s="5">
         <f>IF(G37="","",TODAY()-G37)</f>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -3330,11 +3330,11 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H38" s="5">
         <f>IF(G38="","",TODAY()-G38)</f>
@@ -3342,11 +3342,11 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -3405,11 +3405,11 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H39" s="5">
         <f>IF(G39="","",TODAY()-G39)</f>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H40" s="5">
         <f>IF(G40="","",TODAY()-G40)</f>
@@ -3492,11 +3492,11 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H41" s="5">
         <f>IF(G41="","",TODAY()-G41)</f>
@@ -3567,11 +3567,11 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -3707,11 +3707,11 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H43" s="5">
         <f>IF(G43="","",TODAY()-G43)</f>
@@ -3719,11 +3719,11 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H45" s="5">
         <f>IF(G45="","",TODAY()-G45)</f>
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -3934,11 +3934,11 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H46" s="5">
         <f>IF(G46="","",TODAY()-G46)</f>
@@ -3946,11 +3946,11 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -4009,11 +4009,11 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H47" s="5">
         <f>IF(G47="","",TODAY()-G47)</f>
@@ -4021,11 +4021,11 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -4230,11 +4230,11 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H50" s="5">
         <f>IF(G50="","",TODAY()-G50)</f>
@@ -4242,11 +4242,11 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -4305,11 +4305,11 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H51" s="5">
         <f>IF(G51="","",TODAY()-G51)</f>
@@ -4317,11 +4317,11 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -4380,11 +4380,11 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H52" s="5">
         <f>IF(G52="","",TODAY()-G52)</f>
@@ -4392,11 +4392,11 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -4455,11 +4455,11 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H53" s="5">
         <f>IF(G53="","",TODAY()-G53)</f>
@@ -4467,11 +4467,11 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -4530,11 +4530,11 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H54" s="5">
         <f>IF(G54="","",TODAY()-G54)</f>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H55" s="5">
         <f>IF(G55="","",TODAY()-G55)</f>
@@ -4617,11 +4617,11 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
@@ -4680,11 +4680,11 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H56" s="5">
         <f>IF(G56="","",TODAY()-G56)</f>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H57" s="5">
         <f>IF(G57="","",TODAY()-G57)</f>
@@ -4767,11 +4767,11 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4830,11 +4830,11 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H58" s="5">
         <f>IF(G58="","",TODAY()-G58)</f>
@@ -4842,11 +4842,11 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
@@ -4905,11 +4905,11 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="H59" s="5">
         <f>IF(G59="","",TODAY()-G59)</f>
@@ -4917,11 +4917,11 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8213,7 +8213,7 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"India,Gulf (UAE),Southeast Asia,United Kingdom,Europe,Other,Unknown"</formula1>
+      <formula1>"India,Singapore,United Kingdom,Gulf (UAE),Europe,Other,Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -772,11 +772,11 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H4" s="5">
         <f>IF(G4="","",TODAY()-G4)</f>
@@ -784,11 +784,11 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -847,11 +847,11 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H5" s="5">
         <f>IF(G5="","",TODAY()-G5)</f>
@@ -859,11 +859,11 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H6" s="5">
         <f>IF(G6="","",TODAY()-G6)</f>
@@ -934,11 +934,11 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -997,11 +997,11 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H7" s="5">
         <f>IF(G7="","",TODAY()-G7)</f>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H9" s="5">
         <f>IF(G9="","",TODAY()-G9)</f>
@@ -1163,11 +1163,11 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H11" s="5">
         <f>IF(G11="","",TODAY()-G11)</f>
@@ -1313,11 +1313,11 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1376,11 +1376,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H12" s="5">
         <f>IF(G12="","",TODAY()-G12)</f>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1530,11 +1530,11 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H14" s="5">
         <f>IF(G14="","",TODAY()-G14)</f>
@@ -1542,11 +1542,11 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1605,11 +1605,11 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H15" s="5">
         <f>IF(G15="","",TODAY()-G15)</f>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1988,11 +1988,11 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H20" s="5">
         <f>IF(G20="","",TODAY()-G20)</f>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -2140,11 +2140,11 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H22" s="5">
         <f>IF(G22="","",TODAY()-G22)</f>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -2503,11 +2503,11 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H27" s="5">
         <f>IF(G27="","",TODAY()-G27)</f>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2578,11 +2578,11 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H28" s="5">
         <f>IF(G28="","",TODAY()-G28)</f>
@@ -2590,11 +2590,11 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H29" s="5">
         <f>IF(G29="","",TODAY()-G29)</f>
@@ -2665,11 +2665,11 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -2728,11 +2728,11 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H30" s="5">
         <f>IF(G30="","",TODAY()-G30)</f>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H31" s="5">
         <f>IF(G31="","",TODAY()-G31)</f>
@@ -2815,11 +2815,11 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H33" s="5">
         <f>IF(G33="","",TODAY()-G33)</f>
@@ -2967,11 +2967,11 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -3030,11 +3030,11 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H34" s="5">
         <f>IF(G34="","",TODAY()-G34)</f>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -3105,11 +3105,11 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H35" s="5">
         <f>IF(G35="","",TODAY()-G35)</f>
@@ -3117,11 +3117,11 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
@@ -3180,11 +3180,11 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H36" s="5">
         <f>IF(G36="","",TODAY()-G36)</f>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -3255,11 +3255,11 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H37" s="5">
         <f>IF(G37="","",TODAY()-G37)</f>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -3330,11 +3330,11 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H38" s="5">
         <f>IF(G38="","",TODAY()-G38)</f>
@@ -3342,11 +3342,11 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -3405,11 +3405,11 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H39" s="5">
         <f>IF(G39="","",TODAY()-G39)</f>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H40" s="5">
         <f>IF(G40="","",TODAY()-G40)</f>
@@ -3492,11 +3492,11 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H41" s="5">
         <f>IF(G41="","",TODAY()-G41)</f>
@@ -3567,11 +3567,11 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -3707,11 +3707,11 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H43" s="5">
         <f>IF(G43="","",TODAY()-G43)</f>
@@ -3719,11 +3719,11 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H45" s="5">
         <f>IF(G45="","",TODAY()-G45)</f>
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -3934,11 +3934,11 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H46" s="5">
         <f>IF(G46="","",TODAY()-G46)</f>
@@ -3946,11 +3946,11 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -4009,11 +4009,11 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H47" s="5">
         <f>IF(G47="","",TODAY()-G47)</f>
@@ -4021,11 +4021,11 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -4230,11 +4230,11 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H50" s="5">
         <f>IF(G50="","",TODAY()-G50)</f>
@@ -4242,11 +4242,11 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -4305,11 +4305,11 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H51" s="5">
         <f>IF(G51="","",TODAY()-G51)</f>
@@ -4317,11 +4317,11 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -4380,11 +4380,11 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H52" s="5">
         <f>IF(G52="","",TODAY()-G52)</f>
@@ -4392,11 +4392,11 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -4455,11 +4455,11 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H53" s="5">
         <f>IF(G53="","",TODAY()-G53)</f>
@@ -4467,11 +4467,11 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -4530,11 +4530,11 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H54" s="5">
         <f>IF(G54="","",TODAY()-G54)</f>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H55" s="5">
         <f>IF(G55="","",TODAY()-G55)</f>
@@ -4617,11 +4617,11 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
@@ -4680,11 +4680,11 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H56" s="5">
         <f>IF(G56="","",TODAY()-G56)</f>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H57" s="5">
         <f>IF(G57="","",TODAY()-G57)</f>
@@ -4767,11 +4767,11 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4830,11 +4830,11 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H58" s="5">
         <f>IF(G58="","",TODAY()-G58)</f>
@@ -4842,11 +4842,11 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
@@ -4905,11 +4905,11 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H59" s="5">
         <f>IF(G59="","",TODAY()-G59)</f>
@@ -4917,11 +4917,11 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -772,11 +772,11 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H4" s="5">
         <f>IF(G4="","",TODAY()-G4)</f>
@@ -784,12 +784,10 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -815,7 +813,7 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -847,11 +845,11 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H5" s="5">
         <f>IF(G5="","",TODAY()-G5)</f>
@@ -859,12 +857,10 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -890,7 +886,7 @@
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -922,11 +918,11 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H6" s="5">
         <f>IF(G6="","",TODAY()-G6)</f>
@@ -934,12 +930,10 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -965,7 +959,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -997,11 +991,11 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H7" s="5">
         <f>IF(G7="","",TODAY()-G7)</f>
@@ -1009,12 +1003,10 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1040,7 +1032,7 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1143,11 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H9" s="5">
         <f>IF(G9="","",TODAY()-G9)</f>
@@ -1163,12 +1155,10 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1194,7 +1184,7 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1301,11 +1291,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H11" s="5">
         <f>IF(G11="","",TODAY()-G11)</f>
@@ -1313,12 +1303,10 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1344,7 +1332,7 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1376,11 +1364,11 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H12" s="5">
         <f>IF(G12="","",TODAY()-G12)</f>
@@ -1388,12 +1376,10 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1419,7 +1405,7 @@
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1530,11 +1516,11 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H14" s="5">
         <f>IF(G14="","",TODAY()-G14)</f>
@@ -1542,12 +1528,10 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1573,7 +1557,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1605,11 +1589,11 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H15" s="5">
         <f>IF(G15="","",TODAY()-G15)</f>
@@ -1617,12 +1601,10 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1648,7 +1630,7 @@
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -1988,11 +1970,11 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H20" s="5">
         <f>IF(G20="","",TODAY()-G20)</f>
@@ -2000,12 +1982,10 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2031,7 +2011,7 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2140,11 +2120,11 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H22" s="5">
         <f>IF(G22="","",TODAY()-G22)</f>
@@ -2152,12 +2132,10 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2183,7 +2161,7 @@
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2503,11 +2481,11 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H27" s="5">
         <f>IF(G27="","",TODAY()-G27)</f>
@@ -2515,12 +2493,10 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="n"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2546,7 +2522,7 @@
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context).</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2578,11 +2554,11 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H28" s="5">
         <f>IF(G28="","",TODAY()-G28)</f>
@@ -2590,12 +2566,10 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2621,7 +2595,7 @@
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix</t>
+          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2653,11 +2627,11 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H29" s="5">
         <f>IF(G29="","",TODAY()-G29)</f>
@@ -2665,12 +2639,10 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2696,7 +2668,7 @@
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Solutions Consultant role at ORO Labs</t>
+          <t>Hook: Saw your Solutions Consultant role at ORO Labs 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2728,11 +2700,11 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H30" s="5">
         <f>IF(G30="","",TODAY()-G30)</f>
@@ -2740,12 +2712,10 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2771,7 +2741,7 @@
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems</t>
+          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2803,11 +2773,11 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H31" s="5">
         <f>IF(G31="","",TODAY()-G31)</f>
@@ -2815,12 +2785,10 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2846,7 +2814,7 @@
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -2955,11 +2923,11 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H33" s="5">
         <f>IF(G33="","",TODAY()-G33)</f>
@@ -2967,12 +2935,10 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -2998,7 +2964,7 @@
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3030,11 +2996,11 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H34" s="5">
         <f>IF(G34="","",TODAY()-G34)</f>
@@ -3042,12 +3008,10 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3073,7 +3037,7 @@
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense</t>
+          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3105,11 +3069,11 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H35" s="5">
         <f>IF(G35="","",TODAY()-G35)</f>
@@ -3117,12 +3081,10 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3148,7 +3110,7 @@
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3180,11 +3142,11 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H36" s="5">
         <f>IF(G36="","",TODAY()-G36)</f>
@@ -3192,12 +3154,10 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3223,7 +3183,7 @@
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly</t>
+          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3255,11 +3215,11 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H37" s="5">
         <f>IF(G37="","",TODAY()-G37)</f>
@@ -3267,12 +3227,10 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3298,7 +3256,7 @@
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3330,11 +3288,11 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H38" s="5">
         <f>IF(G38="","",TODAY()-G38)</f>
@@ -3342,12 +3300,10 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3373,7 +3329,7 @@
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited</t>
+          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3405,11 +3361,11 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H39" s="5">
         <f>IF(G39="","",TODAY()-G39)</f>
@@ -3417,12 +3373,10 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3448,7 +3402,7 @@
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3480,11 +3434,11 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H40" s="5">
         <f>IF(G40="","",TODAY()-G40)</f>
@@ -3492,12 +3446,10 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3523,7 +3475,7 @@
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Consultant Manager role at V-Valley</t>
+          <t>Hook: Saw your Presales Consultant Manager role at V-Valley 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3555,11 +3507,11 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H41" s="5">
         <f>IF(G41="","",TODAY()-G41)</f>
@@ -3567,12 +3519,10 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3598,7 +3548,7 @@
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost</t>
+          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3707,11 +3657,11 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H43" s="5">
         <f>IF(G43="","",TODAY()-G43)</f>
@@ -3719,12 +3669,10 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3750,7 +3698,7 @@
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd.</t>
+          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd. 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3859,11 +3807,11 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H45" s="5">
         <f>IF(G45="","",TODAY()-G45)</f>
@@ -3871,12 +3819,10 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n"/>
       <c r="K45" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3902,7 +3848,7 @@
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Commercial Account Manager role at Boomi</t>
+          <t>Hook: Saw your Commercial Account Manager role at Boomi 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -3934,11 +3880,11 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H46" s="5">
         <f>IF(G46="","",TODAY()-G46)</f>
@@ -3946,12 +3892,10 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3977,7 +3921,7 @@
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4009,11 +3953,11 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H47" s="5">
         <f>IF(G47="","",TODAY()-G47)</f>
@@ -4021,12 +3965,10 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4052,7 +3994,7 @@
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo</t>
+          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4172,11 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H50" s="5">
         <f>IF(G50="","",TODAY()-G50)</f>
@@ -4242,12 +4184,10 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4273,7 +4213,7 @@
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager | Account Executive role at kununu</t>
+          <t>Hook: Saw your Sales Manager | Account Executive role at kununu 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4305,11 +4245,11 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H51" s="5">
         <f>IF(G51="","",TODAY()-G51)</f>
@@ -4317,12 +4257,10 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4348,7 +4286,7 @@
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager role at Dyad</t>
+          <t>Hook: Saw your Sales Manager role at Dyad 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4380,11 +4318,11 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H52" s="5">
         <f>IF(G52="","",TODAY()-G52)</f>
@@ -4392,12 +4330,10 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="n"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4423,7 +4359,7 @@
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack</t>
+          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4455,11 +4391,11 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H53" s="5">
         <f>IF(G53="","",TODAY()-G53)</f>
@@ -4467,12 +4403,10 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n"/>
       <c r="K53" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4498,7 +4432,7 @@
       </c>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4530,11 +4464,11 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H54" s="5">
         <f>IF(G54="","",TODAY()-G54)</f>
@@ -4542,12 +4476,10 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4573,7 +4505,7 @@
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4605,11 +4537,11 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H55" s="5">
         <f>IF(G55="","",TODAY()-G55)</f>
@@ -4617,12 +4549,10 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4648,7 +4578,7 @@
       </c>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs</t>
+          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4680,11 +4610,11 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H56" s="5">
         <f>IF(G56="","",TODAY()-G56)</f>
@@ -4692,12 +4622,10 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="n"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4723,7 +4651,7 @@
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad</t>
+          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4683,11 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H57" s="5">
         <f>IF(G57="","",TODAY()-G57)</f>
@@ -4767,12 +4695,10 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4798,7 +4724,7 @@
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4830,11 +4756,11 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H58" s="5">
         <f>IF(G58="","",TODAY()-G58)</f>
@@ -4842,12 +4768,10 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="n"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4873,7 +4797,7 @@
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears</t>
+          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4905,11 +4829,11 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H59" s="5">
         <f>IF(G59="","",TODAY()-G59)</f>
@@ -4917,12 +4841,10 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>46262</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4948,7 +4870,7 @@
       </c>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21)</t>
+          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21) 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +117,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8148,7 +8149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8195,70 +8196,77 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. Lead sourcing (Monday only) targets 6 countries: India, United Arab Emirates (Dubai), Malaysia, Singapore, Thailand, and the United Kingdom. It also rotates through 3 audience segments on a 3-week cycle — Segment A: Presales &amp; Sales Professionals, Segment B: Freshers &amp; Early Career (0-2 yrs, any field), Segment C: SDR/BDR &amp; Delivery people breaking in — one segment per Monday, cycling automatically forever based on the ISO week number.</t>
+          <t>5. Lead sourcing (Monday only) targets 3 English-speaking countries as of 2026-08-22: India, Singapore, and the United Kingdom. As of 2026-08-30, sourcing is additionally weighted 90% India / 10% combined Singapore + United Kingdom (e.g. of a ~30-person target, aim for ~27 India and ~3 Singapore+UK; for Segment A, apply this 90/10 split within each sub-group's ~15 target too). It also rotates through 3 audience segments on a 3-week cycle — Segment A: Presales &amp; Sales Professionals, Segment B: Freshers &amp; Early Career (0-2 yrs, any field), Segment C: SDR/BDR &amp; Delivery people breaking in — one segment per Monday, cycling automatically forever based on the ISO week number.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>6. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>6. This team rotates between multiple free-tier Apollo.io accounts (each renews 75 free lead credits/month) since a paid plan hasn't been purchased yet -- whichever account currently has credits gets connected for that run. This is safe by design: duplicate/bounced/opted-out exclusion is always driven by this Tracker sheet (Email + LinkedIn URL match), never by any single Apollo account's own saved-contacts list, so switching accounts never risks a repeat send or a re-added exclusion regardless of which Apollo account sourced or enriched a lead.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
+          <t>7. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8. Region groups each contact by rough timezone (India / Gulf (UAE) / Southeast Asia / United Kingdom / Other / Unknown; "Europe" is a legacy value from before geography was narrowed, no longer assigned to new rows) — kept for your own visibility into what went out where. It does not control send timing.</t>
+          <t>8. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
+          <t>9. Region groups each contact by country (India / Singapore / United Kingdom / Other / Unknown; "Gulf (UAE)" and "Europe" are legacy values from before geography was narrowed, no longer assigned to new rows) -- kept for your own visibility into what went out where. It does not control send timing.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>10. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+          <t>10. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>11. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+          <t>11. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>12. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+          <t>12. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>13. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>13. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>14. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
+          <t>14. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>15. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4876,1200 +4876,3862 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="6" t="n"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Prity Dixit</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>prity.dixit@adidas.com</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prity-dixit</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H60" s="5">
         <f>IF(G60="","",TODAY()-G60)</f>
         <v/>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="5" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L60" s="6" t="n"/>
-      <c r="M60" s="5" t="n"/>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N60" s="6" t="n"/>
-      <c r="O60" s="5" t="n"/>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Jaya Prasad</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>prasad.j@dxc.com</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jaya-prasad-9392812b</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H61" s="5">
         <f>IF(G61="","",TODAY()-G61)</f>
         <v/>
       </c>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="5" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L61" s="6" t="n"/>
-      <c r="M61" s="5" t="n"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N61" s="6" t="n"/>
-      <c r="O61" s="5" t="n"/>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P61" s="6" t="n"/>
-      <c r="Q61" s="5" t="n"/>
-      <c r="R61" s="5" t="n"/>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="6" t="n"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Surochan Patil</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>surochan@zvolv.com</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/surochan-patil</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H62" s="5">
         <f>IF(G62="","",TODAY()-G62)</f>
         <v/>
       </c>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L62" s="6" t="n"/>
-      <c r="M62" s="5" t="n"/>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N62" s="6" t="n"/>
-      <c r="O62" s="5" t="n"/>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P62" s="6" t="n"/>
-      <c r="Q62" s="5" t="n"/>
-      <c r="R62" s="5" t="n"/>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="6" t="n"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Raj Waghela</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>raja.waghela@topsourceworldwide.com</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rajwaghela</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H63" s="5">
         <f>IF(G63="","",TODAY()-G63)</f>
         <v/>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="5" t="n"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L63" s="6" t="n"/>
-      <c r="M63" s="5" t="n"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N63" s="6" t="n"/>
-      <c r="O63" s="5" t="n"/>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P63" s="6" t="n"/>
-      <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="5" t="n"/>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="6" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Vijay Chowdhary</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>vijay.chowdhary@atos.net</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vijay-chowdhary</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H64" s="5">
         <f>IF(G64="","",TODAY()-G64)</f>
         <v/>
       </c>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="5" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L64" s="6" t="n"/>
-      <c r="M64" s="5" t="n"/>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N64" s="6" t="n"/>
-      <c r="O64" s="5" t="n"/>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P64" s="6" t="n"/>
-      <c r="Q64" s="5" t="n"/>
-      <c r="R64" s="5" t="n"/>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="6" t="n"/>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Brenton Thomas</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>brenton.thomas@bt.com</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brenton-salvo-thomas-67078a36</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H65" s="5">
         <f>IF(G65="","",TODAY()-G65)</f>
         <v/>
       </c>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="5" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L65" s="6" t="n"/>
-      <c r="M65" s="5" t="n"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N65" s="6" t="n"/>
-      <c r="O65" s="5" t="n"/>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P65" s="6" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Lily Sudhakar</t>
+        </is>
+      </c>
       <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lily-s-21a8a12a</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="5">
         <f>IF(G66="","",TODAY()-G66)</f>
         <v/>
       </c>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="5" t="n"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L66" s="6" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N66" s="6" t="n"/>
-      <c r="O66" s="5" t="n"/>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P66" s="6" t="n"/>
-      <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="5" t="n"/>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Consultant - Delivery Lead role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="6" t="n"/>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Avadhoot Naik</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>avadhoot.mnaik@tcs.com</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avadhootnaik</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H67" s="5">
         <f>IF(G67="","",TODAY()-G67)</f>
         <v/>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="5" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L67" s="6" t="n"/>
-      <c r="M67" s="5" t="n"/>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N67" s="6" t="n"/>
-      <c r="O67" s="5" t="n"/>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P67" s="6" t="n"/>
-      <c r="Q67" s="5" t="n"/>
-      <c r="R67" s="5" t="n"/>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="6" t="n"/>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Madhulika Kekre</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>madhulika.joshi@tcs.com</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/madhulika-kekre-8716b4b0</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H68" s="5">
         <f>IF(G68="","",TODAY()-G68)</f>
         <v/>
       </c>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="5" t="n"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L68" s="6" t="n"/>
-      <c r="M68" s="5" t="n"/>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N68" s="6" t="n"/>
-      <c r="O68" s="5" t="n"/>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P68" s="6" t="n"/>
-      <c r="Q68" s="5" t="n"/>
-      <c r="R68" s="5" t="n"/>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="6" t="n"/>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Harsh Kumar</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>hk204@ntrs.com</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsh-kumar-009927108</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H69" s="5">
         <f>IF(G69="","",TODAY()-G69)</f>
         <v/>
       </c>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="5" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L69" s="6" t="n"/>
-      <c r="M69" s="5" t="n"/>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N69" s="6" t="n"/>
-      <c r="O69" s="5" t="n"/>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P69" s="6" t="n"/>
-      <c r="Q69" s="5" t="n"/>
-      <c r="R69" s="5" t="n"/>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R69" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="6" t="n"/>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Ashish Hirlekar</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>ashish.hirlekar@capgemini.com</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashish-hirlekar-281aa43</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H70" s="5">
         <f>IF(G70="","",TODAY()-G70)</f>
         <v/>
       </c>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="5" t="n"/>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L70" s="6" t="n"/>
-      <c r="M70" s="5" t="n"/>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N70" s="6" t="n"/>
-      <c r="O70" s="5" t="n"/>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P70" s="6" t="n"/>
-      <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="5" t="n"/>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="6" t="n"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Ankit Sambyal</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>ankit.sambyal@insight.com</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankitsambyal</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H71" s="5">
         <f>IF(G71="","",TODAY()-G71)</f>
         <v/>
       </c>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="5" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L71" s="6" t="n"/>
-      <c r="M71" s="5" t="n"/>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N71" s="6" t="n"/>
-      <c r="O71" s="5" t="n"/>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P71" s="6" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="6" t="n"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Vaishali Srivastava</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>vsrivastava@vallumassociates.com</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vaishali-srivastava-9225a848</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H72" s="5">
         <f>IF(G72="","",TODAY()-G72)</f>
         <v/>
       </c>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="5" t="n"/>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L72" s="6" t="n"/>
-      <c r="M72" s="5" t="n"/>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N72" s="6" t="n"/>
-      <c r="O72" s="5" t="n"/>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P72" s="6" t="n"/>
-      <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="5" t="n"/>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="6" t="n"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Sushil Shende</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>sushil.shende@worldline.com</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sushilshende</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H73" s="5">
         <f>IF(G73="","",TODAY()-G73)</f>
         <v/>
       </c>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="5" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L73" s="6" t="n"/>
-      <c r="M73" s="5" t="n"/>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N73" s="6" t="n"/>
-      <c r="O73" s="5" t="n"/>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P73" s="6" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="6" t="n"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Ayush Das</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>ayush.das@makunaiglobal.ai</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ayush-das-8b9091146</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H74" s="5">
         <f>IF(G74="","",TODAY()-G74)</f>
         <v/>
       </c>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L74" s="6" t="n"/>
-      <c r="M74" s="5" t="n"/>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N74" s="6" t="n"/>
-      <c r="O74" s="5" t="n"/>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P74" s="6" t="n"/>
-      <c r="Q74" s="5" t="n"/>
-      <c r="R74" s="5" t="n"/>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R74" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Business Development Representative (Software Sales) role at Makunai Global | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Arunprabhu K</t>
+        </is>
+      </c>
       <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arunprabhukannian</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G75" s="6" t="n"/>
       <c r="H75" s="5">
         <f>IF(G75="","",TODAY()-G75)</f>
         <v/>
       </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="5" t="n"/>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L75" s="6" t="n"/>
-      <c r="M75" s="5" t="n"/>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N75" s="6" t="n"/>
-      <c r="O75" s="5" t="n"/>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P75" s="6" t="n"/>
-      <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="5" t="n"/>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Account &amp; Delivery Lead role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="6" t="n"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Neha Mahapatra</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>neha.mahapatra@lhh.com</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neha-mahapatra-3ab7b61b0</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H76" s="5">
         <f>IF(G76="","",TODAY()-G76)</f>
         <v/>
       </c>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="5" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L76" s="6" t="n"/>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N76" s="6" t="n"/>
-      <c r="O76" s="5" t="n"/>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P76" s="6" t="n"/>
-      <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="5" t="n"/>
+      <c r="Q76" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R76" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="6" t="n"/>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Mousumi Saha</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>msaha@vallumassociates.com</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mousumi-saha-622603130</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H77" s="5">
         <f>IF(G77="","",TODAY()-G77)</f>
         <v/>
       </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="5" t="n"/>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L77" s="6" t="n"/>
-      <c r="M77" s="5" t="n"/>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N77" s="6" t="n"/>
-      <c r="O77" s="5" t="n"/>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P77" s="6" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Sivaprakash K</t>
+        </is>
+      </c>
       <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sivaprakash-k-0b312a121</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G78" s="6" t="n"/>
       <c r="H78" s="5">
         <f>IF(G78="","",TODAY()-G78)</f>
         <v/>
       </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="5" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L78" s="6" t="n"/>
-      <c r="M78" s="5" t="n"/>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N78" s="6" t="n"/>
-      <c r="O78" s="5" t="n"/>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P78" s="6" t="n"/>
-      <c r="Q78" s="5" t="n"/>
-      <c r="R78" s="5" t="n"/>
+      <c r="Q78" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R78" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery-Lead Consultant role at Virtusa | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="6" t="n"/>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Chandra Mangali</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>chandra_sekhar_mangali@epam.com</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chandra-sekhar-mangali-b88b3331</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H79" s="5">
         <f>IF(G79="","",TODAY()-G79)</f>
         <v/>
       </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="5" t="n"/>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L79" s="6" t="n"/>
-      <c r="M79" s="5" t="n"/>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N79" s="6" t="n"/>
-      <c r="O79" s="5" t="n"/>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P79" s="6" t="n"/>
-      <c r="Q79" s="5" t="n"/>
-      <c r="R79" s="5" t="n"/>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R79" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="6" t="n"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Ashok Rajavel</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>ashok.rajavel@accenture.com</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashok-rajavel-66844318</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H80" s="5">
         <f>IF(G80="","",TODAY()-G80)</f>
         <v/>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="5" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L80" s="6" t="n"/>
-      <c r="M80" s="5" t="n"/>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N80" s="6" t="n"/>
-      <c r="O80" s="5" t="n"/>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P80" s="6" t="n"/>
-      <c r="Q80" s="5" t="n"/>
-      <c r="R80" s="5" t="n"/>
+      <c r="Q80" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R80" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Sumanth Rao</t>
+        </is>
+      </c>
       <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumanth-rao-42b0996</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G81" s="6" t="n"/>
       <c r="H81" s="5">
         <f>IF(G81="","",TODAY()-G81)</f>
         <v/>
       </c>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="5" t="n"/>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L81" s="6" t="n"/>
-      <c r="M81" s="5" t="n"/>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N81" s="6" t="n"/>
-      <c r="O81" s="5" t="n"/>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P81" s="6" t="n"/>
-      <c r="Q81" s="5" t="n"/>
-      <c r="R81" s="5" t="n"/>
+      <c r="Q81" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R81" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sector Delivery Lead role at Wipro | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n"/>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Shahil Kumar</t>
+        </is>
+      </c>
       <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shahil-kumar-a5ab96371</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="5">
         <f>IF(G82="","",TODAY()-G82)</f>
         <v/>
       </c>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="6" t="n"/>
-      <c r="K82" s="5" t="n"/>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L82" s="6" t="n"/>
-      <c r="M82" s="5" t="n"/>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N82" s="6" t="n"/>
-      <c r="O82" s="5" t="n"/>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P82" s="6" t="n"/>
-      <c r="Q82" s="5" t="n"/>
-      <c r="R82" s="5" t="n"/>
+      <c r="Q82" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R82" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Business Development Representative role at Parijat Controlware Inc. | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n"/>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="6" t="n"/>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Prabhu Padhy</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>prabhu.padhy@splashbi.com</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prabhu-prasad-padhy-a2b41739</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H83" s="5">
         <f>IF(G83="","",TODAY()-G83)</f>
         <v/>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="5" t="n"/>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L83" s="6" t="n"/>
-      <c r="M83" s="5" t="n"/>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N83" s="6" t="n"/>
-      <c r="O83" s="5" t="n"/>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P83" s="6" t="n"/>
-      <c r="Q83" s="5" t="n"/>
-      <c r="R83" s="5" t="n"/>
+      <c r="Q83" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R83" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Delivery Consultant role at SplashBI | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Indrani Das</t>
+        </is>
+      </c>
       <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/indrani-das-1621a7108</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G84" s="6" t="n"/>
       <c r="H84" s="5">
         <f>IF(G84="","",TODAY()-G84)</f>
         <v/>
       </c>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="5" t="n"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L84" s="6" t="n"/>
-      <c r="M84" s="5" t="n"/>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N84" s="6" t="n"/>
-      <c r="O84" s="5" t="n"/>
+      <c r="O84" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P84" s="6" t="n"/>
-      <c r="Q84" s="5" t="n"/>
-      <c r="R84" s="5" t="n"/>
+      <c r="Q84" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R84" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Delivery Consultant role at Epsilon | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="6" t="n"/>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Shubhra Agarwal</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>shubhra.agarwal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubhra-agarwal-61837052</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H85" s="5">
         <f>IF(G85="","",TODAY()-G85)</f>
         <v/>
       </c>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="5" t="n"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L85" s="6" t="n"/>
-      <c r="M85" s="5" t="n"/>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N85" s="6" t="n"/>
-      <c r="O85" s="5" t="n"/>
+      <c r="O85" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P85" s="6" t="n"/>
-      <c r="Q85" s="5" t="n"/>
-      <c r="R85" s="5" t="n"/>
+      <c r="Q85" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R85" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Raman Dhingra</t>
+        </is>
+      </c>
       <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raman-dhingra-24b445181</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="5">
         <f>IF(G86="","",TODAY()-G86)</f>
         <v/>
       </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Send LinkedIn Connection Request</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L86" s="6" t="n"/>
-      <c r="M86" s="5" t="n"/>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N86" s="6" t="n"/>
-      <c r="O86" s="5" t="n"/>
+      <c r="O86" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P86" s="6" t="n"/>
-      <c r="Q86" s="5" t="n"/>
-      <c r="R86" s="5" t="n"/>
+      <c r="Q86" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R86" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales Development Representative role at Closeloop Technologies | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="6" t="n"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Omkar Mane</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>omkar.mane@accenture.com</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/omkar-mane-43819558</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H87" s="5">
         <f>IF(G87="","",TODAY()-G87)</f>
         <v/>
       </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="5" t="n"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L87" s="6" t="n"/>
-      <c r="M87" s="5" t="n"/>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N87" s="6" t="n"/>
-      <c r="O87" s="5" t="n"/>
+      <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P87" s="6" t="n"/>
-      <c r="Q87" s="5" t="n"/>
-      <c r="R87" s="5" t="n"/>
+      <c r="Q87" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="6" t="n"/>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Avik Noronha</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>a.ryan.john.noronha@accenture.com</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aviknoronha</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H88" s="5">
         <f>IF(G88="","",TODAY()-G88)</f>
         <v/>
       </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="5" t="n"/>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L88" s="6" t="n"/>
-      <c r="M88" s="5" t="n"/>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N88" s="6" t="n"/>
-      <c r="O88" s="5" t="n"/>
+      <c r="O88" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P88" s="6" t="n"/>
-      <c r="Q88" s="5" t="n"/>
-      <c r="R88" s="5" t="n"/>
+      <c r="Q88" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R88" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="6" t="n"/>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Hinesh Bheda</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>hinesh.bheda@accenture.com</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hineshbheda</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H89" s="5">
         <f>IF(G89="","",TODAY()-G89)</f>
         <v/>
       </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="5" t="n"/>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L89" s="6" t="n"/>
-      <c r="M89" s="5" t="n"/>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N89" s="6" t="n"/>
-      <c r="O89" s="5" t="n"/>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P89" s="6" t="n"/>
-      <c r="Q89" s="5" t="n"/>
-      <c r="R89" s="5" t="n"/>
+      <c r="Q89" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R89" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="6" t="n"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Madhav Prathapa</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>madhav.prathapa@accenture.com</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/madhavprathapa</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H90" s="5">
         <f>IF(G90="","",TODAY()-G90)</f>
         <v/>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="5" t="n"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L90" s="6" t="n"/>
-      <c r="M90" s="5" t="n"/>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N90" s="6" t="n"/>
-      <c r="O90" s="5" t="n"/>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P90" s="6" t="n"/>
-      <c r="Q90" s="5" t="n"/>
-      <c r="R90" s="5" t="n"/>
+      <c r="Q90" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R90" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="6" t="n"/>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Mugdha Patil</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>mugdha.patil@accenture.com</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mugdha-patil-mrics-pmp%c2%ae-mapm-lssgb-71b55759</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H91" s="5">
         <f>IF(G91="","",TODAY()-G91)</f>
         <v/>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="5" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L91" s="6" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N91" s="6" t="n"/>
-      <c r="O91" s="5" t="n"/>
+      <c r="O91" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P91" s="6" t="n"/>
-      <c r="Q91" s="5" t="n"/>
-      <c r="R91" s="5" t="n"/>
+      <c r="Q91" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="6" t="n"/>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Hema Dalwadi</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>hema.dalwadi@accenture.com</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hema-dalwadi-980b3727</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H92" s="5">
         <f>IF(G92="","",TODAY()-G92)</f>
         <v/>
       </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="5" t="n"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L92" s="6" t="n"/>
-      <c r="M92" s="5" t="n"/>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N92" s="6" t="n"/>
-      <c r="O92" s="5" t="n"/>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P92" s="6" t="n"/>
-      <c r="Q92" s="5" t="n"/>
-      <c r="R92" s="5" t="n"/>
+      <c r="Q92" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R92" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="6" t="n"/>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Vaibhav Pareek</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>vaibhav.pareek@accenture.com</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vaibhav-pareek-53988419</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H93" s="5">
         <f>IF(G93="","",TODAY()-G93)</f>
         <v/>
       </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="5" t="n"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L93" s="6" t="n"/>
-      <c r="M93" s="5" t="n"/>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N93" s="6" t="n"/>
-      <c r="O93" s="5" t="n"/>
+      <c r="O93" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P93" s="6" t="n"/>
-      <c r="Q93" s="5" t="n"/>
-      <c r="R93" s="5" t="n"/>
+      <c r="Q93" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R93" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="6" t="n"/>
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Ankit Jaiswal</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>ankit.d.jaiswal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankit-jaiswal-7a16b59b</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H94" s="5">
         <f>IF(G94="","",TODAY()-G94)</f>
         <v/>
       </c>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="5" t="n"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L94" s="6" t="n"/>
-      <c r="M94" s="5" t="n"/>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N94" s="6" t="n"/>
-      <c r="O94" s="5" t="n"/>
+      <c r="O94" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P94" s="6" t="n"/>
-      <c r="Q94" s="5" t="n"/>
-      <c r="R94" s="5" t="n"/>
+      <c r="Q94" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R94" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="6" t="n"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Roopashri Shetty</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>roopashri.c.shetty@accenture.com</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roopashri-shetty</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H95" s="5">
         <f>IF(G95="","",TODAY()-G95)</f>
         <v/>
       </c>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="5" t="n"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L95" s="6" t="n"/>
-      <c r="M95" s="5" t="n"/>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N95" s="6" t="n"/>
-      <c r="O95" s="5" t="n"/>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P95" s="6" t="n"/>
-      <c r="Q95" s="5" t="n"/>
-      <c r="R95" s="5" t="n"/>
+      <c r="Q95" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R95" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="6" t="n"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Ankush Khosla</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>ankush.khosla@accenture.com</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankushkhosla33</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H96" s="5">
         <f>IF(G96="","",TODAY()-G96)</f>
         <v/>
       </c>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="5" t="n"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L96" s="6" t="n"/>
-      <c r="M96" s="5" t="n"/>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N96" s="6" t="n"/>
-      <c r="O96" s="5" t="n"/>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P96" s="6" t="n"/>
-      <c r="Q96" s="5" t="n"/>
-      <c r="R96" s="5" t="n"/>
+      <c r="Q96" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R96" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="6" t="n"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Swapnil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>swapnil.chaudhary@vnvcs.com</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/swapnil-chaudhary-199560250</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H97" s="5">
         <f>IF(G97="","",TODAY()-G97)</f>
         <v/>
       </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="5" t="n"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L97" s="6" t="n"/>
-      <c r="M97" s="5" t="n"/>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N97" s="6" t="n"/>
-      <c r="O97" s="5" t="n"/>
+      <c r="O97" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P97" s="6" t="n"/>
-      <c r="Q97" s="5" t="n"/>
-      <c r="R97" s="5" t="n"/>
+      <c r="Q97" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R97" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="6" t="n"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Manish Gupta</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>m.gupta@accenture.com</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manish-gupta-86459926</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H98" s="5">
         <f>IF(G98="","",TODAY()-G98)</f>
         <v/>
       </c>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="5" t="n"/>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L98" s="6" t="n"/>
-      <c r="M98" s="5" t="n"/>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N98" s="6" t="n"/>
-      <c r="O98" s="5" t="n"/>
+      <c r="O98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P98" s="6" t="n"/>
-      <c r="Q98" s="5" t="n"/>
-      <c r="R98" s="5" t="n"/>
+      <c r="Q98" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R98" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="n"/>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="6" t="n"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Venkades Arjunan</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>venkades.arjunan@accenture.com</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/venkades-arjunan-99a442213</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H99" s="5">
         <f>IF(G99="","",TODAY()-G99)</f>
         <v/>
       </c>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="6" t="n"/>
-      <c r="K99" s="5" t="n"/>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L99" s="6" t="n"/>
-      <c r="M99" s="5" t="n"/>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N99" s="6" t="n"/>
-      <c r="O99" s="5" t="n"/>
+      <c r="O99" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P99" s="6" t="n"/>
-      <c r="Q99" s="5" t="n"/>
-      <c r="R99" s="5" t="n"/>
+      <c r="Q99" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R99" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="6" t="n"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Abhishek Jaiswal</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>abhishek.jaiswal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abhishek-jaiswal-32283565</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H100" s="5">
         <f>IF(G100="","",TODAY()-G100)</f>
         <v/>
       </c>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="5" t="n"/>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L100" s="6" t="n"/>
-      <c r="M100" s="5" t="n"/>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N100" s="6" t="n"/>
-      <c r="O100" s="5" t="n"/>
+      <c r="O100" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P100" s="6" t="n"/>
-      <c r="Q100" s="5" t="n"/>
-      <c r="R100" s="5" t="n"/>
+      <c r="Q100" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R100" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="6" t="n"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Harsha Dediya</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>harsha.dediya@accenture.com</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsha-dediya-854b4294</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H101" s="5">
         <f>IF(G101="","",TODAY()-G101)</f>
         <v/>
       </c>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="5" t="n"/>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L101" s="6" t="n"/>
-      <c r="M101" s="5" t="n"/>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N101" s="6" t="n"/>
-      <c r="O101" s="5" t="n"/>
+      <c r="O101" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P101" s="6" t="n"/>
-      <c r="Q101" s="5" t="n"/>
-      <c r="R101" s="5" t="n"/>
+      <c r="Q101" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R101" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="5" t="n"/>
-      <c r="D102" s="5" t="n"/>
-      <c r="E102" s="5" t="n"/>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="6" t="n"/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Nandish Venkatesh</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>nandish.venkatesh@accenture.com</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nandish-venkatesh-48b93873</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H102" s="5">
         <f>IF(G102="","",TODAY()-G102)</f>
         <v/>
       </c>
-      <c r="I102" s="5" t="n"/>
-      <c r="J102" s="6" t="n"/>
-      <c r="K102" s="5" t="n"/>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L102" s="6" t="n"/>
-      <c r="M102" s="5" t="n"/>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N102" s="6" t="n"/>
-      <c r="O102" s="5" t="n"/>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P102" s="6" t="n"/>
-      <c r="Q102" s="5" t="n"/>
-      <c r="R102" s="5" t="n"/>
+      <c r="Q102" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="6" t="n"/>
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Jagdish Deshmukh</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>jagdish.deshmukh@globant.com</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jagdish-deshmukh-a3783b80</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H103" s="5">
         <f>IF(G103="","",TODAY()-G103)</f>
         <v/>
       </c>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="6" t="n"/>
-      <c r="K103" s="5" t="n"/>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L103" s="6" t="n"/>
-      <c r="M103" s="5" t="n"/>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N103" s="6" t="n"/>
-      <c r="O103" s="5" t="n"/>
+      <c r="O103" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P103" s="6" t="n"/>
-      <c r="Q103" s="5" t="n"/>
-      <c r="R103" s="5" t="n"/>
+      <c r="Q103" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R103" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Consultant - Project role at Globant | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="6" t="n"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>manisha.thapa@accenture.com</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manisha-thapa-659b63105</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H104" s="5">
         <f>IF(G104="","",TODAY()-G104)</f>
         <v/>
       </c>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="6" t="n"/>
-      <c r="K104" s="5" t="n"/>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L104" s="6" t="n"/>
-      <c r="M104" s="5" t="n"/>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N104" s="6" t="n"/>
-      <c r="O104" s="5" t="n"/>
+      <c r="O104" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P104" s="6" t="n"/>
-      <c r="Q104" s="5" t="n"/>
-      <c r="R104" s="5" t="n"/>
+      <c r="Q104" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R104" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="6" t="n"/>
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Yathiraj Moily</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>yathiraj.moily@accenture.com</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yathirajmoily</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H105" s="5">
         <f>IF(G105="","",TODAY()-G105)</f>
         <v/>
       </c>
-      <c r="I105" s="5" t="n"/>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="5" t="n"/>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L105" s="6" t="n"/>
-      <c r="M105" s="5" t="n"/>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N105" s="6" t="n"/>
-      <c r="O105" s="5" t="n"/>
+      <c r="O105" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P105" s="6" t="n"/>
-      <c r="Q105" s="5" t="n"/>
-      <c r="R105" s="5" t="n"/>
+      <c r="Q105" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R105" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="6" t="n"/>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Sudha G</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>sudha.g@accenture.com</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sudha-g-ab4575a8</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H106" s="5">
         <f>IF(G106="","",TODAY()-G106)</f>
         <v/>
       </c>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="5" t="n"/>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L106" s="6" t="n"/>
-      <c r="M106" s="5" t="n"/>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N106" s="6" t="n"/>
-      <c r="O106" s="5" t="n"/>
+      <c r="O106" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P106" s="6" t="n"/>
-      <c r="Q106" s="5" t="n"/>
-      <c r="R106" s="5" t="n"/>
+      <c r="Q106" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R106" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="5" t="n"/>
-      <c r="G107" s="6" t="n"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Saravanan Palani</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>saravanan.palani@accenture.com</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saravanan-palani-72515233</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H107" s="5">
         <f>IF(G107="","",TODAY()-G107)</f>
         <v/>
       </c>
-      <c r="I107" s="5" t="n"/>
-      <c r="J107" s="6" t="n"/>
-      <c r="K107" s="5" t="n"/>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L107" s="6" t="n"/>
-      <c r="M107" s="5" t="n"/>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N107" s="6" t="n"/>
-      <c r="O107" s="5" t="n"/>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P107" s="6" t="n"/>
-      <c r="Q107" s="5" t="n"/>
-      <c r="R107" s="5" t="n"/>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="6" t="n"/>
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Yashvant Patil</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>yashvantmahesh.p@infosys.com</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yashvant-patil-81932771</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H108" s="5">
         <f>IF(G108="","",TODAY()-G108)</f>
         <v/>
       </c>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="6" t="n"/>
-      <c r="K108" s="5" t="n"/>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L108" s="6" t="n"/>
-      <c r="M108" s="5" t="n"/>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N108" s="6" t="n"/>
-      <c r="O108" s="5" t="n"/>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P108" s="6" t="n"/>
-      <c r="Q108" s="5" t="n"/>
-      <c r="R108" s="5" t="n"/>
+      <c r="Q108" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="6" t="n"/>
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Shantelle Morris</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>shantelle.morris@burendo.com</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shantelle-morris-42861853</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H109" s="5">
         <f>IF(G109="","",TODAY()-G109)</f>
         <v/>
       </c>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="5" t="n"/>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L109" s="6" t="n"/>
-      <c r="M109" s="5" t="n"/>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N109" s="6" t="n"/>
-      <c r="O109" s="5" t="n"/>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P109" s="6" t="n"/>
-      <c r="Q109" s="5" t="n"/>
-      <c r="R109" s="5" t="n"/>
+      <c r="Q109" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n"/>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="5" t="n"/>
-      <c r="D110" s="5" t="n"/>
-      <c r="E110" s="5" t="n"/>
-      <c r="F110" s="5" t="n"/>
-      <c r="G110" s="6" t="n"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Ernest Nwadinobi</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>ernest.nwadinobi@tombola.com</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ernest-c-nwadinobi-miet-a2397756</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H110" s="5">
         <f>IF(G110="","",TODAY()-G110)</f>
         <v/>
       </c>
-      <c r="I110" s="5" t="n"/>
-      <c r="J110" s="6" t="n"/>
-      <c r="K110" s="5" t="n"/>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L110" s="6" t="n"/>
-      <c r="M110" s="5" t="n"/>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N110" s="6" t="n"/>
-      <c r="O110" s="5" t="n"/>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P110" s="6" t="n"/>
-      <c r="Q110" s="5" t="n"/>
-      <c r="R110" s="5" t="n"/>
+      <c r="Q110" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n"/>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="6" t="n"/>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Darius Young</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>darius.young@cygnus-systems.com</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/darius-young-5b8372257</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Breaking into Sales or Presales</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>46265</v>
+      </c>
       <c r="H111" s="5">
         <f>IF(G111="","",TODAY()-G111)</f>
         <v/>
       </c>
-      <c r="I111" s="5" t="n"/>
-      <c r="J111" s="6" t="n"/>
-      <c r="K111" s="5" t="n"/>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L111" s="6" t="n"/>
-      <c r="M111" s="5" t="n"/>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N111" s="6" t="n"/>
-      <c r="O111" s="5" t="n"/>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P111" s="6" t="n"/>
-      <c r="Q111" s="5" t="n"/>
-      <c r="R111" s="5" t="n"/>
+      <c r="Q111" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -8149,7 +10811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8196,7 +10858,7 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. Lead sourcing (Monday only) targets 3 English-speaking countries as of 2026-08-22: India, Singapore, and the United Kingdom. As of 2026-08-30, sourcing is additionally weighted 90% India / 10% combined Singapore + United Kingdom (e.g. of a ~30-person target, aim for ~27 India and ~3 Singapore+UK; for Segment A, apply this 90/10 split within each sub-group's ~15 target too). It also rotates through 3 audience segments on a 3-week cycle — Segment A: Presales &amp; Sales Professionals, Segment B: Freshers &amp; Early Career (0-2 yrs, any field), Segment C: SDR/BDR &amp; Delivery people breaking in — one segment per Monday, cycling automatically forever based on the ISO week number.</t>
+          <t>5. Lead sourcing (Monday only) targets 3 English-speaking countries as of 2026-08-22: India, Singapore, and the United Kingdom, weighted 90% India / 10% combined Singapore + United Kingdom as of 2026-08-30. The weekly net-new target was raised from ~30 to ~50 as of 2026-08-31. It also rotates through 3 audience segments on a 3-week cycle — Segment A: Presales &amp; Sales Professionals, Segment B: Freshers &amp; Early Career (0-2 yrs, any field), Segment C: SDR/BDR &amp; Delivery people breaking in — one segment per Monday, cycling automatically forever based on the ISO week number.</t>
         </is>
       </c>
     </row>
@@ -8208,65 +10870,72 @@
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>7. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>7. If the connected Apollo.io account's prospecting/search API is plan-gated (a free trial can show available lead credits while still blocking apollo_agent_find_prospects with an API_INACCESSIBLE error -- this happened 2026-08-31), the fallback is manual sourcing: search Apollo's own web app by hand (its UI search still works on a trial plan even when the API doesn't), export results to a simple Name/Email/LinkedIn URL/Title/Company/Country spreadsheet, and hand it to the assistant to dedup, log to Apollo Archive, add to Tracker, and send from -- same exclusion rules apply regardless of how a candidate was sourced.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
+          <t>8. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. Region groups each contact by country (India / Singapore / United Kingdom / Other / Unknown; "Gulf (UAE)" and "Europe" are legacy values from before geography was narrowed, no longer assigned to new rows) -- kept for your own visibility into what went out where. It does not control send timing.</t>
+          <t>9. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>10. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
+          <t>10. Region groups each contact by country (India / Singapore / United Kingdom / Other / Unknown; "Gulf (UAE)" and "Europe" are legacy values from before geography was narrowed, no longer assigned to new rows) -- kept for your own visibility into what went out where. It does not control send timing.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>11. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+          <t>11. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>12. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+          <t>12. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>13. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+          <t>13. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>14. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>14. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>15. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
+          <t>15. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>16. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
         </is>
       </c>
     </row>
@@ -11397,788 +14066,3128 @@
       <c r="L58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="5" t="n"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Prity Dixit</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>prity.dixit@adidas.com</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prity-dixit</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead/ Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>adidas</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="5" t="n"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Jaya Prasad</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>prasad.j@dxc.com</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jaya-prasad-9392812b</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Manager, Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="5" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Surochan Patil</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>surochan@zvolv.com</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/surochan-patil</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Zvolv</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Raj Waghela</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>raja.waghela@topsourceworldwide.com</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rajwaghela</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Representative - Sales</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>TopSource</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="5" t="n"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Vijay Chowdhary</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>vijay.chowdhary@atos.net</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vijay-chowdhary</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Lead Consultant/Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Atos</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="5" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Brenton Thomas</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>brenton.thomas@bt.com</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brenton-salvo-thomas-67078a36</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Lead Consultant / Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>BT Group</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n"/>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Lily Sudhakar</t>
+        </is>
+      </c>
       <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="5" t="n"/>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lily-s-21a8a12a</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Lead Consultant - Delivery Lead/Manager</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="5" t="n"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Avadhoot Naik</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>avadhoot.mnaik@tcs.com</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avadhootnaik</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Consultant/Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="5" t="n"/>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Madhulika Kekre</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>madhulika.joshi@tcs.com</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/madhulika-kekre-8716b4b0</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Consultant - Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="5" t="n"/>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Harsh Kumar</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>hk204@ntrs.com</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsh-kumar-009927108</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Consultant, Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Northern Trust</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="5" t="n"/>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Ashish Hirlekar</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>ashish.hirlekar@capgemini.com</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashish-hirlekar-281aa43</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Executive | Delivery Manager | Program Manager</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="5" t="n"/>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Ankit Sambyal</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>ankit.sambyal@insight.com</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankitsambyal</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Representative, Enterprise Sales</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="5" t="n"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Vaishali Srivastava</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>vsrivastava@vallumassociates.com</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vaishali-srivastava-9225a848</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Lead Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Vallum Associates</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="5" t="n"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Sushil Shende</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>sushil.shende@worldline.com</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sushilshende</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Consultant Delivery-Lead</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Worldline Global Services</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="5" t="n"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Ayush Das</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>ayush.das@makunaiglobal.ai</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ayush-das-8b9091146</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Representative (Software Sales)</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Makunai Global</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Arunprabhu K</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arunprabhukannian</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Account &amp; Delivery Lead / Senior Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="5" t="n"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Neha Mahapatra</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>neha.mahapatra@lhh.com</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neha-mahapatra-3ab7b61b0</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Lead Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>LHH</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="5" t="n"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Mousumi Saha</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>msaha@vallumassociates.com</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mousumi-saha-622603130</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Lead Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Vallum Associates</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n"/>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Sivaprakash K</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="5" t="n"/>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sivaprakash-k-0b312a121</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Delivery-Lead Consultant</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Virtusa</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="5" t="n"/>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="5" t="n"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Chandra Mangali</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>chandra_sekhar_mangali@epam.com</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chandra-sekhar-mangali-b88b3331</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Senior Delivery Manager/ Account Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="5" t="n"/>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Ashok Rajavel</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>ashok.rajavel@accenture.com</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashok-rajavel-66844318</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Sumanth Rao</t>
+        </is>
+      </c>
       <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="5" t="n"/>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumanth-rao-42b0996</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Sector Delivery Lead / Service Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Shahil Kumar</t>
+        </is>
+      </c>
       <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="5" t="n"/>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shahil-kumar-a5ab96371</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Representative | Sales &amp; Operations</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Parijat Controlware Inc.</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n"/>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="6" t="n"/>
-      <c r="K82" s="5" t="n"/>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Prabhu Padhy</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>prabhu.padhy@splashbi.com</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prabhu-prasad-padhy-a2b41739</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Lead Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>SplashBI</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n"/>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Indrani Das</t>
+        </is>
+      </c>
       <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="5" t="n"/>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/indrani-das-1621a7108</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Lead Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n"/>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="5" t="n"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Shubhra Agarwal</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>shubhra.agarwal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubhra-agarwal-61837052</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n"/>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Raman Dhingra</t>
+        </is>
+      </c>
       <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="5" t="n"/>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raman-dhingra-24b445181</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Sales Development Representative, Business Analyst</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Closeloop Technologies</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n"/>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="5" t="n"/>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Omkar Mane</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>omkar.mane@accenture.com</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/omkar-mane-43819558</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="5" t="n"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Avik Noronha</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>a.ryan.john.noronha@accenture.com</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aviknoronha</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="5" t="n"/>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Hinesh Bheda</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>hinesh.bheda@accenture.com</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hineshbheda</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="5" t="n"/>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Madhav Prathapa</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>madhav.prathapa@accenture.com</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/madhavprathapa</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="5" t="n"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Mugdha Patil</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>mugdha.patil@accenture.com</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mugdha-patil-mrics-pmp%c2%ae-mapm-lssgb-71b55759</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="5" t="n"/>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Hema Dalwadi</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>hema.dalwadi@accenture.com</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hema-dalwadi-980b3727</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="5" t="n"/>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Vaibhav Pareek</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>vaibhav.pareek@accenture.com</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vaibhav-pareek-53988419</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="5" t="n"/>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Ankit Jaiswal</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>ankit.d.jaiswal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankit-jaiswal-7a16b59b</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="n"/>
-      <c r="H94" s="5" t="n"/>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="5" t="n"/>
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Roopashri Shetty</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>roopashri.c.shetty@accenture.com</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roopashri-shetty</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="5" t="n"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Ankush Khosla</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>ankush.khosla@accenture.com</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankushkhosla33</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="n"/>
-      <c r="H96" s="5" t="n"/>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="5" t="n"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Swapnil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>swapnil.chaudhary@vnvcs.com</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/swapnil-chaudhary-199560250</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Service Delivery Manager / Application Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>V &amp; V Comptech Systems Private Limited</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="5" t="n"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Manish Gupta</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>m.gupta@accenture.com</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manish-gupta-86459926</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="5" t="n"/>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="5" t="n"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Venkades Arjunan</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>venkades.arjunan@accenture.com</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/venkades-arjunan-99a442213</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="n"/>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="5" t="n"/>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="6" t="n"/>
-      <c r="K99" s="5" t="n"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Abhishek Jaiswal</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>abhishek.jaiswal@accenture.com</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abhishek-jaiswal-32283565</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="5" t="n"/>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="5" t="n"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Harsha Dediya</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>harsha.dediya@accenture.com</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsha-dediya-854b4294</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="5" t="n"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Nandish Venkatesh</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>nandish.venkatesh@accenture.com</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nandish-venkatesh-48b93873</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L101" s="5" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="5" t="n"/>
-      <c r="D102" s="5" t="n"/>
-      <c r="E102" s="5" t="n"/>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="5" t="n"/>
-      <c r="I102" s="5" t="n"/>
-      <c r="J102" s="6" t="n"/>
-      <c r="K102" s="5" t="n"/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Jagdish Deshmukh</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>jagdish.deshmukh@globant.com</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jagdish-deshmukh-a3783b80</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Lead Consultant - Project/Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="6" t="n"/>
-      <c r="K103" s="5" t="n"/>
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>manisha.thapa@accenture.com</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manisha-thapa-659b63105</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="6" t="n"/>
-      <c r="K104" s="5" t="n"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Yathiraj Moily</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>yathiraj.moily@accenture.com</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yathirajmoily</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="5" t="n"/>
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Sudha G</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>sudha.g@accenture.com</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sudha-g-ab4575a8</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L105" s="5" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="5" t="n"/>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Saravanan Palani</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>saravanan.palani@accenture.com</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saravanan-palani-72515233</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Lead Manager</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L106" s="5" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="5" t="n"/>
-      <c r="G107" s="5" t="n"/>
-      <c r="H107" s="5" t="n"/>
-      <c r="I107" s="5" t="n"/>
-      <c r="J107" s="6" t="n"/>
-      <c r="K107" s="5" t="n"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Yashvant Patil</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>yashvantmahesh.p@infosys.com</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yashvant-patil-81932771</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Lead Consultant | Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="6" t="n"/>
-      <c r="K108" s="5" t="n"/>
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Shantelle Morris</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>shantelle.morris@burendo.com</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shantelle-morris-42861853</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Manager (Consultant) - Senior Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Burendo</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="5" t="n"/>
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Ernest Nwadinobi</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>ernest.nwadinobi@tombola.com</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ernest-c-nwadinobi-miet-a2397756</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Agile Delivery Manager | Delivery Lead</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>tombola</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n"/>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="5" t="n"/>
-      <c r="D110" s="5" t="n"/>
-      <c r="E110" s="5" t="n"/>
-      <c r="F110" s="5" t="n"/>
-      <c r="G110" s="5" t="n"/>
-      <c r="H110" s="5" t="n"/>
-      <c r="I110" s="5" t="n"/>
-      <c r="J110" s="6" t="n"/>
-      <c r="K110" s="5" t="n"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Darius Young</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>darius.young@cygnus-systems.com</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/darius-young-5b8372257</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Sales and Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Cygnus Group Ltd</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L110" s="5" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n"/>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="5" t="n"/>
-      <c r="H111" s="5" t="n"/>
-      <c r="I111" s="5" t="n"/>
-      <c r="J111" s="6" t="n"/>
-      <c r="K111" s="5" t="n"/>
-      <c r="L111" s="5" t="n"/>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Sakshi Maheshwari</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>sakmahes@cisco.com</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sakshimaheshwari19</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Sales Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>duplicate of existing tracker row</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n"/>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="5" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="5" t="n"/>
-      <c r="H112" s="5" t="n"/>
-      <c r="I112" s="5" t="n"/>
-      <c r="J112" s="6" t="n"/>
-      <c r="K112" s="5" t="n"/>
-      <c r="L112" s="5" t="n"/>
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Katie Collopy</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>katie@maverickmedia.eu</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katie-collopy-37a0191a1</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Sales and Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Maverick Media</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>duplicate of existing tracker row (already Bounced)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="5" t="n"/>
-      <c r="D113" s="5" t="n"/>
-      <c r="E113" s="5" t="n"/>
-      <c r="F113" s="5" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="5" t="n"/>
-      <c r="I113" s="5" t="n"/>
-      <c r="J113" s="6" t="n"/>
-      <c r="K113" s="5" t="n"/>
-      <c r="L113" s="5" t="n"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Mehdi Rabia</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>mehdi.rabia@flatpay.com</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mehdi-rabia-346189389</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Sales Business Development Representative</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Flatpay</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>duplicate of existing tracker row (already Bounced)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="5" t="n"/>
-      <c r="G114" s="5" t="n"/>
-      <c r="H114" s="5" t="n"/>
-      <c r="I114" s="5" t="n"/>
-      <c r="J114" s="6" t="n"/>
-      <c r="K114" s="5" t="n"/>
-      <c r="L114" s="5" t="n"/>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Tristan Sarmiento</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>tristan.sarmiento@amlwatcher.com</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stansarmientooneoff</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Compliance Consultant | APAC &amp; ANZ</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>AML Watcher</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Segment C</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI - API blocked on trial plan)</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>wrong segment title (not SDR/BDR/Delivery)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10811,7 +10811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -10865,77 +10865,84 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>6. This team rotates between multiple free-tier Apollo.io accounts (each renews 75 free lead credits/month) since a paid plan hasn't been purchased yet -- whichever account currently has credits gets connected for that run. This is safe by design: duplicate/bounced/opted-out exclusion is always driven by this Tracker sheet (Email + LinkedIn URL match), never by any single Apollo account's own saved-contacts list, so switching accounts never risks a repeat send or a re-added exclusion regardless of which Apollo account sourced or enriched a lead.</t>
+          <t>6. As of 2026-08-31, Segment A sub-group A1 "Presales" is additionally filtered to 0-7 years of total professional experience -- this applies to Presales titles specifically, not sub-group A2 "Sales", and not the other segments (B, C) which have their own separate experience/tenure criteria already.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>7. If the connected Apollo.io account's prospecting/search API is plan-gated (a free trial can show available lead credits while still blocking apollo_agent_find_prospects with an API_INACCESSIBLE error -- this happened 2026-08-31), the fallback is manual sourcing: search Apollo's own web app by hand (its UI search still works on a trial plan even when the API doesn't), export results to a simple Name/Email/LinkedIn URL/Title/Company/Country spreadsheet, and hand it to the assistant to dedup, log to Apollo Archive, add to Tracker, and send from -- same exclusion rules apply regardless of how a candidate was sourced.</t>
+          <t>7. This team rotates between multiple free-tier Apollo.io accounts (each renews 75 free lead credits/month) since a paid plan hasn't been purchased yet -- whichever account currently has credits gets connected for that run. This is safe by design: duplicate/bounced/opted-out exclusion is always driven by this Tracker sheet (Email + LinkedIn URL match), never by any single Apollo account's own saved-contacts list, so switching accounts never risks a repeat send or a re-added exclusion regardless of which Apollo account sourced or enriched a lead.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>8. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>8. If the connected Apollo.io account's prospecting/search API is plan-gated (a free trial can show available lead credits while still blocking apollo_agent_find_prospects with an API_INACCESSIBLE error -- this happened 2026-08-31), the fallback is manual sourcing: search Apollo's own web app by hand (its UI search still works on a trial plan even when the API doesn't), export results to a simple Name/Email/LinkedIn URL/Title/Company/Country spreadsheet, and hand it to the assistant to dedup, log to Apollo Archive, add to Tracker, and send from -- same exclusion rules apply regardless of how a candidate was sourced.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
+          <t>9. Next Action + Next Action Date tell you (or the automated routines) what to do and when.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>10. Region groups each contact by country (India / Singapore / United Kingdom / Other / Unknown; "Gulf (UAE)" and "Europe" are legacy values from before geography was narrowed, no longer assigned to new rows) -- kept for your own visibility into what went out where. It does not control send timing.</t>
+          <t>10. Days Since Contact calculates automatically from Last Contact Date — use it to spot who's overdue for a follow-up.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>11. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
+          <t>11. Region groups each contact by country (India / Singapore / United Kingdom / Other / Unknown; "Gulf (UAE)" and "Europe" are legacy values from before geography was narrowed, no longer assigned to new rows) -- kept for your own visibility into what went out where. It does not control send timing.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>12. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
+          <t>12. LinkedIn messages are generated as text for you but NOT sent automatically — there is no LinkedIn connector and LinkedIn's terms prohibit automated messaging, so you paste and send them yourself, then update Stage.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>13. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
+          <t>13. Mark Booked = Y and fill Booking Date as soon as a booking confirmation arrives (email/SMS/WhatsApp) — booked contacts are excluded from further follow-ups.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>14. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
+          <t>14. Mark Opted Out = Y and fill Opt-Out Date if someone asks to stop hearing from you (via the email unsubscribe link, a reply, or manually) — opted-out contacts are permanently excluded from all future emails, LinkedIn messages, and even from being re-added if Apollo surfaces them again later.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>15. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+          <t>15. Mark Bounced = Y and fill Bounce Date if you get a "Delivery Status Notification (Failure)" from Gmail for that contact — stop emailing that address, but it's fine to still try LinkedIn if you have their profile URL. The automation checks for these automatically each run.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>16. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
+          <t>16. See email_templates.md / email_templates.html and linkedin_templates.md in this folder for the message sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>17. "Apollo Archive" (third sheet) is a permanent historical log of every candidate Apollo has ever returned to the Monday routine — including duplicates and rejects that never made it into the active Tracker — with richer raw data (title, company, country) for your own future reference. It's a passive record only; it never drives outreach decisions or exclusions on its own.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4903,11 +4903,11 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H60" s="5">
         <f>IF(G60="","",TODAY()-G60)</f>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -4978,11 +4978,11 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H61" s="5">
         <f>IF(G61="","",TODAY()-G61)</f>
@@ -4990,11 +4990,11 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
@@ -5053,11 +5053,11 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H62" s="5">
         <f>IF(G62="","",TODAY()-G62)</f>
@@ -5065,11 +5065,11 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H63" s="5">
         <f>IF(G63="","",TODAY()-G63)</f>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H64" s="5">
         <f>IF(G64="","",TODAY()-G64)</f>
@@ -5215,11 +5215,11 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
@@ -5278,11 +5278,11 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H65" s="5">
         <f>IF(G65="","",TODAY()-G65)</f>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -5422,11 +5422,11 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H67" s="5">
         <f>IF(G67="","",TODAY()-G67)</f>
@@ -5434,11 +5434,11 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H68" s="5">
         <f>IF(G68="","",TODAY()-G68)</f>
@@ -5509,11 +5509,11 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H69" s="5">
         <f>IF(G69="","",TODAY()-G69)</f>
@@ -5584,11 +5584,11 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H70" s="5">
         <f>IF(G70="","",TODAY()-G70)</f>
@@ -5659,11 +5659,11 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -5722,11 +5722,11 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H71" s="5">
         <f>IF(G71="","",TODAY()-G71)</f>
@@ -5734,11 +5734,11 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -5797,11 +5797,11 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H72" s="5">
         <f>IF(G72="","",TODAY()-G72)</f>
@@ -5809,11 +5809,11 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H73" s="5">
         <f>IF(G73="","",TODAY()-G73)</f>
@@ -5884,11 +5884,11 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
@@ -5947,11 +5947,11 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H74" s="5">
         <f>IF(G74="","",TODAY()-G74)</f>
@@ -5959,11 +5959,11 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -6091,11 +6091,11 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H76" s="5">
         <f>IF(G76="","",TODAY()-G76)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -6166,11 +6166,11 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H77" s="5">
         <f>IF(G77="","",TODAY()-G77)</f>
@@ -6178,11 +6178,11 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J77" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H79" s="5">
         <f>IF(G79="","",TODAY()-G79)</f>
@@ -6322,11 +6322,11 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -6385,11 +6385,11 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H80" s="5">
         <f>IF(G80="","",TODAY()-G80)</f>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
@@ -6630,10 +6630,12 @@
       <c r="N83" s="6" t="n"/>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P83" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -6641,7 +6643,7 @@
       </c>
       <c r="R83" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at SplashBI | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at SplashBI | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -6742,11 +6744,11 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H85" s="5">
         <f>IF(G85="","",TODAY()-G85)</f>
@@ -6754,11 +6756,11 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J85" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
@@ -6886,11 +6888,11 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H87" s="5">
         <f>IF(G87="","",TODAY()-G87)</f>
@@ -6898,11 +6900,11 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J87" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
@@ -6961,11 +6963,11 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H88" s="5">
         <f>IF(G88="","",TODAY()-G88)</f>
@@ -6973,11 +6975,11 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
@@ -7036,11 +7038,11 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H89" s="5">
         <f>IF(G89="","",TODAY()-G89)</f>
@@ -7048,11 +7050,11 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -7111,11 +7113,11 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H90" s="5">
         <f>IF(G90="","",TODAY()-G90)</f>
@@ -7123,11 +7125,11 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -7218,10 +7220,12 @@
       <c r="N91" s="6" t="n"/>
       <c r="O91" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P91" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -7229,7 +7233,7 @@
       </c>
       <c r="R91" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -7261,11 +7265,11 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H92" s="5">
         <f>IF(G92="","",TODAY()-G92)</f>
@@ -7273,11 +7277,11 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J92" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
@@ -7368,10 +7372,12 @@
       <c r="N93" s="6" t="n"/>
       <c r="O93" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P93" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -7379,7 +7385,7 @@
       </c>
       <c r="R93" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -7411,11 +7417,11 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H94" s="5">
         <f>IF(G94="","",TODAY()-G94)</f>
@@ -7423,11 +7429,11 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -7486,11 +7492,11 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H95" s="5">
         <f>IF(G95="","",TODAY()-G95)</f>
@@ -7498,11 +7504,11 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J95" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
@@ -7561,11 +7567,11 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H96" s="5">
         <f>IF(G96="","",TODAY()-G96)</f>
@@ -7573,11 +7579,11 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J96" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -7636,11 +7642,11 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H97" s="5">
         <f>IF(G97="","",TODAY()-G97)</f>
@@ -7648,11 +7654,11 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J97" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
@@ -7711,11 +7717,11 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H98" s="5">
         <f>IF(G98="","",TODAY()-G98)</f>
@@ -7723,11 +7729,11 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J98" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7786,11 +7792,11 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H99" s="5">
         <f>IF(G99="","",TODAY()-G99)</f>
@@ -7798,11 +7804,11 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J99" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7893,10 +7899,12 @@
       <c r="N100" s="6" t="n"/>
       <c r="O100" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P100" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -7904,7 +7912,7 @@
       </c>
       <c r="R100" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -7936,11 +7944,11 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H101" s="5">
         <f>IF(G101="","",TODAY()-G101)</f>
@@ -7948,11 +7956,11 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J101" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
@@ -8043,10 +8051,12 @@
       <c r="N102" s="6" t="n"/>
       <c r="O102" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P102" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -8054,7 +8064,7 @@
       </c>
       <c r="R102" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -8118,10 +8128,12 @@
       <c r="N103" s="6" t="n"/>
       <c r="O103" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P103" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -8129,7 +8141,7 @@
       </c>
       <c r="R103" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant - Project role at Globant | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Consultant - Project role at Globant | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -8161,11 +8173,11 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G104" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H104" s="5">
         <f>IF(G104="","",TODAY()-G104)</f>
@@ -8173,11 +8185,11 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J104" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
@@ -8236,11 +8248,11 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H105" s="5">
         <f>IF(G105="","",TODAY()-G105)</f>
@@ -8248,11 +8260,11 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J105" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
@@ -8343,10 +8355,12 @@
       <c r="N106" s="6" t="n"/>
       <c r="O106" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P106" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -8354,7 +8368,7 @@
       </c>
       <c r="R106" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -8418,10 +8432,12 @@
       <c r="N107" s="6" t="n"/>
       <c r="O107" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P107" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="n">
+        <v>46267</v>
+      </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>India</t>
@@ -8429,7 +8445,7 @@
       </c>
       <c r="R107" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Bounced 2026-09-02: Follow-up 1 send failed - "Address not found" (mailer-daemon). Has LinkedIn URL, left Stage/Next Action as-is for manual LinkedIn fallback.</t>
         </is>
       </c>
     </row>
@@ -8461,11 +8477,11 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H108" s="5">
         <f>IF(G108="","",TODAY()-G108)</f>
@@ -8473,11 +8489,11 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J108" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
@@ -8536,11 +8552,11 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H109" s="5">
         <f>IF(G109="","",TODAY()-G109)</f>
@@ -8548,11 +8564,11 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J109" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
@@ -8611,11 +8627,11 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H110" s="5">
         <f>IF(G110="","",TODAY()-G110)</f>
@@ -8623,11 +8639,11 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
@@ -8686,11 +8702,11 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Email 1 Sent</t>
+          <t>Follow-up 1 Sent</t>
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H111" s="5">
         <f>IF(G111="","",TODAY()-G111)</f>
@@ -8698,11 +8714,11 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 1</t>
+          <t>Send Follow-up 2</t>
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4903,11 +4903,11 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H60" s="5">
         <f>IF(G60="","",TODAY()-G60)</f>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -4978,11 +4978,11 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H61" s="5">
         <f>IF(G61="","",TODAY()-G61)</f>
@@ -4990,11 +4990,11 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
@@ -5053,11 +5053,11 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H62" s="5">
         <f>IF(G62="","",TODAY()-G62)</f>
@@ -5065,11 +5065,11 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H63" s="5">
         <f>IF(G63="","",TODAY()-G63)</f>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H64" s="5">
         <f>IF(G64="","",TODAY()-G64)</f>
@@ -5215,11 +5215,11 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
@@ -5278,11 +5278,11 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H65" s="5">
         <f>IF(G65="","",TODAY()-G65)</f>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -5422,11 +5422,11 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H67" s="5">
         <f>IF(G67="","",TODAY()-G67)</f>
@@ -5434,11 +5434,11 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H68" s="5">
         <f>IF(G68="","",TODAY()-G68)</f>
@@ -5509,11 +5509,11 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H69" s="5">
         <f>IF(G69="","",TODAY()-G69)</f>
@@ -5584,11 +5584,11 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H70" s="5">
         <f>IF(G70="","",TODAY()-G70)</f>
@@ -5659,11 +5659,11 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -5722,11 +5722,11 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H71" s="5">
         <f>IF(G71="","",TODAY()-G71)</f>
@@ -5734,11 +5734,11 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -5797,11 +5797,11 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H72" s="5">
         <f>IF(G72="","",TODAY()-G72)</f>
@@ -5809,11 +5809,11 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H73" s="5">
         <f>IF(G73="","",TODAY()-G73)</f>
@@ -5884,11 +5884,11 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
@@ -5947,11 +5947,11 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H74" s="5">
         <f>IF(G74="","",TODAY()-G74)</f>
@@ -5959,11 +5959,11 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -6091,11 +6091,11 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H76" s="5">
         <f>IF(G76="","",TODAY()-G76)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -6166,11 +6166,11 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H77" s="5">
         <f>IF(G77="","",TODAY()-G77)</f>
@@ -6178,11 +6178,11 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J77" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H79" s="5">
         <f>IF(G79="","",TODAY()-G79)</f>
@@ -6322,11 +6322,11 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -6385,11 +6385,11 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H80" s="5">
         <f>IF(G80="","",TODAY()-G80)</f>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
@@ -6744,11 +6744,11 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H85" s="5">
         <f>IF(G85="","",TODAY()-G85)</f>
@@ -6756,11 +6756,11 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J85" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
@@ -6888,11 +6888,11 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H87" s="5">
         <f>IF(G87="","",TODAY()-G87)</f>
@@ -6900,11 +6900,11 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J87" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
@@ -6963,11 +6963,11 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H88" s="5">
         <f>IF(G88="","",TODAY()-G88)</f>
@@ -6975,11 +6975,11 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
@@ -7038,11 +7038,11 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H89" s="5">
         <f>IF(G89="","",TODAY()-G89)</f>
@@ -7050,11 +7050,11 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -7113,11 +7113,11 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H90" s="5">
         <f>IF(G90="","",TODAY()-G90)</f>
@@ -7125,11 +7125,11 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -7265,11 +7265,11 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H92" s="5">
         <f>IF(G92="","",TODAY()-G92)</f>
@@ -7277,11 +7277,11 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J92" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H94" s="5">
         <f>IF(G94="","",TODAY()-G94)</f>
@@ -7429,11 +7429,11 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H95" s="5">
         <f>IF(G95="","",TODAY()-G95)</f>
@@ -7504,11 +7504,11 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J95" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
@@ -7567,11 +7567,11 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H96" s="5">
         <f>IF(G96="","",TODAY()-G96)</f>
@@ -7579,11 +7579,11 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J96" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -7642,11 +7642,11 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H97" s="5">
         <f>IF(G97="","",TODAY()-G97)</f>
@@ -7654,11 +7654,11 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J97" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
@@ -7717,11 +7717,11 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H98" s="5">
         <f>IF(G98="","",TODAY()-G98)</f>
@@ -7729,11 +7729,11 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J98" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7792,11 +7792,11 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H99" s="5">
         <f>IF(G99="","",TODAY()-G99)</f>
@@ -7804,11 +7804,11 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J99" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7944,11 +7944,11 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H101" s="5">
         <f>IF(G101="","",TODAY()-G101)</f>
@@ -7956,11 +7956,11 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J101" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
@@ -8173,11 +8173,11 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G104" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H104" s="5">
         <f>IF(G104="","",TODAY()-G104)</f>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J104" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
@@ -8248,11 +8248,11 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H105" s="5">
         <f>IF(G105="","",TODAY()-G105)</f>
@@ -8260,11 +8260,11 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J105" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
@@ -8477,11 +8477,11 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H108" s="5">
         <f>IF(G108="","",TODAY()-G108)</f>
@@ -8489,11 +8489,11 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J108" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
@@ -8552,11 +8552,11 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H109" s="5">
         <f>IF(G109="","",TODAY()-G109)</f>
@@ -8564,11 +8564,11 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J109" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
@@ -8627,11 +8627,11 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H110" s="5">
         <f>IF(G110="","",TODAY()-G110)</f>
@@ -8639,11 +8639,11 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
@@ -8702,11 +8702,11 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 1 Sent</t>
+          <t>Follow-up 2 Sent</t>
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H111" s="5">
         <f>IF(G111="","",TODAY()-G111)</f>
@@ -8714,11 +8714,11 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 2</t>
+          <t>Send Follow-up 3</t>
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
